--- a/data/cox_xlsx/PAALb.CO.xlsx
+++ b/data/cox_xlsx/PAALb.CO.xlsx
@@ -1416,7 +1416,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1493,6 +1493,9 @@
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="9" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="7" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="9" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -11413,15 +11416,33 @@
       <c r="O47" s="16">
         <v>1447.97</v>
       </c>
-      <c r="P47" s="15"/>
+      <c r="P47" s="15">
+        <f>P49+P52+P54+P57+P60</f>
+        <v>1490.95</v>
+      </c>
       <c r="Q47" s="16">
         <v>1381.92</v>
       </c>
-      <c r="R47" s="15"/>
-      <c r="S47" s="15"/>
-      <c r="T47" s="15"/>
-      <c r="U47" s="15"/>
-      <c r="V47" s="15"/>
+      <c r="R47" s="15">
+        <f t="shared" ref="R47:V47" si="1">R49+R52+R54+R57+R60</f>
+        <v>1341.45</v>
+      </c>
+      <c r="S47" s="15">
+        <f t="shared" si="1"/>
+        <v>1203.21</v>
+      </c>
+      <c r="T47" s="26">
+        <f t="shared" si="1"/>
+        <v>936.79</v>
+      </c>
+      <c r="U47" s="26">
+        <f t="shared" si="1"/>
+        <v>972.12</v>
+      </c>
+      <c r="V47" s="26">
+        <f t="shared" si="1"/>
+        <v>791.62</v>
+      </c>
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
@@ -19415,67 +19436,67 @@
       <c r="A59" s="17" t="s">
         <v>332</v>
       </c>
-      <c r="B59" s="26">
+      <c r="B59" s="27">
         <v>-1591.47</v>
       </c>
-      <c r="C59" s="26">
+      <c r="C59" s="27">
         <v>-1233.77</v>
       </c>
-      <c r="D59" s="26">
+      <c r="D59" s="27">
         <v>-1228.35</v>
       </c>
-      <c r="E59" s="26">
+      <c r="E59" s="27">
         <v>-1555.44</v>
       </c>
-      <c r="F59" s="26">
+      <c r="F59" s="27">
         <v>-941.56</v>
       </c>
-      <c r="G59" s="26">
+      <c r="G59" s="27">
         <v>-946.34</v>
       </c>
-      <c r="H59" s="26">
+      <c r="H59" s="27">
         <v>-868.22</v>
       </c>
-      <c r="I59" s="26">
+      <c r="I59" s="27">
         <v>-506.14</v>
       </c>
-      <c r="J59" s="26">
+      <c r="J59" s="27">
         <v>-604.81</v>
       </c>
-      <c r="K59" s="26">
+      <c r="K59" s="27">
         <v>-963.73</v>
       </c>
-      <c r="L59" s="26">
+      <c r="L59" s="27">
         <v>-735.53</v>
       </c>
-      <c r="M59" s="26">
+      <c r="M59" s="27">
         <v>-282.58</v>
       </c>
-      <c r="N59" s="26">
+      <c r="N59" s="27">
         <v>-376.77</v>
       </c>
-      <c r="O59" s="26">
+      <c r="O59" s="27">
         <v>-287.89</v>
       </c>
-      <c r="P59" s="26">
+      <c r="P59" s="27">
         <v>-452.55</v>
       </c>
-      <c r="Q59" s="26">
+      <c r="Q59" s="27">
         <v>-235.46</v>
       </c>
-      <c r="R59" s="26">
+      <c r="R59" s="27">
         <v>-323.05</v>
       </c>
-      <c r="S59" s="26">
+      <c r="S59" s="27">
         <v>-338.1</v>
       </c>
-      <c r="T59" s="26">
+      <c r="T59" s="27">
         <v>-186.9</v>
       </c>
-      <c r="U59" s="26">
+      <c r="U59" s="27">
         <v>-300.73</v>
       </c>
-      <c r="V59" s="26">
+      <c r="V59" s="27">
         <v>-139.27</v>
       </c>
     </row>
@@ -19917,10 +19938,10 @@
       <c r="A71" s="17" t="s">
         <v>342</v>
       </c>
-      <c r="B71" s="26">
+      <c r="B71" s="27">
         <v>-1461.2</v>
       </c>
-      <c r="C71" s="26">
+      <c r="C71" s="27">
         <v>-2138.11</v>
       </c>
       <c r="D71" s="25">
@@ -19929,25 +19950,25 @@
       <c r="E71" s="19">
         <v>705.19</v>
       </c>
-      <c r="F71" s="26">
+      <c r="F71" s="27">
         <v>-601.7</v>
       </c>
-      <c r="G71" s="26">
+      <c r="G71" s="27">
         <v>-448.57</v>
       </c>
-      <c r="H71" s="26">
+      <c r="H71" s="27">
         <v>-305.67</v>
       </c>
-      <c r="I71" s="26">
+      <c r="I71" s="27">
         <v>-154.65</v>
       </c>
-      <c r="J71" s="26">
+      <c r="J71" s="27">
         <v>-118.92</v>
       </c>
       <c r="K71" s="25">
         <v>-96.69</v>
       </c>
-      <c r="L71" s="26">
+      <c r="L71" s="27">
         <v>-107.14</v>
       </c>
       <c r="M71" s="25">
@@ -20204,16 +20225,16 @@
       <c r="B76" s="19">
         <v>1335.64</v>
       </c>
-      <c r="C76" s="26">
+      <c r="C76" s="27">
         <v>-298.34</v>
       </c>
       <c r="D76" s="19">
         <v>387.59</v>
       </c>
-      <c r="E76" s="26">
+      <c r="E76" s="27">
         <v>-169.25</v>
       </c>
-      <c r="F76" s="26">
+      <c r="F76" s="27">
         <v>-881.66</v>
       </c>
       <c r="G76" s="19">
@@ -20225,10 +20246,10 @@
       <c r="I76" s="19">
         <v>323.04</v>
       </c>
-      <c r="J76" s="26">
+      <c r="J76" s="27">
         <v>-118.04</v>
       </c>
-      <c r="K76" s="26">
+      <c r="K76" s="27">
         <v>-540.88</v>
       </c>
       <c r="L76" s="19">
@@ -20237,7 +20258,7 @@
       <c r="M76" s="19">
         <v>359.62</v>
       </c>
-      <c r="N76" s="26">
+      <c r="N76" s="27">
         <v>-358.51</v>
       </c>
       <c r="O76" s="24">
@@ -20288,7 +20309,7 @@
       <c r="R77" s="15"/>
       <c r="S77" s="15"/>
       <c r="T77" s="15"/>
-      <c r="U77" s="27">
+      <c r="U77" s="28">
         <v>0.0</v>
       </c>
       <c r="V77" s="15"/>
@@ -22066,3902 +22087,3902 @@
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="28" t="s">
+      <c r="A20" s="29" t="s">
         <v>371</v>
       </c>
-      <c r="B20" s="29"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="29"/>
-      <c r="J20" s="29"/>
-      <c r="K20" s="29"/>
-      <c r="L20" s="29"/>
-      <c r="M20" s="29"/>
-      <c r="N20" s="29"/>
-      <c r="O20" s="29"/>
-      <c r="P20" s="29"/>
-      <c r="Q20" s="29"/>
-      <c r="R20" s="29"/>
-      <c r="S20" s="29"/>
-      <c r="T20" s="29"/>
-      <c r="U20" s="29"/>
-      <c r="V20" s="29"/>
-      <c r="W20" s="29"/>
-      <c r="X20" s="29"/>
-      <c r="Y20" s="29"/>
-      <c r="Z20" s="29"/>
-      <c r="AA20" s="29"/>
-      <c r="AB20" s="29"/>
-      <c r="AC20" s="29"/>
-      <c r="AD20" s="29"/>
-      <c r="AE20" s="29"/>
-      <c r="AF20" s="29"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="30"/>
+      <c r="N20" s="30"/>
+      <c r="O20" s="30"/>
+      <c r="P20" s="30"/>
+      <c r="Q20" s="30"/>
+      <c r="R20" s="30"/>
+      <c r="S20" s="30"/>
+      <c r="T20" s="30"/>
+      <c r="U20" s="30"/>
+      <c r="V20" s="30"/>
+      <c r="W20" s="30"/>
+      <c r="X20" s="30"/>
+      <c r="Y20" s="30"/>
+      <c r="Z20" s="30"/>
+      <c r="AA20" s="30"/>
+      <c r="AB20" s="30"/>
+      <c r="AC20" s="30"/>
+      <c r="AD20" s="30"/>
+      <c r="AE20" s="30"/>
+      <c r="AF20" s="30"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="30" t="s">
+      <c r="A21" s="31" t="s">
         <v>371</v>
       </c>
-      <c r="B21" s="31">
+      <c r="B21" s="32">
         <v>19693.17</v>
       </c>
-      <c r="C21" s="31">
+      <c r="C21" s="32">
         <v>13170.89</v>
       </c>
-      <c r="D21" s="31">
+      <c r="D21" s="32">
         <v>11589.26</v>
       </c>
-      <c r="E21" s="32">
+      <c r="E21" s="33">
         <v>6762.7</v>
       </c>
-      <c r="F21" s="32">
+      <c r="F21" s="33">
         <v>6276.3</v>
       </c>
-      <c r="G21" s="32">
+      <c r="G21" s="33">
         <v>6114.62</v>
       </c>
-      <c r="H21" s="32">
+      <c r="H21" s="33">
         <v>5675.19</v>
       </c>
-      <c r="I21" s="32">
+      <c r="I21" s="33">
         <v>6367.1</v>
       </c>
-      <c r="J21" s="32">
+      <c r="J21" s="33">
         <v>5101.79</v>
       </c>
-      <c r="K21" s="32">
+      <c r="K21" s="33">
         <v>4094.97</v>
       </c>
-      <c r="L21" s="32">
+      <c r="L21" s="33">
         <v>5723.97</v>
       </c>
-      <c r="M21" s="32">
+      <c r="M21" s="33">
         <v>2467.25</v>
       </c>
-      <c r="N21" s="32">
+      <c r="N21" s="33">
         <v>2146.32</v>
       </c>
-      <c r="O21" s="32">
+      <c r="O21" s="33">
         <v>981.08</v>
       </c>
-      <c r="P21" s="32">
+      <c r="P21" s="33">
         <v>1089.14</v>
       </c>
-      <c r="Q21" s="32">
+      <c r="Q21" s="33">
         <v>1052.02</v>
       </c>
-      <c r="R21" s="32">
+      <c r="R21" s="33">
         <v>1501.54</v>
       </c>
-      <c r="S21" s="32">
+      <c r="S21" s="33">
         <v>1473.91</v>
       </c>
-      <c r="T21" s="32">
+      <c r="T21" s="33">
         <v>2047.17</v>
       </c>
-      <c r="U21" s="32">
+      <c r="U21" s="33">
         <v>1627.05</v>
       </c>
-      <c r="V21" s="32">
+      <c r="V21" s="33">
         <v>1276.55</v>
       </c>
-      <c r="W21" s="32">
+      <c r="W21" s="33">
         <v>842.47</v>
       </c>
-      <c r="X21" s="32">
+      <c r="X21" s="33">
         <v>617.89</v>
       </c>
-      <c r="Y21" s="32">
+      <c r="Y21" s="33">
         <v>692.09</v>
       </c>
-      <c r="Z21" s="32">
+      <c r="Z21" s="33">
         <v>753.74</v>
       </c>
-      <c r="AA21" s="32">
+      <c r="AA21" s="33">
         <v>837.03</v>
       </c>
-      <c r="AB21" s="32">
+      <c r="AB21" s="33">
         <v>739.03</v>
       </c>
-      <c r="AC21" s="32">
+      <c r="AC21" s="33">
         <v>678.76</v>
       </c>
-      <c r="AD21" s="32">
+      <c r="AD21" s="33">
         <v>949.43</v>
       </c>
-      <c r="AE21" s="32">
+      <c r="AE21" s="33">
         <v>916.36</v>
       </c>
-      <c r="AF21" s="32">
+      <c r="AF21" s="33">
         <v>672.72</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="30" t="s">
+      <c r="A22" s="31" t="s">
         <v>372</v>
       </c>
-      <c r="B22" s="31">
+      <c r="B22" s="32">
         <v>11890.74</v>
       </c>
-      <c r="C22" s="32">
+      <c r="C22" s="33">
         <v>9292.11</v>
       </c>
-      <c r="D22" s="32">
+      <c r="D22" s="33">
         <v>7698.58</v>
       </c>
-      <c r="E22" s="32">
+      <c r="E22" s="33">
         <v>6538.28</v>
       </c>
-      <c r="F22" s="32">
+      <c r="F22" s="33">
         <v>6020.41</v>
       </c>
-      <c r="G22" s="32">
+      <c r="G22" s="33">
         <v>6139.0</v>
       </c>
-      <c r="H22" s="32">
+      <c r="H22" s="33">
         <v>5634.5</v>
       </c>
-      <c r="I22" s="32">
+      <c r="I22" s="33">
         <v>4869.11</v>
       </c>
-      <c r="J22" s="32">
+      <c r="J22" s="33">
         <v>4082.75</v>
       </c>
-      <c r="K22" s="32">
+      <c r="K22" s="33">
         <v>3161.04</v>
       </c>
-      <c r="L22" s="32">
+      <c r="L22" s="33">
         <v>2741.11</v>
       </c>
-      <c r="M22" s="32">
+      <c r="M22" s="33">
         <v>1577.72</v>
       </c>
-      <c r="N22" s="32">
+      <c r="N22" s="33">
         <v>1373.44</v>
       </c>
-      <c r="O22" s="32">
+      <c r="O22" s="33">
         <v>1117.07</v>
       </c>
-      <c r="P22" s="32">
+      <c r="P22" s="33">
         <v>1403.72</v>
       </c>
-      <c r="Q22" s="32">
+      <c r="Q22" s="33">
         <v>1520.85</v>
       </c>
-      <c r="R22" s="32">
+      <c r="R22" s="33">
         <v>1659.52</v>
       </c>
-      <c r="S22" s="32">
+      <c r="S22" s="33">
         <v>1494.37</v>
       </c>
-      <c r="T22" s="32">
+      <c r="T22" s="33">
         <v>1231.47</v>
       </c>
-      <c r="U22" s="32">
+      <c r="U22" s="33">
         <v>1042.77</v>
       </c>
-      <c r="V22" s="32">
+      <c r="V22" s="33">
         <v>826.68</v>
       </c>
-      <c r="W22" s="32">
+      <c r="W22" s="33">
         <v>780.49</v>
       </c>
-      <c r="X22" s="32">
+      <c r="X22" s="33">
         <v>753.8</v>
       </c>
-      <c r="Y22" s="32">
+      <c r="Y22" s="33">
         <v>674.84</v>
       </c>
-      <c r="Z22" s="32">
+      <c r="Z22" s="33">
         <v>788.89</v>
       </c>
-      <c r="AA22" s="32">
+      <c r="AA22" s="33">
         <v>806.58</v>
       </c>
-      <c r="AB22" s="32">
+      <c r="AB22" s="33">
         <v>787.24</v>
       </c>
-      <c r="AC22" s="31"/>
-      <c r="AD22" s="31"/>
-      <c r="AE22" s="31"/>
-      <c r="AF22" s="31"/>
+      <c r="AC22" s="32"/>
+      <c r="AD22" s="32"/>
+      <c r="AE22" s="32"/>
+      <c r="AF22" s="32"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="28" t="s">
+      <c r="A23" s="29" t="s">
         <v>373</v>
       </c>
-      <c r="B23" s="29"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="29"/>
-      <c r="J23" s="29"/>
-      <c r="K23" s="29"/>
-      <c r="L23" s="29"/>
-      <c r="M23" s="29"/>
-      <c r="N23" s="29"/>
-      <c r="O23" s="29"/>
-      <c r="P23" s="29"/>
-      <c r="Q23" s="29"/>
-      <c r="R23" s="29"/>
-      <c r="S23" s="29"/>
-      <c r="T23" s="29"/>
-      <c r="U23" s="29"/>
-      <c r="V23" s="29"/>
-      <c r="W23" s="29"/>
-      <c r="X23" s="29"/>
-      <c r="Y23" s="29"/>
-      <c r="Z23" s="29"/>
-      <c r="AA23" s="29"/>
-      <c r="AB23" s="29"/>
-      <c r="AC23" s="29"/>
-      <c r="AD23" s="29"/>
-      <c r="AE23" s="29"/>
-      <c r="AF23" s="29"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="30"/>
+      <c r="M23" s="30"/>
+      <c r="N23" s="30"/>
+      <c r="O23" s="30"/>
+      <c r="P23" s="30"/>
+      <c r="Q23" s="30"/>
+      <c r="R23" s="30"/>
+      <c r="S23" s="30"/>
+      <c r="T23" s="30"/>
+      <c r="U23" s="30"/>
+      <c r="V23" s="30"/>
+      <c r="W23" s="30"/>
+      <c r="X23" s="30"/>
+      <c r="Y23" s="30"/>
+      <c r="Z23" s="30"/>
+      <c r="AA23" s="30"/>
+      <c r="AB23" s="30"/>
+      <c r="AC23" s="30"/>
+      <c r="AD23" s="30"/>
+      <c r="AE23" s="30"/>
+      <c r="AF23" s="30"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="30" t="s">
+      <c r="A24" s="31" t="s">
         <v>373</v>
       </c>
-      <c r="B24" s="31">
+      <c r="B24" s="32">
         <v>19650.8</v>
       </c>
-      <c r="C24" s="31">
+      <c r="C24" s="32">
         <v>11614.67</v>
       </c>
-      <c r="D24" s="32">
+      <c r="D24" s="33">
         <v>9356.27</v>
       </c>
-      <c r="E24" s="32">
+      <c r="E24" s="33">
         <v>5103.94</v>
       </c>
-      <c r="F24" s="32">
+      <c r="F24" s="33">
         <v>6813.44</v>
       </c>
-      <c r="G24" s="32">
+      <c r="G24" s="33">
         <v>7490.86</v>
       </c>
-      <c r="H24" s="32">
+      <c r="H24" s="33">
         <v>6285.9</v>
       </c>
-      <c r="I24" s="32">
+      <c r="I24" s="33">
         <v>6568.34</v>
       </c>
-      <c r="J24" s="32">
+      <c r="J24" s="33">
         <v>4986.14</v>
       </c>
-      <c r="K24" s="32">
+      <c r="K24" s="33">
         <v>4088.03</v>
       </c>
-      <c r="L24" s="32">
+      <c r="L24" s="33">
         <v>6263.52</v>
       </c>
-      <c r="M24" s="32">
+      <c r="M24" s="33">
         <v>2270.91</v>
       </c>
-      <c r="N24" s="32">
+      <c r="N24" s="33">
         <v>1581.83</v>
       </c>
-      <c r="O24" s="32">
+      <c r="O24" s="33">
         <v>833.54</v>
       </c>
-      <c r="P24" s="32">
+      <c r="P24" s="33">
         <v>845.24</v>
       </c>
-      <c r="Q24" s="32">
+      <c r="Q24" s="33">
         <v>944.6</v>
       </c>
-      <c r="R24" s="32">
+      <c r="R24" s="33">
         <v>1399.41</v>
       </c>
-      <c r="S24" s="32">
+      <c r="S24" s="33">
         <v>1168.39</v>
       </c>
-      <c r="T24" s="32">
+      <c r="T24" s="33">
         <v>1702.26</v>
       </c>
-      <c r="U24" s="32">
+      <c r="U24" s="33">
         <v>1191.16</v>
       </c>
-      <c r="V24" s="32">
+      <c r="V24" s="33">
         <v>1040.0</v>
       </c>
-      <c r="W24" s="32">
+      <c r="W24" s="33">
         <v>616.96</v>
       </c>
-      <c r="X24" s="32">
+      <c r="X24" s="33">
         <v>419.42</v>
       </c>
-      <c r="Y24" s="32">
+      <c r="Y24" s="33">
         <v>418.9</v>
       </c>
-      <c r="Z24" s="32">
+      <c r="Z24" s="33">
         <v>389.01</v>
       </c>
-      <c r="AA24" s="32">
+      <c r="AA24" s="33">
         <v>742.45</v>
       </c>
-      <c r="AB24" s="32">
+      <c r="AB24" s="33">
         <v>680.43</v>
       </c>
-      <c r="AC24" s="32">
+      <c r="AC24" s="33">
         <v>669.7</v>
       </c>
-      <c r="AD24" s="32">
+      <c r="AD24" s="33">
         <v>942.84</v>
       </c>
-      <c r="AE24" s="32">
+      <c r="AE24" s="33">
         <v>955.61</v>
       </c>
-      <c r="AF24" s="32">
+      <c r="AF24" s="33">
         <v>715.77</v>
       </c>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="30" t="s">
+      <c r="A25" s="31" t="s">
         <v>374</v>
       </c>
-      <c r="B25" s="31">
+      <c r="B25" s="32">
         <v>10870.44</v>
       </c>
-      <c r="C25" s="32">
+      <c r="C25" s="33">
         <v>8571.74</v>
       </c>
-      <c r="D25" s="32">
+      <c r="D25" s="33">
         <v>7444.46</v>
       </c>
-      <c r="E25" s="32">
+      <c r="E25" s="33">
         <v>6766.16</v>
       </c>
-      <c r="F25" s="32">
+      <c r="F25" s="33">
         <v>6526.55</v>
       </c>
-      <c r="G25" s="32">
+      <c r="G25" s="33">
         <v>6567.47</v>
       </c>
-      <c r="H25" s="32">
+      <c r="H25" s="33">
         <v>5885.3</v>
       </c>
-      <c r="I25" s="32">
+      <c r="I25" s="33">
         <v>4946.27</v>
       </c>
-      <c r="J25" s="32">
+      <c r="J25" s="33">
         <v>3988.73</v>
       </c>
-      <c r="K25" s="32">
+      <c r="K25" s="33">
         <v>3057.37</v>
       </c>
-      <c r="L25" s="32">
+      <c r="L25" s="33">
         <v>2573.95</v>
       </c>
-      <c r="M25" s="32">
+      <c r="M25" s="33">
         <v>1320.84</v>
       </c>
-      <c r="N25" s="32">
+      <c r="N25" s="33">
         <v>1136.09</v>
       </c>
-      <c r="O25" s="32">
+      <c r="O25" s="33">
         <v>950.01</v>
       </c>
-      <c r="P25" s="32">
+      <c r="P25" s="33">
         <v>1186.04</v>
       </c>
-      <c r="Q25" s="32">
+      <c r="Q25" s="33">
         <v>1264.8</v>
       </c>
-      <c r="R25" s="32">
+      <c r="R25" s="33">
         <v>1360.74</v>
       </c>
-      <c r="S25" s="32">
+      <c r="S25" s="33">
         <v>1177.84</v>
       </c>
-      <c r="T25" s="32">
+      <c r="T25" s="33">
         <v>956.78</v>
       </c>
-      <c r="U25" s="32">
+      <c r="U25" s="33">
         <v>759.21</v>
       </c>
-      <c r="V25" s="32">
+      <c r="V25" s="33">
         <v>569.64</v>
       </c>
-      <c r="W25" s="32">
+      <c r="W25" s="33">
         <v>538.35</v>
       </c>
-      <c r="X25" s="32">
+      <c r="X25" s="33">
         <v>547.13</v>
       </c>
-      <c r="Y25" s="32">
+      <c r="Y25" s="33">
         <v>524.88</v>
       </c>
-      <c r="Z25" s="32">
+      <c r="Z25" s="33">
         <v>682.16</v>
       </c>
-      <c r="AA25" s="32">
+      <c r="AA25" s="33">
         <v>780.82</v>
       </c>
-      <c r="AB25" s="32">
+      <c r="AB25" s="33">
         <v>788.58</v>
       </c>
-      <c r="AC25" s="31"/>
-      <c r="AD25" s="31"/>
-      <c r="AE25" s="31"/>
-      <c r="AF25" s="31"/>
+      <c r="AC25" s="32"/>
+      <c r="AD25" s="32"/>
+      <c r="AE25" s="32"/>
+      <c r="AF25" s="32"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="28" t="s">
+      <c r="A26" s="29" t="s">
         <v>375</v>
       </c>
-      <c r="B26" s="29"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="29"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="29"/>
-      <c r="I26" s="29"/>
-      <c r="J26" s="29"/>
-      <c r="K26" s="29"/>
-      <c r="L26" s="29"/>
-      <c r="M26" s="29"/>
-      <c r="N26" s="29"/>
-      <c r="O26" s="29"/>
-      <c r="P26" s="29"/>
-      <c r="Q26" s="29"/>
-      <c r="R26" s="29"/>
-      <c r="S26" s="29"/>
-      <c r="T26" s="29"/>
-      <c r="U26" s="29"/>
-      <c r="V26" s="29"/>
-      <c r="W26" s="29"/>
-      <c r="X26" s="29"/>
-      <c r="Y26" s="29"/>
-      <c r="Z26" s="29"/>
-      <c r="AA26" s="29"/>
-      <c r="AB26" s="29"/>
-      <c r="AC26" s="29"/>
-      <c r="AD26" s="29"/>
-      <c r="AE26" s="29"/>
-      <c r="AF26" s="29"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="30"/>
+      <c r="L26" s="30"/>
+      <c r="M26" s="30"/>
+      <c r="N26" s="30"/>
+      <c r="O26" s="30"/>
+      <c r="P26" s="30"/>
+      <c r="Q26" s="30"/>
+      <c r="R26" s="30"/>
+      <c r="S26" s="30"/>
+      <c r="T26" s="30"/>
+      <c r="U26" s="30"/>
+      <c r="V26" s="30"/>
+      <c r="W26" s="30"/>
+      <c r="X26" s="30"/>
+      <c r="Y26" s="30"/>
+      <c r="Z26" s="30"/>
+      <c r="AA26" s="30"/>
+      <c r="AB26" s="30"/>
+      <c r="AC26" s="30"/>
+      <c r="AD26" s="30"/>
+      <c r="AE26" s="30"/>
+      <c r="AF26" s="30"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="30" t="s">
+      <c r="A27" s="31" t="s">
         <v>376</v>
       </c>
-      <c r="B27" s="32">
+      <c r="B27" s="33">
         <v>1076.64</v>
       </c>
-      <c r="C27" s="32">
+      <c r="C27" s="33">
         <v>636.35</v>
       </c>
-      <c r="D27" s="32">
+      <c r="D27" s="33">
         <v>490.83</v>
       </c>
-      <c r="E27" s="32">
+      <c r="E27" s="33">
         <v>267.75</v>
       </c>
-      <c r="F27" s="32">
+      <c r="F27" s="33">
         <v>357.44</v>
       </c>
-      <c r="G27" s="32">
+      <c r="G27" s="33">
         <v>392.97</v>
       </c>
-      <c r="H27" s="32">
+      <c r="H27" s="33">
         <v>294.74</v>
       </c>
-      <c r="I27" s="32">
+      <c r="I27" s="33">
         <v>307.98</v>
       </c>
-      <c r="J27" s="32">
+      <c r="J27" s="33">
         <v>233.79</v>
       </c>
-      <c r="K27" s="32">
+      <c r="K27" s="33">
         <v>191.68</v>
       </c>
-      <c r="L27" s="32">
+      <c r="L27" s="33">
         <v>292.21</v>
       </c>
-      <c r="M27" s="32">
+      <c r="M27" s="33">
         <v>105.94</v>
       </c>
-      <c r="N27" s="33">
+      <c r="N27" s="34">
         <v>74.26</v>
       </c>
-      <c r="O27" s="33">
+      <c r="O27" s="34">
         <v>39.13</v>
       </c>
-      <c r="P27" s="33">
+      <c r="P27" s="34">
         <v>39.68</v>
       </c>
-      <c r="Q27" s="33">
+      <c r="Q27" s="34">
         <v>44.35</v>
       </c>
-      <c r="R27" s="33">
+      <c r="R27" s="34">
         <v>65.7</v>
       </c>
-      <c r="S27" s="33">
+      <c r="S27" s="34">
         <v>54.85</v>
       </c>
-      <c r="T27" s="33">
+      <c r="T27" s="34">
         <v>79.92</v>
       </c>
-      <c r="U27" s="33">
+      <c r="U27" s="34">
         <v>55.92</v>
       </c>
-      <c r="V27" s="33">
+      <c r="V27" s="34">
         <v>48.83</v>
       </c>
-      <c r="W27" s="33">
+      <c r="W27" s="34">
         <v>28.97</v>
       </c>
-      <c r="X27" s="33">
+      <c r="X27" s="34">
         <v>19.69</v>
       </c>
-      <c r="Y27" s="33">
+      <c r="Y27" s="34">
         <v>19.67</v>
       </c>
-      <c r="Z27" s="33">
+      <c r="Z27" s="34">
         <v>18.26</v>
       </c>
-      <c r="AA27" s="33">
+      <c r="AA27" s="34">
         <v>34.86</v>
       </c>
-      <c r="AB27" s="33">
+      <c r="AB27" s="34">
         <v>31.94</v>
       </c>
-      <c r="AC27" s="33">
+      <c r="AC27" s="34">
         <v>31.44</v>
       </c>
-      <c r="AD27" s="33">
+      <c r="AD27" s="34">
         <v>44.26</v>
       </c>
-      <c r="AE27" s="33">
+      <c r="AE27" s="34">
         <v>44.86</v>
       </c>
-      <c r="AF27" s="33">
+      <c r="AF27" s="34">
         <v>34.0</v>
       </c>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="31" t="s">
         <v>377</v>
       </c>
-      <c r="B28" s="32">
+      <c r="B28" s="33">
         <v>584.81</v>
       </c>
-      <c r="C28" s="32">
+      <c r="C28" s="33">
         <v>455.09</v>
       </c>
-      <c r="D28" s="32">
+      <c r="D28" s="33">
         <v>382.55</v>
       </c>
-      <c r="E28" s="32">
+      <c r="E28" s="33">
         <v>339.1</v>
       </c>
-      <c r="F28" s="32">
+      <c r="F28" s="33">
         <v>321.35</v>
       </c>
-      <c r="G28" s="32">
+      <c r="G28" s="33">
         <v>316.29</v>
       </c>
-      <c r="H28" s="32">
+      <c r="H28" s="33">
         <v>275.65</v>
       </c>
-      <c r="I28" s="32">
+      <c r="I28" s="33">
         <v>231.51</v>
       </c>
-      <c r="J28" s="32">
+      <c r="J28" s="33">
         <v>186.63</v>
       </c>
-      <c r="K28" s="32">
+      <c r="K28" s="33">
         <v>142.99</v>
       </c>
-      <c r="L28" s="32">
+      <c r="L28" s="33">
         <v>120.31</v>
       </c>
-      <c r="M28" s="33">
+      <c r="M28" s="34">
         <v>61.88</v>
       </c>
-      <c r="N28" s="33">
+      <c r="N28" s="34">
         <v>53.34</v>
       </c>
-      <c r="O28" s="33">
+      <c r="O28" s="34">
         <v>44.6</v>
       </c>
-      <c r="P28" s="33">
+      <c r="P28" s="34">
         <v>55.68</v>
       </c>
-      <c r="Q28" s="33">
+      <c r="Q28" s="34">
         <v>59.38</v>
       </c>
-      <c r="R28" s="33">
+      <c r="R28" s="34">
         <v>63.88</v>
       </c>
-      <c r="S28" s="33">
+      <c r="S28" s="34">
         <v>55.3</v>
       </c>
-      <c r="T28" s="33">
+      <c r="T28" s="34">
         <v>44.92</v>
       </c>
-      <c r="U28" s="33">
+      <c r="U28" s="34">
         <v>35.64</v>
       </c>
-      <c r="V28" s="33">
+      <c r="V28" s="34">
         <v>26.74</v>
       </c>
-      <c r="W28" s="33">
+      <c r="W28" s="34">
         <v>25.27</v>
       </c>
-      <c r="X28" s="33">
+      <c r="X28" s="34">
         <v>25.69</v>
       </c>
-      <c r="Y28" s="33">
+      <c r="Y28" s="34">
         <v>24.64</v>
       </c>
-      <c r="Z28" s="33">
+      <c r="Z28" s="34">
         <v>32.03</v>
       </c>
-      <c r="AA28" s="33">
+      <c r="AA28" s="34">
         <v>36.66</v>
       </c>
-      <c r="AB28" s="33">
+      <c r="AB28" s="34">
         <v>37.1</v>
       </c>
-      <c r="AC28" s="31"/>
-      <c r="AD28" s="31"/>
-      <c r="AE28" s="31"/>
-      <c r="AF28" s="31"/>
+      <c r="AC28" s="32"/>
+      <c r="AD28" s="32"/>
+      <c r="AE28" s="32"/>
+      <c r="AF28" s="32"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="28" t="s">
+      <c r="A29" s="29" t="s">
         <v>378</v>
       </c>
-      <c r="B29" s="29"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29"/>
-      <c r="I29" s="29"/>
-      <c r="J29" s="29"/>
-      <c r="K29" s="29"/>
-      <c r="L29" s="29"/>
-      <c r="M29" s="29"/>
-      <c r="N29" s="29"/>
-      <c r="O29" s="29"/>
-      <c r="P29" s="29"/>
-      <c r="Q29" s="29"/>
-      <c r="R29" s="29"/>
-      <c r="S29" s="29"/>
-      <c r="T29" s="29"/>
-      <c r="U29" s="29"/>
-      <c r="V29" s="29"/>
-      <c r="W29" s="29"/>
-      <c r="X29" s="29"/>
-      <c r="Y29" s="29"/>
-      <c r="Z29" s="29"/>
-      <c r="AA29" s="29"/>
-      <c r="AB29" s="29"/>
-      <c r="AC29" s="29"/>
-      <c r="AD29" s="29"/>
-      <c r="AE29" s="29"/>
-      <c r="AF29" s="29"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="30"/>
+      <c r="N29" s="30"/>
+      <c r="O29" s="30"/>
+      <c r="P29" s="30"/>
+      <c r="Q29" s="30"/>
+      <c r="R29" s="30"/>
+      <c r="S29" s="30"/>
+      <c r="T29" s="30"/>
+      <c r="U29" s="30"/>
+      <c r="V29" s="30"/>
+      <c r="W29" s="30"/>
+      <c r="X29" s="30"/>
+      <c r="Y29" s="30"/>
+      <c r="Z29" s="30"/>
+      <c r="AA29" s="30"/>
+      <c r="AB29" s="30"/>
+      <c r="AC29" s="30"/>
+      <c r="AD29" s="30"/>
+      <c r="AE29" s="30"/>
+      <c r="AF29" s="30"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="30" t="s">
+      <c r="A30" s="31" t="s">
         <v>379</v>
       </c>
-      <c r="B30" s="34">
+      <c r="B30" s="35">
         <v>14.26</v>
       </c>
-      <c r="C30" s="34">
+      <c r="C30" s="35">
         <v>14.55</v>
       </c>
-      <c r="D30" s="34">
+      <c r="D30" s="35">
         <v>2.93</v>
       </c>
-      <c r="E30" s="35">
+      <c r="E30" s="36">
         <v>-8.53</v>
       </c>
-      <c r="F30" s="35">
+      <c r="F30" s="36">
         <v>-5.18</v>
       </c>
-      <c r="G30" s="34">
+      <c r="G30" s="35">
         <v>19.54</v>
       </c>
-      <c r="H30" s="34">
+      <c r="H30" s="35">
         <v>10.32</v>
       </c>
-      <c r="I30" s="34">
+      <c r="I30" s="35">
         <v>5.76</v>
       </c>
-      <c r="J30" s="35">
+      <c r="J30" s="36">
         <v>-1.75</v>
       </c>
-      <c r="K30" s="35">
+      <c r="K30" s="36">
         <v>-7.33</v>
       </c>
-      <c r="L30" s="34">
+      <c r="L30" s="35">
         <v>15.13</v>
       </c>
-      <c r="M30" s="34">
+      <c r="M30" s="35">
         <v>15.64</v>
       </c>
-      <c r="N30" s="35">
+      <c r="N30" s="36">
         <v>-19.73</v>
       </c>
-      <c r="O30" s="34">
+      <c r="O30" s="35">
         <v>7.59</v>
       </c>
-      <c r="P30" s="34">
+      <c r="P30" s="35">
         <v>4.41</v>
       </c>
-      <c r="Q30" s="35">
+      <c r="Q30" s="36">
         <v>-7.85</v>
       </c>
-      <c r="R30" s="34">
+      <c r="R30" s="35">
         <v>10.97</v>
       </c>
-      <c r="S30" s="34">
+      <c r="S30" s="35">
         <v>2.24</v>
       </c>
-      <c r="T30" s="34">
+      <c r="T30" s="35">
         <v>14.96</v>
       </c>
-      <c r="U30" s="35">
+      <c r="U30" s="36">
         <v>-12.59</v>
       </c>
-      <c r="V30" s="35">
+      <c r="V30" s="36">
         <v>-5.39</v>
       </c>
-      <c r="W30" s="35">
+      <c r="W30" s="36">
         <v>-3.15</v>
       </c>
-      <c r="X30" s="34">
+      <c r="X30" s="35">
         <v>32.22</v>
       </c>
-      <c r="Y30" s="34">
+      <c r="Y30" s="35">
         <v>17.04</v>
       </c>
-      <c r="Z30" s="34"/>
-      <c r="AA30" s="34">
+      <c r="Z30" s="35"/>
+      <c r="AA30" s="35">
         <v>3.16</v>
       </c>
-      <c r="AB30" s="34">
+      <c r="AB30" s="35">
         <v>3.11</v>
       </c>
-      <c r="AC30" s="34">
+      <c r="AC30" s="35">
         <v>0.18</v>
       </c>
-      <c r="AD30" s="35">
+      <c r="AD30" s="36">
         <v>-3.92</v>
       </c>
-      <c r="AE30" s="34">
+      <c r="AE30" s="35">
         <v>1.94</v>
       </c>
-      <c r="AF30" s="35">
+      <c r="AF30" s="36">
         <v>-1.41</v>
       </c>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="30" t="s">
+      <c r="A31" s="31" t="s">
         <v>380</v>
       </c>
-      <c r="B31" s="34">
+      <c r="B31" s="35">
         <v>7.33</v>
       </c>
-      <c r="C31" s="34">
+      <c r="C31" s="35">
         <v>6.3</v>
       </c>
-      <c r="D31" s="34">
+      <c r="D31" s="35">
         <v>4.37</v>
       </c>
-      <c r="E31" s="34">
+      <c r="E31" s="35">
         <v>5.05</v>
       </c>
-      <c r="F31" s="34">
+      <c r="F31" s="35">
         <v>6.13</v>
       </c>
-      <c r="G31" s="34">
+      <c r="G31" s="35">
         <v>6.9</v>
       </c>
-      <c r="H31" s="34">
+      <c r="H31" s="35">
         <v>5.46</v>
       </c>
-      <c r="I31" s="34">
+      <c r="I31" s="35">
         <v>5.36</v>
       </c>
-      <c r="J31" s="34">
+      <c r="J31" s="35">
         <v>2.92</v>
       </c>
-      <c r="K31" s="34">
+      <c r="K31" s="35">
         <v>4.68</v>
       </c>
-      <c r="L31" s="34">
+      <c r="L31" s="35">
         <v>8.71</v>
       </c>
-      <c r="M31" s="34">
+      <c r="M31" s="35">
         <v>1.12</v>
       </c>
-      <c r="N31" s="35">
+      <c r="N31" s="36">
         <v>-2.31</v>
       </c>
-      <c r="O31" s="34">
+      <c r="O31" s="35">
         <v>3.93</v>
       </c>
-      <c r="P31" s="34">
+      <c r="P31" s="35">
         <v>6.62</v>
       </c>
-      <c r="Q31" s="34">
+      <c r="Q31" s="35">
         <v>3.43</v>
       </c>
-      <c r="R31" s="34">
+      <c r="R31" s="35">
         <v>3.63</v>
       </c>
-      <c r="S31" s="34">
+      <c r="S31" s="35">
         <v>1.22</v>
       </c>
-      <c r="T31" s="34">
+      <c r="T31" s="35">
         <v>3.53</v>
       </c>
-      <c r="U31" s="35">
+      <c r="U31" s="36">
         <v>-0.31</v>
       </c>
-      <c r="V31" s="34"/>
-      <c r="W31" s="34"/>
-      <c r="X31" s="34"/>
-      <c r="Y31" s="34"/>
-      <c r="Z31" s="34"/>
-      <c r="AA31" s="34">
+      <c r="V31" s="35"/>
+      <c r="W31" s="35"/>
+      <c r="X31" s="35"/>
+      <c r="Y31" s="35"/>
+      <c r="Z31" s="35"/>
+      <c r="AA31" s="35">
         <v>0.65</v>
       </c>
-      <c r="AB31" s="35">
+      <c r="AB31" s="36">
         <v>-0.2</v>
       </c>
-      <c r="AC31" s="34"/>
-      <c r="AD31" s="34"/>
-      <c r="AE31" s="34"/>
-      <c r="AF31" s="34"/>
+      <c r="AC31" s="35"/>
+      <c r="AD31" s="35"/>
+      <c r="AE31" s="35"/>
+      <c r="AF31" s="35"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="28" t="s">
+      <c r="A32" s="29" t="s">
         <v>381</v>
       </c>
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="29"/>
-      <c r="K32" s="29"/>
-      <c r="L32" s="29"/>
-      <c r="M32" s="29"/>
-      <c r="N32" s="29"/>
-      <c r="O32" s="29"/>
-      <c r="P32" s="29"/>
-      <c r="Q32" s="29"/>
-      <c r="R32" s="29"/>
-      <c r="S32" s="29"/>
-      <c r="T32" s="29"/>
-      <c r="U32" s="29"/>
-      <c r="V32" s="29"/>
-      <c r="W32" s="29"/>
-      <c r="X32" s="29"/>
-      <c r="Y32" s="29"/>
-      <c r="Z32" s="29"/>
-      <c r="AA32" s="29"/>
-      <c r="AB32" s="29"/>
-      <c r="AC32" s="29"/>
-      <c r="AD32" s="29"/>
-      <c r="AE32" s="29"/>
-      <c r="AF32" s="29"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="30"/>
+      <c r="O32" s="30"/>
+      <c r="P32" s="30"/>
+      <c r="Q32" s="30"/>
+      <c r="R32" s="30"/>
+      <c r="S32" s="30"/>
+      <c r="T32" s="30"/>
+      <c r="U32" s="30"/>
+      <c r="V32" s="30"/>
+      <c r="W32" s="30"/>
+      <c r="X32" s="30"/>
+      <c r="Y32" s="30"/>
+      <c r="Z32" s="30"/>
+      <c r="AA32" s="30"/>
+      <c r="AB32" s="30"/>
+      <c r="AC32" s="30"/>
+      <c r="AD32" s="30"/>
+      <c r="AE32" s="30"/>
+      <c r="AF32" s="30"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="30" t="s">
+      <c r="A33" s="31" t="s">
         <v>382</v>
       </c>
-      <c r="B33" s="34">
+      <c r="B33" s="35">
         <v>1.6</v>
       </c>
-      <c r="C33" s="34">
+      <c r="C33" s="35">
         <v>2.48</v>
       </c>
-      <c r="D33" s="34">
+      <c r="D33" s="35">
         <v>2.47</v>
       </c>
-      <c r="E33" s="34">
+      <c r="E33" s="35">
         <v>4.29</v>
       </c>
-      <c r="F33" s="34">
+      <c r="F33" s="35">
         <v>2.48</v>
       </c>
-      <c r="G33" s="34">
+      <c r="G33" s="35">
         <v>2.06</v>
       </c>
-      <c r="H33" s="34">
+      <c r="H33" s="35">
         <v>2.25</v>
       </c>
-      <c r="I33" s="34">
+      <c r="I33" s="35">
         <v>1.65</v>
       </c>
-      <c r="J33" s="34">
+      <c r="J33" s="35">
         <v>2.16</v>
       </c>
-      <c r="K33" s="34">
+      <c r="K33" s="35">
         <v>1.89</v>
       </c>
-      <c r="L33" s="34">
+      <c r="L33" s="35">
         <v>0.65</v>
       </c>
-      <c r="M33" s="34">
+      <c r="M33" s="35">
         <v>1.03</v>
       </c>
-      <c r="N33" s="34">
+      <c r="N33" s="35">
         <v>1.47</v>
       </c>
-      <c r="O33" s="34">
+      <c r="O33" s="35">
         <v>1.21</v>
       </c>
-      <c r="P33" s="34">
+      <c r="P33" s="35">
         <v>0.92</v>
       </c>
-      <c r="Q33" s="34">
+      <c r="Q33" s="35">
         <v>0.84</v>
       </c>
-      <c r="R33" s="34">
+      <c r="R33" s="35">
         <v>0.6</v>
       </c>
-      <c r="S33" s="34">
+      <c r="S33" s="35">
         <v>0.7</v>
       </c>
-      <c r="T33" s="34">
+      <c r="T33" s="35">
         <v>0.45</v>
       </c>
-      <c r="U33" s="34">
+      <c r="U33" s="35">
         <v>0.34</v>
       </c>
-      <c r="V33" s="34">
+      <c r="V33" s="35">
         <v>0.37</v>
       </c>
-      <c r="W33" s="34">
+      <c r="W33" s="35">
         <v>0.67</v>
       </c>
-      <c r="X33" s="34">
+      <c r="X33" s="35">
         <v>0.97</v>
       </c>
-      <c r="Y33" s="34">
+      <c r="Y33" s="35">
         <v>0.86</v>
       </c>
-      <c r="Z33" s="34">
+      <c r="Z33" s="35">
         <v>1.03</v>
       </c>
-      <c r="AA33" s="34">
+      <c r="AA33" s="35">
         <v>0.55</v>
       </c>
-      <c r="AB33" s="34">
+      <c r="AB33" s="35">
         <v>0.62</v>
       </c>
-      <c r="AC33" s="34">
+      <c r="AC33" s="35">
         <v>0.56</v>
       </c>
-      <c r="AD33" s="34">
+      <c r="AD33" s="35">
         <v>0.36</v>
       </c>
-      <c r="AE33" s="34">
+      <c r="AE33" s="35">
         <v>0.37</v>
       </c>
-      <c r="AF33" s="34">
+      <c r="AF33" s="35">
         <v>0.44</v>
       </c>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="30" t="s">
+      <c r="A34" s="31" t="s">
         <v>383</v>
       </c>
-      <c r="B34" s="34">
+      <c r="B34" s="35">
         <v>2.33</v>
       </c>
-      <c r="C34" s="34">
+      <c r="C34" s="35">
         <v>2.63</v>
       </c>
-      <c r="D34" s="34">
+      <c r="D34" s="35">
         <v>2.61</v>
       </c>
-      <c r="E34" s="34">
+      <c r="E34" s="35">
         <v>2.45</v>
       </c>
-      <c r="F34" s="34">
+      <c r="F34" s="35">
         <v>2.12</v>
       </c>
-      <c r="G34" s="34">
+      <c r="G34" s="35">
         <v>2.0</v>
       </c>
-      <c r="H34" s="34">
+      <c r="H34" s="35">
         <v>1.69</v>
       </c>
-      <c r="I34" s="34">
+      <c r="I34" s="35">
         <v>1.48</v>
       </c>
-      <c r="J34" s="34">
+      <c r="J34" s="35">
         <v>1.42</v>
       </c>
-      <c r="K34" s="34">
+      <c r="K34" s="35">
         <v>1.18</v>
       </c>
-      <c r="L34" s="34">
+      <c r="L34" s="35">
         <v>0.92</v>
       </c>
-      <c r="M34" s="34">
+      <c r="M34" s="35">
         <v>1.12</v>
       </c>
-      <c r="N34" s="34">
+      <c r="N34" s="35">
         <v>1.03</v>
       </c>
-      <c r="O34" s="34">
+      <c r="O34" s="35">
         <v>0.82</v>
       </c>
-      <c r="P34" s="34">
+      <c r="P34" s="35">
         <v>0.66</v>
       </c>
-      <c r="Q34" s="34">
+      <c r="Q34" s="35">
         <v>0.56</v>
       </c>
-      <c r="R34" s="34">
+      <c r="R34" s="35">
         <v>0.49</v>
       </c>
-      <c r="S34" s="34">
+      <c r="S34" s="35">
         <v>0.48</v>
       </c>
-      <c r="T34" s="34">
+      <c r="T34" s="35">
         <v>0.48</v>
       </c>
-      <c r="U34" s="34">
+      <c r="U34" s="35">
         <v>0.54</v>
       </c>
-      <c r="V34" s="34">
+      <c r="V34" s="35">
         <v>0.68</v>
       </c>
-      <c r="W34" s="34">
+      <c r="W34" s="35">
         <v>0.77</v>
       </c>
-      <c r="X34" s="34">
+      <c r="X34" s="35">
         <v>0.76</v>
       </c>
-      <c r="Y34" s="34">
+      <c r="Y34" s="35">
         <v>0.68</v>
       </c>
-      <c r="Z34" s="34">
+      <c r="Z34" s="35">
         <v>0.57</v>
       </c>
-      <c r="AA34" s="34">
+      <c r="AA34" s="35">
         <v>0.47</v>
       </c>
-      <c r="AB34" s="34">
+      <c r="AB34" s="35">
         <v>0.45</v>
       </c>
-      <c r="AC34" s="34"/>
-      <c r="AD34" s="34"/>
-      <c r="AE34" s="34"/>
-      <c r="AF34" s="34"/>
+      <c r="AC34" s="35"/>
+      <c r="AD34" s="35"/>
+      <c r="AE34" s="35"/>
+      <c r="AF34" s="35"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="30" t="s">
+      <c r="A35" s="31" t="s">
         <v>384</v>
       </c>
-      <c r="B35" s="34">
+      <c r="B35" s="35">
         <v>1.6</v>
       </c>
-      <c r="C35" s="34">
+      <c r="C35" s="35">
         <v>2.48</v>
       </c>
-      <c r="D35" s="34">
+      <c r="D35" s="35">
         <v>2.47</v>
       </c>
-      <c r="E35" s="34">
+      <c r="E35" s="35">
         <v>4.29</v>
       </c>
-      <c r="F35" s="34">
+      <c r="F35" s="35">
         <v>2.48</v>
       </c>
-      <c r="G35" s="34">
+      <c r="G35" s="35">
         <v>2.06</v>
       </c>
-      <c r="H35" s="34">
+      <c r="H35" s="35">
         <v>2.25</v>
       </c>
-      <c r="I35" s="34">
+      <c r="I35" s="35">
         <v>1.65</v>
       </c>
-      <c r="J35" s="34">
+      <c r="J35" s="35">
         <v>2.16</v>
       </c>
-      <c r="K35" s="34">
+      <c r="K35" s="35">
         <v>1.89</v>
       </c>
-      <c r="L35" s="34">
+      <c r="L35" s="35">
         <v>0.65</v>
       </c>
-      <c r="M35" s="34">
+      <c r="M35" s="35">
         <v>1.03</v>
       </c>
-      <c r="N35" s="34">
+      <c r="N35" s="35">
         <v>1.47</v>
       </c>
-      <c r="O35" s="34">
+      <c r="O35" s="35">
         <v>1.21</v>
       </c>
-      <c r="P35" s="34">
+      <c r="P35" s="35">
         <v>1.28</v>
       </c>
-      <c r="Q35" s="34">
+      <c r="Q35" s="35">
         <v>1.16</v>
       </c>
-      <c r="R35" s="34">
+      <c r="R35" s="35">
         <v>0.83</v>
       </c>
-      <c r="S35" s="34">
+      <c r="S35" s="35">
         <v>0.97</v>
       </c>
-      <c r="T35" s="34">
+      <c r="T35" s="35">
         <v>0.62</v>
       </c>
-      <c r="U35" s="34">
+      <c r="U35" s="35">
         <v>0.48</v>
       </c>
-      <c r="V35" s="34">
+      <c r="V35" s="35">
         <v>0.52</v>
       </c>
-      <c r="W35" s="34">
+      <c r="W35" s="35">
         <v>0.93</v>
       </c>
-      <c r="X35" s="34">
+      <c r="X35" s="35">
         <v>1.35</v>
       </c>
-      <c r="Y35" s="34">
+      <c r="Y35" s="35">
         <v>1.2</v>
       </c>
-      <c r="Z35" s="34">
+      <c r="Z35" s="35">
         <v>1.43</v>
       </c>
-      <c r="AA35" s="34">
+      <c r="AA35" s="35">
         <v>0.74</v>
       </c>
-      <c r="AB35" s="34">
+      <c r="AB35" s="35">
         <v>0.83</v>
       </c>
-      <c r="AC35" s="34">
+      <c r="AC35" s="35">
         <v>0.74</v>
       </c>
-      <c r="AD35" s="34">
+      <c r="AD35" s="35">
         <v>0.48</v>
       </c>
-      <c r="AE35" s="34">
+      <c r="AE35" s="35">
         <v>0.5</v>
       </c>
-      <c r="AF35" s="34">
+      <c r="AF35" s="35">
         <v>0.62</v>
       </c>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="30" t="s">
+      <c r="A36" s="31" t="s">
         <v>385</v>
       </c>
-      <c r="B36" s="34">
+      <c r="B36" s="35">
         <v>2.33</v>
       </c>
-      <c r="C36" s="34">
+      <c r="C36" s="35">
         <v>2.63</v>
       </c>
-      <c r="D36" s="34">
+      <c r="D36" s="35">
         <v>2.61</v>
       </c>
-      <c r="E36" s="34">
+      <c r="E36" s="35">
         <v>2.45</v>
       </c>
-      <c r="F36" s="34">
+      <c r="F36" s="35">
         <v>2.12</v>
       </c>
-      <c r="G36" s="34">
+      <c r="G36" s="35">
         <v>2.0</v>
       </c>
-      <c r="H36" s="34">
+      <c r="H36" s="35">
         <v>1.69</v>
       </c>
-      <c r="I36" s="34">
+      <c r="I36" s="35">
         <v>1.48</v>
       </c>
-      <c r="J36" s="34">
+      <c r="J36" s="35">
         <v>1.42</v>
       </c>
-      <c r="K36" s="34">
+      <c r="K36" s="35">
         <v>1.18</v>
       </c>
-      <c r="L36" s="34">
+      <c r="L36" s="35">
         <v>0.95</v>
       </c>
-      <c r="M36" s="34">
+      <c r="M36" s="35">
         <v>1.21</v>
       </c>
-      <c r="N36" s="34">
+      <c r="N36" s="35">
         <v>1.19</v>
       </c>
-      <c r="O36" s="34">
+      <c r="O36" s="35">
         <v>1.06</v>
       </c>
-      <c r="P36" s="34">
+      <c r="P36" s="35">
         <v>0.91</v>
       </c>
-      <c r="Q36" s="34">
+      <c r="Q36" s="35">
         <v>0.78</v>
       </c>
-      <c r="R36" s="34">
+      <c r="R36" s="35">
         <v>0.68</v>
       </c>
-      <c r="S36" s="34">
+      <c r="S36" s="35">
         <v>0.67</v>
       </c>
-      <c r="T36" s="34">
+      <c r="T36" s="35">
         <v>0.66</v>
       </c>
-      <c r="U36" s="34">
+      <c r="U36" s="35">
         <v>0.75</v>
       </c>
-      <c r="V36" s="34">
+      <c r="V36" s="35">
         <v>0.95</v>
       </c>
-      <c r="W36" s="34">
+      <c r="W36" s="35">
         <v>1.06</v>
       </c>
-      <c r="X36" s="34">
+      <c r="X36" s="35">
         <v>1.03</v>
       </c>
-      <c r="Y36" s="34">
+      <c r="Y36" s="35">
         <v>0.93</v>
       </c>
-      <c r="Z36" s="34">
+      <c r="Z36" s="35">
         <v>0.76</v>
       </c>
-      <c r="AA36" s="34">
+      <c r="AA36" s="35">
         <v>0.63</v>
       </c>
-      <c r="AB36" s="34">
+      <c r="AB36" s="35">
         <v>0.61</v>
       </c>
-      <c r="AC36" s="34"/>
-      <c r="AD36" s="34"/>
-      <c r="AE36" s="34"/>
-      <c r="AF36" s="34"/>
+      <c r="AC36" s="35"/>
+      <c r="AD36" s="35"/>
+      <c r="AE36" s="35"/>
+      <c r="AF36" s="35"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="28" t="s">
+      <c r="A37" s="29" t="s">
         <v>386</v>
       </c>
-      <c r="B37" s="29"/>
-      <c r="C37" s="29"/>
-      <c r="D37" s="29"/>
-      <c r="E37" s="29"/>
-      <c r="F37" s="29"/>
-      <c r="G37" s="29"/>
-      <c r="H37" s="29"/>
-      <c r="I37" s="29"/>
-      <c r="J37" s="29"/>
-      <c r="K37" s="29"/>
-      <c r="L37" s="29"/>
-      <c r="M37" s="29"/>
-      <c r="N37" s="29"/>
-      <c r="O37" s="29"/>
-      <c r="P37" s="29"/>
-      <c r="Q37" s="29"/>
-      <c r="R37" s="29"/>
-      <c r="S37" s="29"/>
-      <c r="T37" s="29"/>
-      <c r="U37" s="29"/>
-      <c r="V37" s="29"/>
-      <c r="W37" s="29"/>
-      <c r="X37" s="29"/>
-      <c r="Y37" s="29"/>
-      <c r="Z37" s="29"/>
-      <c r="AA37" s="29"/>
-      <c r="AB37" s="29"/>
-      <c r="AC37" s="29"/>
-      <c r="AD37" s="29"/>
-      <c r="AE37" s="29"/>
-      <c r="AF37" s="29"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="30"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="30"/>
+      <c r="K37" s="30"/>
+      <c r="L37" s="30"/>
+      <c r="M37" s="30"/>
+      <c r="N37" s="30"/>
+      <c r="O37" s="30"/>
+      <c r="P37" s="30"/>
+      <c r="Q37" s="30"/>
+      <c r="R37" s="30"/>
+      <c r="S37" s="30"/>
+      <c r="T37" s="30"/>
+      <c r="U37" s="30"/>
+      <c r="V37" s="30"/>
+      <c r="W37" s="30"/>
+      <c r="X37" s="30"/>
+      <c r="Y37" s="30"/>
+      <c r="Z37" s="30"/>
+      <c r="AA37" s="30"/>
+      <c r="AB37" s="30"/>
+      <c r="AC37" s="30"/>
+      <c r="AD37" s="30"/>
+      <c r="AE37" s="30"/>
+      <c r="AF37" s="30"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="30" t="s">
+      <c r="A38" s="31" t="s">
         <v>387</v>
       </c>
-      <c r="B38" s="33">
+      <c r="B38" s="34">
         <v>2.34</v>
       </c>
-      <c r="C38" s="33">
+      <c r="C38" s="34">
         <v>1.55</v>
       </c>
-      <c r="D38" s="33">
+      <c r="D38" s="34">
         <v>1.41</v>
       </c>
-      <c r="E38" s="33">
+      <c r="E38" s="34">
         <v>0.95</v>
       </c>
-      <c r="F38" s="33">
+      <c r="F38" s="34">
         <v>1.43</v>
       </c>
-      <c r="G38" s="33">
+      <c r="G38" s="34">
         <v>1.62</v>
       </c>
-      <c r="H38" s="33">
+      <c r="H38" s="34">
         <v>1.44</v>
       </c>
-      <c r="I38" s="33">
+      <c r="I38" s="34">
         <v>1.7</v>
       </c>
-      <c r="J38" s="33">
+      <c r="J38" s="34">
         <v>1.4</v>
       </c>
-      <c r="K38" s="33">
+      <c r="K38" s="34">
         <v>1.3</v>
       </c>
-      <c r="L38" s="33">
+      <c r="L38" s="34">
         <v>2.07</v>
       </c>
-      <c r="M38" s="33">
+      <c r="M38" s="34">
         <v>1.02</v>
       </c>
-      <c r="N38" s="33">
+      <c r="N38" s="34">
         <v>0.81</v>
       </c>
-      <c r="O38" s="33">
+      <c r="O38" s="34">
         <v>0.51</v>
       </c>
-      <c r="P38" s="33">
+      <c r="P38" s="34">
         <v>0.52</v>
       </c>
-      <c r="Q38" s="33">
+      <c r="Q38" s="34">
         <v>0.6</v>
       </c>
-      <c r="R38" s="33">
+      <c r="R38" s="34">
         <v>0.89</v>
       </c>
-      <c r="S38" s="33">
+      <c r="S38" s="34">
         <v>0.82</v>
       </c>
-      <c r="T38" s="33">
+      <c r="T38" s="34">
         <v>1.53</v>
       </c>
-      <c r="U38" s="33">
+      <c r="U38" s="34">
         <v>1.14</v>
       </c>
-      <c r="V38" s="33">
+      <c r="V38" s="34">
         <v>1.16</v>
       </c>
-      <c r="W38" s="33">
+      <c r="W38" s="34">
         <v>0.64</v>
       </c>
-      <c r="X38" s="33">
+      <c r="X38" s="34">
         <v>0.46</v>
       </c>
-      <c r="Y38" s="33">
+      <c r="Y38" s="34">
         <v>0.52</v>
       </c>
-      <c r="Z38" s="33">
+      <c r="Z38" s="34">
         <v>0.46</v>
       </c>
-      <c r="AA38" s="33">
+      <c r="AA38" s="34">
         <v>0.92</v>
       </c>
-      <c r="AB38" s="33">
+      <c r="AB38" s="34">
         <v>0.9</v>
       </c>
-      <c r="AC38" s="33">
+      <c r="AC38" s="34">
         <v>0.97</v>
       </c>
-      <c r="AD38" s="33">
+      <c r="AD38" s="34">
         <v>1.68</v>
       </c>
-      <c r="AE38" s="33">
+      <c r="AE38" s="34">
         <v>1.83</v>
       </c>
-      <c r="AF38" s="33">
+      <c r="AF38" s="34">
         <v>1.59</v>
       </c>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="30" t="s">
+      <c r="A39" s="31" t="s">
         <v>388</v>
       </c>
-      <c r="B39" s="33">
+      <c r="B39" s="34">
         <v>1.6</v>
       </c>
-      <c r="C39" s="33">
+      <c r="C39" s="34">
         <v>1.4</v>
       </c>
-      <c r="D39" s="33">
+      <c r="D39" s="34">
         <v>1.36</v>
       </c>
-      <c r="E39" s="33">
+      <c r="E39" s="34">
         <v>1.4</v>
       </c>
-      <c r="F39" s="33">
+      <c r="F39" s="34">
         <v>1.52</v>
       </c>
-      <c r="G39" s="33">
+      <c r="G39" s="34">
         <v>1.5</v>
       </c>
-      <c r="H39" s="33">
+      <c r="H39" s="34">
         <v>1.57</v>
       </c>
-      <c r="I39" s="33">
+      <c r="I39" s="34">
         <v>1.51</v>
       </c>
-      <c r="J39" s="33">
+      <c r="J39" s="34">
         <v>1.36</v>
       </c>
-      <c r="K39" s="33">
+      <c r="K39" s="34">
         <v>1.21</v>
       </c>
-      <c r="L39" s="33">
+      <c r="L39" s="34">
         <v>1.07</v>
       </c>
-      <c r="M39" s="33">
+      <c r="M39" s="34">
         <v>0.71</v>
       </c>
-      <c r="N39" s="33">
+      <c r="N39" s="34">
         <v>0.66</v>
       </c>
-      <c r="O39" s="33">
+      <c r="O39" s="34">
         <v>0.66</v>
       </c>
-      <c r="P39" s="33">
+      <c r="P39" s="34">
         <v>0.83</v>
       </c>
-      <c r="Q39" s="33">
+      <c r="Q39" s="34">
         <v>0.96</v>
       </c>
-      <c r="R39" s="33">
+      <c r="R39" s="34">
         <v>1.08</v>
       </c>
-      <c r="S39" s="33">
+      <c r="S39" s="34">
         <v>1.06</v>
       </c>
-      <c r="T39" s="33">
+      <c r="T39" s="34">
         <v>1.02</v>
       </c>
-      <c r="U39" s="33">
+      <c r="U39" s="34">
         <v>0.79</v>
       </c>
-      <c r="V39" s="33">
+      <c r="V39" s="34">
         <v>0.65</v>
       </c>
-      <c r="W39" s="33">
+      <c r="W39" s="34">
         <v>0.59</v>
       </c>
-      <c r="X39" s="33">
+      <c r="X39" s="34">
         <v>0.64</v>
       </c>
-      <c r="Y39" s="33">
+      <c r="Y39" s="34">
         <v>0.73</v>
       </c>
-      <c r="Z39" s="33">
+      <c r="Z39" s="34">
         <v>0.94</v>
       </c>
-      <c r="AA39" s="33">
+      <c r="AA39" s="34">
         <v>1.2</v>
       </c>
-      <c r="AB39" s="33">
+      <c r="AB39" s="34">
         <v>1.34</v>
       </c>
-      <c r="AC39" s="31"/>
-      <c r="AD39" s="31"/>
-      <c r="AE39" s="31"/>
-      <c r="AF39" s="31"/>
+      <c r="AC39" s="32"/>
+      <c r="AD39" s="32"/>
+      <c r="AE39" s="32"/>
+      <c r="AF39" s="32"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="28" t="s">
+      <c r="A40" s="29" t="s">
         <v>389</v>
       </c>
-      <c r="B40" s="29"/>
-      <c r="C40" s="29"/>
-      <c r="D40" s="29"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="29"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="29"/>
-      <c r="I40" s="29"/>
-      <c r="J40" s="29"/>
-      <c r="K40" s="29"/>
-      <c r="L40" s="29"/>
-      <c r="M40" s="29"/>
-      <c r="N40" s="29"/>
-      <c r="O40" s="29"/>
-      <c r="P40" s="29"/>
-      <c r="Q40" s="29"/>
-      <c r="R40" s="29"/>
-      <c r="S40" s="29"/>
-      <c r="T40" s="29"/>
-      <c r="U40" s="29"/>
-      <c r="V40" s="29"/>
-      <c r="W40" s="29"/>
-      <c r="X40" s="29"/>
-      <c r="Y40" s="29"/>
-      <c r="Z40" s="29"/>
-      <c r="AA40" s="29"/>
-      <c r="AB40" s="29"/>
-      <c r="AC40" s="29"/>
-      <c r="AD40" s="29"/>
-      <c r="AE40" s="29"/>
-      <c r="AF40" s="29"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="30"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="30"/>
+      <c r="K40" s="30"/>
+      <c r="L40" s="30"/>
+      <c r="M40" s="30"/>
+      <c r="N40" s="30"/>
+      <c r="O40" s="30"/>
+      <c r="P40" s="30"/>
+      <c r="Q40" s="30"/>
+      <c r="R40" s="30"/>
+      <c r="S40" s="30"/>
+      <c r="T40" s="30"/>
+      <c r="U40" s="30"/>
+      <c r="V40" s="30"/>
+      <c r="W40" s="30"/>
+      <c r="X40" s="30"/>
+      <c r="Y40" s="30"/>
+      <c r="Z40" s="30"/>
+      <c r="AA40" s="30"/>
+      <c r="AB40" s="30"/>
+      <c r="AC40" s="30"/>
+      <c r="AD40" s="30"/>
+      <c r="AE40" s="30"/>
+      <c r="AF40" s="30"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="30" t="s">
+      <c r="A41" s="31" t="s">
         <v>390</v>
       </c>
-      <c r="B41" s="33">
+      <c r="B41" s="34">
         <v>2.73</v>
       </c>
-      <c r="C41" s="33">
+      <c r="C41" s="34">
         <v>1.8</v>
       </c>
-      <c r="D41" s="33">
+      <c r="D41" s="34">
         <v>1.67</v>
       </c>
-      <c r="E41" s="33">
+      <c r="E41" s="34">
         <v>1.16</v>
       </c>
-      <c r="F41" s="33">
+      <c r="F41" s="34">
         <v>1.58</v>
       </c>
-      <c r="G41" s="33">
+      <c r="G41" s="34">
         <v>1.78</v>
       </c>
-      <c r="H41" s="33">
+      <c r="H41" s="34">
         <v>1.63</v>
       </c>
-      <c r="I41" s="33">
+      <c r="I41" s="34">
         <v>1.96</v>
       </c>
-      <c r="J41" s="33">
+      <c r="J41" s="34">
         <v>1.64</v>
       </c>
-      <c r="K41" s="33">
+      <c r="K41" s="34">
         <v>1.49</v>
       </c>
-      <c r="L41" s="33">
+      <c r="L41" s="34">
         <v>2.24</v>
       </c>
-      <c r="M41" s="33">
+      <c r="M41" s="34">
         <v>1.11</v>
       </c>
-      <c r="N41" s="33">
+      <c r="N41" s="34">
         <v>0.9</v>
       </c>
-      <c r="O41" s="33">
+      <c r="O41" s="34">
         <v>0.55</v>
       </c>
-      <c r="P41" s="33">
+      <c r="P41" s="34">
         <v>0.52</v>
       </c>
-      <c r="Q41" s="33">
+      <c r="Q41" s="34">
         <v>0.61</v>
       </c>
-      <c r="R41" s="33">
+      <c r="R41" s="34">
         <v>0.92</v>
       </c>
-      <c r="S41" s="33">
+      <c r="S41" s="34">
         <v>0.86</v>
       </c>
-      <c r="T41" s="33">
+      <c r="T41" s="34">
         <v>1.61</v>
       </c>
-      <c r="U41" s="33">
+      <c r="U41" s="34">
         <v>1.25</v>
       </c>
-      <c r="V41" s="33">
+      <c r="V41" s="34">
         <v>1.24</v>
       </c>
-      <c r="W41" s="33">
+      <c r="W41" s="34">
         <v>0.65</v>
       </c>
-      <c r="X41" s="33">
+      <c r="X41" s="34">
         <v>0.47</v>
       </c>
-      <c r="Y41" s="33">
+      <c r="Y41" s="34">
         <v>0.54</v>
       </c>
-      <c r="Z41" s="33">
+      <c r="Z41" s="34">
         <v>0.48</v>
       </c>
-      <c r="AA41" s="33">
+      <c r="AA41" s="34">
         <v>0.98</v>
       </c>
-      <c r="AB41" s="33">
+      <c r="AB41" s="34">
         <v>0.94</v>
       </c>
-      <c r="AC41" s="33">
+      <c r="AC41" s="34">
         <v>1.03</v>
       </c>
-      <c r="AD41" s="33">
+      <c r="AD41" s="34">
         <v>1.8</v>
       </c>
-      <c r="AE41" s="33">
+      <c r="AE41" s="34">
         <v>1.83</v>
       </c>
-      <c r="AF41" s="33">
+      <c r="AF41" s="34">
         <v>1.59</v>
       </c>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="30" t="s">
+      <c r="A42" s="31" t="s">
         <v>391</v>
       </c>
-      <c r="B42" s="33">
+      <c r="B42" s="34">
         <v>1.87</v>
       </c>
-      <c r="C42" s="33">
+      <c r="C42" s="34">
         <v>1.61</v>
       </c>
-      <c r="D42" s="33">
+      <c r="D42" s="34">
         <v>1.56</v>
       </c>
-      <c r="E42" s="33">
+      <c r="E42" s="34">
         <v>1.6</v>
       </c>
-      <c r="F42" s="33">
+      <c r="F42" s="34">
         <v>1.71</v>
       </c>
-      <c r="G42" s="33">
+      <c r="G42" s="34">
         <v>1.71</v>
       </c>
-      <c r="H42" s="33">
+      <c r="H42" s="34">
         <v>1.78</v>
       </c>
-      <c r="I42" s="33">
+      <c r="I42" s="34">
         <v>1.71</v>
       </c>
-      <c r="J42" s="33">
+      <c r="J42" s="34">
         <v>1.52</v>
       </c>
-      <c r="K42" s="33">
+      <c r="K42" s="34">
         <v>1.33</v>
       </c>
-      <c r="L42" s="33">
+      <c r="L42" s="34">
         <v>1.15</v>
       </c>
-      <c r="M42" s="33">
+      <c r="M42" s="34">
         <v>0.76</v>
       </c>
-      <c r="N42" s="33">
+      <c r="N42" s="34">
         <v>0.7</v>
       </c>
-      <c r="O42" s="33">
+      <c r="O42" s="34">
         <v>0.68</v>
       </c>
-      <c r="P42" s="33">
+      <c r="P42" s="34">
         <v>0.86</v>
       </c>
-      <c r="Q42" s="33">
+      <c r="Q42" s="34">
         <v>1.0</v>
       </c>
-      <c r="R42" s="33">
+      <c r="R42" s="34">
         <v>1.14</v>
       </c>
-      <c r="S42" s="33">
+      <c r="S42" s="34">
         <v>1.12</v>
       </c>
-      <c r="T42" s="33">
+      <c r="T42" s="34">
         <v>1.07</v>
       </c>
-      <c r="U42" s="33">
+      <c r="U42" s="34">
         <v>0.84</v>
       </c>
-      <c r="V42" s="33">
+      <c r="V42" s="34">
         <v>0.68</v>
       </c>
-      <c r="W42" s="33">
+      <c r="W42" s="34">
         <v>0.62</v>
       </c>
-      <c r="X42" s="33">
+      <c r="X42" s="34">
         <v>0.67</v>
       </c>
-      <c r="Y42" s="33">
+      <c r="Y42" s="34">
         <v>0.77</v>
       </c>
-      <c r="Z42" s="33">
+      <c r="Z42" s="34">
         <v>0.99</v>
       </c>
-      <c r="AA42" s="33">
+      <c r="AA42" s="34">
         <v>1.26</v>
       </c>
-      <c r="AB42" s="33">
+      <c r="AB42" s="34">
         <v>1.39</v>
       </c>
-      <c r="AC42" s="31"/>
-      <c r="AD42" s="31"/>
-      <c r="AE42" s="31"/>
-      <c r="AF42" s="31"/>
+      <c r="AC42" s="32"/>
+      <c r="AD42" s="32"/>
+      <c r="AE42" s="32"/>
+      <c r="AF42" s="32"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="28" t="s">
+      <c r="A43" s="29" t="s">
         <v>392</v>
       </c>
-      <c r="B43" s="29"/>
-      <c r="C43" s="29"/>
-      <c r="D43" s="29"/>
-      <c r="E43" s="29"/>
-      <c r="F43" s="29"/>
-      <c r="G43" s="29"/>
-      <c r="H43" s="29"/>
-      <c r="I43" s="29"/>
-      <c r="J43" s="29"/>
-      <c r="K43" s="29"/>
-      <c r="L43" s="29"/>
-      <c r="M43" s="29"/>
-      <c r="N43" s="29"/>
-      <c r="O43" s="29"/>
-      <c r="P43" s="29"/>
-      <c r="Q43" s="29"/>
-      <c r="R43" s="29"/>
-      <c r="S43" s="29"/>
-      <c r="T43" s="29"/>
-      <c r="U43" s="29"/>
-      <c r="V43" s="29"/>
-      <c r="W43" s="29"/>
-      <c r="X43" s="29"/>
-      <c r="Y43" s="29"/>
-      <c r="Z43" s="29"/>
-      <c r="AA43" s="29"/>
-      <c r="AB43" s="29"/>
-      <c r="AC43" s="29"/>
-      <c r="AD43" s="29"/>
-      <c r="AE43" s="29"/>
-      <c r="AF43" s="29"/>
+      <c r="B43" s="30"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="30"/>
+      <c r="I43" s="30"/>
+      <c r="J43" s="30"/>
+      <c r="K43" s="30"/>
+      <c r="L43" s="30"/>
+      <c r="M43" s="30"/>
+      <c r="N43" s="30"/>
+      <c r="O43" s="30"/>
+      <c r="P43" s="30"/>
+      <c r="Q43" s="30"/>
+      <c r="R43" s="30"/>
+      <c r="S43" s="30"/>
+      <c r="T43" s="30"/>
+      <c r="U43" s="30"/>
+      <c r="V43" s="30"/>
+      <c r="W43" s="30"/>
+      <c r="X43" s="30"/>
+      <c r="Y43" s="30"/>
+      <c r="Z43" s="30"/>
+      <c r="AA43" s="30"/>
+      <c r="AB43" s="30"/>
+      <c r="AC43" s="30"/>
+      <c r="AD43" s="30"/>
+      <c r="AE43" s="30"/>
+      <c r="AF43" s="30"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="30" t="s">
+      <c r="A44" s="31" t="s">
         <v>393</v>
       </c>
-      <c r="B44" s="33">
+      <c r="B44" s="34">
         <v>0.59</v>
       </c>
-      <c r="C44" s="33">
+      <c r="C44" s="34">
         <v>0.36</v>
       </c>
-      <c r="D44" s="33">
+      <c r="D44" s="34">
         <v>0.31</v>
       </c>
-      <c r="E44" s="33">
+      <c r="E44" s="34">
         <v>0.2</v>
       </c>
-      <c r="F44" s="33">
+      <c r="F44" s="34">
         <v>0.36</v>
       </c>
-      <c r="G44" s="33">
+      <c r="G44" s="34">
         <v>0.41</v>
       </c>
-      <c r="H44" s="33">
+      <c r="H44" s="34">
         <v>0.34</v>
       </c>
-      <c r="I44" s="33">
+      <c r="I44" s="34">
         <v>0.41</v>
       </c>
-      <c r="J44" s="33">
+      <c r="J44" s="34">
         <v>0.34</v>
       </c>
-      <c r="K44" s="33">
+      <c r="K44" s="34">
         <v>0.31</v>
       </c>
-      <c r="L44" s="33">
+      <c r="L44" s="34">
         <v>0.46</v>
       </c>
-      <c r="M44" s="33">
+      <c r="M44" s="34">
         <v>0.23</v>
       </c>
-      <c r="N44" s="33">
+      <c r="N44" s="34">
         <v>0.19</v>
       </c>
-      <c r="O44" s="33">
+      <c r="O44" s="34">
         <v>0.12</v>
       </c>
-      <c r="P44" s="33">
+      <c r="P44" s="34">
         <v>0.12</v>
       </c>
-      <c r="Q44" s="33">
+      <c r="Q44" s="34">
         <v>0.2</v>
       </c>
-      <c r="R44" s="33">
+      <c r="R44" s="34">
         <v>0.25</v>
       </c>
-      <c r="S44" s="33">
+      <c r="S44" s="34">
         <v>0.19</v>
       </c>
-      <c r="T44" s="33">
+      <c r="T44" s="34">
         <v>0.37</v>
       </c>
-      <c r="U44" s="33">
+      <c r="U44" s="34">
         <v>0.28</v>
       </c>
-      <c r="V44" s="33">
+      <c r="V44" s="34">
         <v>0.28</v>
       </c>
-      <c r="W44" s="33">
+      <c r="W44" s="34">
         <v>0.17</v>
       </c>
-      <c r="X44" s="33">
+      <c r="X44" s="34">
         <v>0.11</v>
       </c>
-      <c r="Y44" s="33">
+      <c r="Y44" s="34">
         <v>0.13</v>
       </c>
-      <c r="Z44" s="33">
+      <c r="Z44" s="34">
         <v>0.13</v>
       </c>
-      <c r="AA44" s="33">
+      <c r="AA44" s="34">
         <v>0.25</v>
       </c>
-      <c r="AB44" s="33">
+      <c r="AB44" s="34">
         <v>0.22</v>
       </c>
-      <c r="AC44" s="33">
+      <c r="AC44" s="34">
         <v>0.26</v>
       </c>
-      <c r="AD44" s="33">
+      <c r="AD44" s="34">
         <v>0.44</v>
       </c>
-      <c r="AE44" s="33">
+      <c r="AE44" s="34">
         <v>0.48</v>
       </c>
-      <c r="AF44" s="33">
+      <c r="AF44" s="34">
         <v>0.46</v>
       </c>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="30" t="s">
+      <c r="A45" s="31" t="s">
         <v>394</v>
       </c>
-      <c r="B45" s="33">
+      <c r="B45" s="34">
         <v>0.37</v>
       </c>
-      <c r="C45" s="33">
+      <c r="C45" s="34">
         <v>0.32</v>
       </c>
-      <c r="D45" s="33">
+      <c r="D45" s="34">
         <v>0.32</v>
       </c>
-      <c r="E45" s="33">
+      <c r="E45" s="34">
         <v>0.33</v>
       </c>
-      <c r="F45" s="33">
+      <c r="F45" s="34">
         <v>0.37</v>
       </c>
-      <c r="G45" s="33">
+      <c r="G45" s="34">
         <v>0.36</v>
       </c>
-      <c r="H45" s="33">
+      <c r="H45" s="34">
         <v>0.37</v>
       </c>
-      <c r="I45" s="33">
+      <c r="I45" s="34">
         <v>0.36</v>
       </c>
-      <c r="J45" s="33">
+      <c r="J45" s="34">
         <v>0.32</v>
       </c>
-      <c r="K45" s="33">
+      <c r="K45" s="34">
         <v>0.28</v>
       </c>
-      <c r="L45" s="33">
+      <c r="L45" s="34">
         <v>0.25</v>
       </c>
-      <c r="M45" s="33">
+      <c r="M45" s="34">
         <v>0.18</v>
       </c>
-      <c r="N45" s="33">
+      <c r="N45" s="34">
         <v>0.17</v>
       </c>
-      <c r="O45" s="33">
+      <c r="O45" s="34">
         <v>0.17</v>
       </c>
-      <c r="P45" s="33">
+      <c r="P45" s="34">
         <v>0.22</v>
       </c>
-      <c r="Q45" s="33">
+      <c r="Q45" s="34">
         <v>0.25</v>
       </c>
-      <c r="R45" s="33">
+      <c r="R45" s="34">
         <v>0.27</v>
       </c>
-      <c r="S45" s="33">
+      <c r="S45" s="34">
         <v>0.26</v>
       </c>
-      <c r="T45" s="33">
+      <c r="T45" s="34">
         <v>0.25</v>
       </c>
-      <c r="U45" s="33">
+      <c r="U45" s="34">
         <v>0.19</v>
       </c>
-      <c r="V45" s="33">
+      <c r="V45" s="34">
         <v>0.16</v>
       </c>
-      <c r="W45" s="33">
+      <c r="W45" s="34">
         <v>0.15</v>
       </c>
-      <c r="X45" s="33">
+      <c r="X45" s="34">
         <v>0.16</v>
       </c>
-      <c r="Y45" s="33">
+      <c r="Y45" s="34">
         <v>0.19</v>
       </c>
-      <c r="Z45" s="33">
+      <c r="Z45" s="34">
         <v>0.25</v>
       </c>
-      <c r="AA45" s="33">
+      <c r="AA45" s="34">
         <v>0.31</v>
       </c>
-      <c r="AB45" s="33">
+      <c r="AB45" s="34">
         <v>0.35</v>
       </c>
-      <c r="AC45" s="31"/>
-      <c r="AD45" s="31"/>
-      <c r="AE45" s="31"/>
-      <c r="AF45" s="31"/>
+      <c r="AC45" s="32"/>
+      <c r="AD45" s="32"/>
+      <c r="AE45" s="32"/>
+      <c r="AF45" s="32"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="28" t="s">
+      <c r="A46" s="29" t="s">
         <v>395</v>
       </c>
-      <c r="B46" s="29"/>
-      <c r="C46" s="29"/>
-      <c r="D46" s="29"/>
-      <c r="E46" s="29"/>
-      <c r="F46" s="29"/>
-      <c r="G46" s="29"/>
-      <c r="H46" s="29"/>
-      <c r="I46" s="29"/>
-      <c r="J46" s="29"/>
-      <c r="K46" s="29"/>
-      <c r="L46" s="29"/>
-      <c r="M46" s="29"/>
-      <c r="N46" s="29"/>
-      <c r="O46" s="29"/>
-      <c r="P46" s="29"/>
-      <c r="Q46" s="29"/>
-      <c r="R46" s="29"/>
-      <c r="S46" s="29"/>
-      <c r="T46" s="29"/>
-      <c r="U46" s="29"/>
-      <c r="V46" s="29"/>
-      <c r="W46" s="29"/>
-      <c r="X46" s="29"/>
-      <c r="Y46" s="29"/>
-      <c r="Z46" s="29"/>
-      <c r="AA46" s="29"/>
-      <c r="AB46" s="29"/>
-      <c r="AC46" s="29"/>
-      <c r="AD46" s="29"/>
-      <c r="AE46" s="29"/>
-      <c r="AF46" s="29"/>
+      <c r="B46" s="30"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="30"/>
+      <c r="I46" s="30"/>
+      <c r="J46" s="30"/>
+      <c r="K46" s="30"/>
+      <c r="L46" s="30"/>
+      <c r="M46" s="30"/>
+      <c r="N46" s="30"/>
+      <c r="O46" s="30"/>
+      <c r="P46" s="30"/>
+      <c r="Q46" s="30"/>
+      <c r="R46" s="30"/>
+      <c r="S46" s="30"/>
+      <c r="T46" s="30"/>
+      <c r="U46" s="30"/>
+      <c r="V46" s="30"/>
+      <c r="W46" s="30"/>
+      <c r="X46" s="30"/>
+      <c r="Y46" s="30"/>
+      <c r="Z46" s="30"/>
+      <c r="AA46" s="30"/>
+      <c r="AB46" s="30"/>
+      <c r="AC46" s="30"/>
+      <c r="AD46" s="30"/>
+      <c r="AE46" s="30"/>
+      <c r="AF46" s="30"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="30" t="s">
+      <c r="A47" s="31" t="s">
         <v>396</v>
       </c>
-      <c r="B47" s="33">
+      <c r="B47" s="34">
         <v>7.01</v>
       </c>
-      <c r="C47" s="33">
+      <c r="C47" s="34">
         <v>6.87</v>
       </c>
-      <c r="D47" s="33">
+      <c r="D47" s="34">
         <v>34.07</v>
       </c>
-      <c r="E47" s="31"/>
-      <c r="F47" s="31"/>
-      <c r="G47" s="33">
+      <c r="E47" s="32"/>
+      <c r="F47" s="32"/>
+      <c r="G47" s="34">
         <v>5.12</v>
       </c>
-      <c r="H47" s="33">
+      <c r="H47" s="34">
         <v>9.69</v>
       </c>
-      <c r="I47" s="33">
+      <c r="I47" s="34">
         <v>17.36</v>
       </c>
-      <c r="J47" s="31"/>
-      <c r="K47" s="31"/>
-      <c r="L47" s="33">
+      <c r="J47" s="32"/>
+      <c r="K47" s="32"/>
+      <c r="L47" s="34">
         <v>6.61</v>
       </c>
-      <c r="M47" s="33">
+      <c r="M47" s="34">
         <v>6.4</v>
       </c>
-      <c r="N47" s="31"/>
-      <c r="O47" s="33">
+      <c r="N47" s="32"/>
+      <c r="O47" s="34">
         <v>13.17</v>
       </c>
-      <c r="P47" s="33">
+      <c r="P47" s="34">
         <v>22.7</v>
       </c>
-      <c r="Q47" s="31"/>
-      <c r="R47" s="33">
+      <c r="Q47" s="32"/>
+      <c r="R47" s="34">
         <v>9.12</v>
       </c>
-      <c r="S47" s="33">
+      <c r="S47" s="34">
         <v>44.71</v>
       </c>
-      <c r="T47" s="33">
+      <c r="T47" s="34">
         <v>6.69</v>
       </c>
-      <c r="U47" s="31"/>
-      <c r="V47" s="31"/>
-      <c r="W47" s="31"/>
-      <c r="X47" s="33">
+      <c r="U47" s="32"/>
+      <c r="V47" s="32"/>
+      <c r="W47" s="32"/>
+      <c r="X47" s="34">
         <v>3.1</v>
       </c>
-      <c r="Y47" s="33">
+      <c r="Y47" s="34">
         <v>5.87</v>
       </c>
-      <c r="Z47" s="31"/>
-      <c r="AA47" s="33">
+      <c r="Z47" s="32"/>
+      <c r="AA47" s="34">
         <v>31.61</v>
       </c>
-      <c r="AB47" s="33">
+      <c r="AB47" s="34">
         <v>32.15</v>
       </c>
-      <c r="AC47" s="32">
+      <c r="AC47" s="33">
         <v>545.64</v>
       </c>
-      <c r="AD47" s="31"/>
-      <c r="AE47" s="33">
+      <c r="AD47" s="32"/>
+      <c r="AE47" s="34">
         <v>51.44</v>
       </c>
-      <c r="AF47" s="31"/>
+      <c r="AF47" s="32"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="30" t="s">
+      <c r="A48" s="31" t="s">
         <v>397</v>
       </c>
-      <c r="B48" s="33">
+      <c r="B48" s="34">
         <v>13.64</v>
       </c>
-      <c r="C48" s="33">
+      <c r="C48" s="34">
         <v>15.87</v>
       </c>
-      <c r="D48" s="33">
+      <c r="D48" s="34">
         <v>22.89</v>
       </c>
-      <c r="E48" s="33">
+      <c r="E48" s="34">
         <v>19.81</v>
       </c>
-      <c r="F48" s="33">
+      <c r="F48" s="34">
         <v>16.31</v>
       </c>
-      <c r="G48" s="33">
+      <c r="G48" s="34">
         <v>14.49</v>
       </c>
-      <c r="H48" s="33">
+      <c r="H48" s="34">
         <v>18.31</v>
       </c>
-      <c r="I48" s="33">
+      <c r="I48" s="34">
         <v>18.65</v>
       </c>
-      <c r="J48" s="33">
+      <c r="J48" s="34">
         <v>34.29</v>
       </c>
-      <c r="K48" s="33">
+      <c r="K48" s="34">
         <v>21.35</v>
       </c>
-      <c r="L48" s="33">
+      <c r="L48" s="34">
         <v>11.48</v>
       </c>
-      <c r="M48" s="33">
+      <c r="M48" s="34">
         <v>88.98</v>
       </c>
-      <c r="N48" s="31"/>
-      <c r="O48" s="33">
+      <c r="N48" s="32"/>
+      <c r="O48" s="34">
         <v>25.43</v>
       </c>
-      <c r="P48" s="33">
+      <c r="P48" s="34">
         <v>15.1</v>
       </c>
-      <c r="Q48" s="33">
+      <c r="Q48" s="34">
         <v>29.18</v>
       </c>
-      <c r="R48" s="33">
+      <c r="R48" s="34">
         <v>27.54</v>
       </c>
-      <c r="S48" s="33">
+      <c r="S48" s="34">
         <v>81.73</v>
       </c>
-      <c r="T48" s="33">
+      <c r="T48" s="34">
         <v>28.36</v>
       </c>
-      <c r="U48" s="31"/>
-      <c r="V48" s="31"/>
-      <c r="W48" s="31"/>
-      <c r="X48" s="31"/>
-      <c r="Y48" s="31"/>
-      <c r="Z48" s="31"/>
-      <c r="AA48" s="32">
+      <c r="U48" s="32"/>
+      <c r="V48" s="32"/>
+      <c r="W48" s="32"/>
+      <c r="X48" s="32"/>
+      <c r="Y48" s="32"/>
+      <c r="Z48" s="32"/>
+      <c r="AA48" s="33">
         <v>152.87</v>
       </c>
-      <c r="AB48" s="31"/>
-      <c r="AC48" s="31"/>
-      <c r="AD48" s="31"/>
-      <c r="AE48" s="31"/>
-      <c r="AF48" s="31"/>
+      <c r="AB48" s="32"/>
+      <c r="AC48" s="32"/>
+      <c r="AD48" s="32"/>
+      <c r="AE48" s="32"/>
+      <c r="AF48" s="32"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="28" t="s">
+      <c r="A49" s="29" t="s">
         <v>398</v>
       </c>
-      <c r="B49" s="29"/>
-      <c r="C49" s="29"/>
-      <c r="D49" s="29"/>
-      <c r="E49" s="29"/>
-      <c r="F49" s="29"/>
-      <c r="G49" s="29"/>
-      <c r="H49" s="29"/>
-      <c r="I49" s="29"/>
-      <c r="J49" s="29"/>
-      <c r="K49" s="29"/>
-      <c r="L49" s="29"/>
-      <c r="M49" s="29"/>
-      <c r="N49" s="29"/>
-      <c r="O49" s="29"/>
-      <c r="P49" s="29"/>
-      <c r="Q49" s="29"/>
-      <c r="R49" s="29"/>
-      <c r="S49" s="29"/>
-      <c r="T49" s="29"/>
-      <c r="U49" s="29"/>
-      <c r="V49" s="29"/>
-      <c r="W49" s="29"/>
-      <c r="X49" s="29"/>
-      <c r="Y49" s="29"/>
-      <c r="Z49" s="29"/>
-      <c r="AA49" s="29"/>
-      <c r="AB49" s="29"/>
-      <c r="AC49" s="29"/>
-      <c r="AD49" s="29"/>
-      <c r="AE49" s="29"/>
-      <c r="AF49" s="29"/>
+      <c r="B49" s="30"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="30"/>
+      <c r="E49" s="30"/>
+      <c r="F49" s="30"/>
+      <c r="G49" s="30"/>
+      <c r="H49" s="30"/>
+      <c r="I49" s="30"/>
+      <c r="J49" s="30"/>
+      <c r="K49" s="30"/>
+      <c r="L49" s="30"/>
+      <c r="M49" s="30"/>
+      <c r="N49" s="30"/>
+      <c r="O49" s="30"/>
+      <c r="P49" s="30"/>
+      <c r="Q49" s="30"/>
+      <c r="R49" s="30"/>
+      <c r="S49" s="30"/>
+      <c r="T49" s="30"/>
+      <c r="U49" s="30"/>
+      <c r="V49" s="30"/>
+      <c r="W49" s="30"/>
+      <c r="X49" s="30"/>
+      <c r="Y49" s="30"/>
+      <c r="Z49" s="30"/>
+      <c r="AA49" s="30"/>
+      <c r="AB49" s="30"/>
+      <c r="AC49" s="30"/>
+      <c r="AD49" s="30"/>
+      <c r="AE49" s="30"/>
+      <c r="AF49" s="30"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="30" t="s">
+      <c r="A50" s="31" t="s">
         <v>399</v>
       </c>
-      <c r="B50" s="33">
+      <c r="B50" s="34">
         <v>7.32</v>
       </c>
-      <c r="C50" s="33">
+      <c r="C50" s="34">
         <v>4.78</v>
       </c>
-      <c r="D50" s="33">
+      <c r="D50" s="34">
         <v>4.01</v>
       </c>
-      <c r="E50" s="33">
+      <c r="E50" s="34">
         <v>3.08</v>
       </c>
-      <c r="F50" s="33">
+      <c r="F50" s="34">
         <v>5.03</v>
       </c>
-      <c r="G50" s="33">
+      <c r="G50" s="34">
         <v>5.11</v>
       </c>
-      <c r="H50" s="33">
+      <c r="H50" s="34">
         <v>5.67</v>
       </c>
-      <c r="I50" s="33">
+      <c r="I50" s="34">
         <v>6.82</v>
       </c>
-      <c r="J50" s="33">
+      <c r="J50" s="34">
         <v>6.1</v>
       </c>
-      <c r="K50" s="33">
+      <c r="K50" s="34">
         <v>5.21</v>
       </c>
-      <c r="L50" s="33">
+      <c r="L50" s="34">
         <v>7.01</v>
       </c>
-      <c r="M50" s="33">
+      <c r="M50" s="34">
         <v>3.72</v>
       </c>
-      <c r="N50" s="33">
+      <c r="N50" s="34">
         <v>3.27</v>
       </c>
-      <c r="O50" s="33">
+      <c r="O50" s="34">
         <v>2.02</v>
       </c>
-      <c r="P50" s="33">
+      <c r="P50" s="34">
         <v>2.26</v>
       </c>
-      <c r="Q50" s="33">
+      <c r="Q50" s="34">
         <v>4.06</v>
       </c>
-      <c r="R50" s="33">
+      <c r="R50" s="34">
         <v>3.73</v>
       </c>
-      <c r="S50" s="33">
+      <c r="S50" s="34">
         <v>2.84</v>
       </c>
-      <c r="T50" s="33">
+      <c r="T50" s="34">
         <v>5.38</v>
       </c>
-      <c r="U50" s="33">
+      <c r="U50" s="34">
         <v>4.57</v>
       </c>
-      <c r="V50" s="33">
+      <c r="V50" s="34">
         <v>5.55</v>
       </c>
-      <c r="W50" s="33">
+      <c r="W50" s="34">
         <v>3.16</v>
       </c>
-      <c r="X50" s="33">
+      <c r="X50" s="34">
         <v>2.65</v>
       </c>
-      <c r="Y50" s="33">
+      <c r="Y50" s="34">
         <v>2.43</v>
       </c>
-      <c r="Z50" s="33">
+      <c r="Z50" s="34">
         <v>2.26</v>
       </c>
-      <c r="AA50" s="33">
+      <c r="AA50" s="34">
         <v>3.8</v>
       </c>
-      <c r="AB50" s="33">
+      <c r="AB50" s="34">
         <v>3.15</v>
       </c>
-      <c r="AC50" s="33">
+      <c r="AC50" s="34">
         <v>3.84</v>
       </c>
-      <c r="AD50" s="33">
+      <c r="AD50" s="34">
         <v>6.79</v>
       </c>
-      <c r="AE50" s="33">
+      <c r="AE50" s="34">
         <v>6.6</v>
       </c>
-      <c r="AF50" s="33">
+      <c r="AF50" s="34">
         <v>6.64</v>
       </c>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="30" t="s">
+      <c r="A51" s="31" t="s">
         <v>400</v>
       </c>
-      <c r="B51" s="33">
+      <c r="B51" s="34">
         <v>5.01</v>
       </c>
-      <c r="C51" s="33">
+      <c r="C51" s="34">
         <v>4.37</v>
       </c>
-      <c r="D51" s="33">
+      <c r="D51" s="34">
         <v>4.43</v>
       </c>
-      <c r="E51" s="33">
+      <c r="E51" s="34">
         <v>4.92</v>
       </c>
-      <c r="F51" s="33">
+      <c r="F51" s="34">
         <v>5.63</v>
       </c>
-      <c r="G51" s="33">
+      <c r="G51" s="34">
         <v>5.73</v>
       </c>
-      <c r="H51" s="33">
+      <c r="H51" s="34">
         <v>6.17</v>
       </c>
-      <c r="I51" s="33">
+      <c r="I51" s="34">
         <v>5.88</v>
       </c>
-      <c r="J51" s="33">
+      <c r="J51" s="34">
         <v>5.26</v>
       </c>
-      <c r="K51" s="33">
+      <c r="K51" s="34">
         <v>4.57</v>
       </c>
-      <c r="L51" s="33">
+      <c r="L51" s="34">
         <v>4.07</v>
       </c>
-      <c r="M51" s="33">
+      <c r="M51" s="34">
         <v>3.04</v>
       </c>
-      <c r="N51" s="33">
+      <c r="N51" s="34">
         <v>2.95</v>
       </c>
-      <c r="O51" s="33">
+      <c r="O51" s="34">
         <v>2.85</v>
       </c>
-      <c r="P51" s="33">
+      <c r="P51" s="34">
         <v>3.56</v>
       </c>
-      <c r="Q51" s="33">
+      <c r="Q51" s="34">
         <v>4.04</v>
       </c>
-      <c r="R51" s="33">
+      <c r="R51" s="34">
         <v>4.22</v>
       </c>
-      <c r="S51" s="33">
+      <c r="S51" s="34">
         <v>4.21</v>
       </c>
-      <c r="T51" s="33">
+      <c r="T51" s="34">
         <v>4.48</v>
       </c>
-      <c r="U51" s="33">
+      <c r="U51" s="34">
         <v>3.77</v>
       </c>
-      <c r="V51" s="33">
+      <c r="V51" s="34">
         <v>3.26</v>
       </c>
-      <c r="W51" s="33">
+      <c r="W51" s="34">
         <v>2.89</v>
       </c>
-      <c r="X51" s="33">
+      <c r="X51" s="34">
         <v>2.89</v>
       </c>
-      <c r="Y51" s="33">
+      <c r="Y51" s="34">
         <v>3.1</v>
       </c>
-      <c r="Z51" s="33">
+      <c r="Z51" s="34">
         <v>3.84</v>
       </c>
-      <c r="AA51" s="33">
+      <c r="AA51" s="34">
         <v>4.61</v>
       </c>
-      <c r="AB51" s="33">
+      <c r="AB51" s="34">
         <v>5.09</v>
       </c>
-      <c r="AC51" s="31"/>
-      <c r="AD51" s="31"/>
-      <c r="AE51" s="31"/>
-      <c r="AF51" s="31"/>
+      <c r="AC51" s="32"/>
+      <c r="AD51" s="32"/>
+      <c r="AE51" s="32"/>
+      <c r="AF51" s="32"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="28" t="s">
+      <c r="A52" s="29" t="s">
         <v>401</v>
       </c>
-      <c r="B52" s="29"/>
-      <c r="C52" s="29"/>
-      <c r="D52" s="29"/>
-      <c r="E52" s="29"/>
-      <c r="F52" s="29"/>
-      <c r="G52" s="29"/>
-      <c r="H52" s="29"/>
-      <c r="I52" s="29"/>
-      <c r="J52" s="29"/>
-      <c r="K52" s="29"/>
-      <c r="L52" s="29"/>
-      <c r="M52" s="29"/>
-      <c r="N52" s="29"/>
-      <c r="O52" s="29"/>
-      <c r="P52" s="29"/>
-      <c r="Q52" s="29"/>
-      <c r="R52" s="29"/>
-      <c r="S52" s="29"/>
-      <c r="T52" s="29"/>
-      <c r="U52" s="29"/>
-      <c r="V52" s="29"/>
-      <c r="W52" s="29"/>
-      <c r="X52" s="29"/>
-      <c r="Y52" s="29"/>
-      <c r="Z52" s="29"/>
-      <c r="AA52" s="29"/>
-      <c r="AB52" s="29"/>
-      <c r="AC52" s="29"/>
-      <c r="AD52" s="29"/>
-      <c r="AE52" s="29"/>
-      <c r="AF52" s="29"/>
+      <c r="B52" s="30"/>
+      <c r="C52" s="30"/>
+      <c r="D52" s="30"/>
+      <c r="E52" s="30"/>
+      <c r="F52" s="30"/>
+      <c r="G52" s="30"/>
+      <c r="H52" s="30"/>
+      <c r="I52" s="30"/>
+      <c r="J52" s="30"/>
+      <c r="K52" s="30"/>
+      <c r="L52" s="30"/>
+      <c r="M52" s="30"/>
+      <c r="N52" s="30"/>
+      <c r="O52" s="30"/>
+      <c r="P52" s="30"/>
+      <c r="Q52" s="30"/>
+      <c r="R52" s="30"/>
+      <c r="S52" s="30"/>
+      <c r="T52" s="30"/>
+      <c r="U52" s="30"/>
+      <c r="V52" s="30"/>
+      <c r="W52" s="30"/>
+      <c r="X52" s="30"/>
+      <c r="Y52" s="30"/>
+      <c r="Z52" s="30"/>
+      <c r="AA52" s="30"/>
+      <c r="AB52" s="30"/>
+      <c r="AC52" s="30"/>
+      <c r="AD52" s="30"/>
+      <c r="AE52" s="30"/>
+      <c r="AF52" s="30"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="30" t="s">
+      <c r="A53" s="31" t="s">
         <v>402</v>
       </c>
-      <c r="B53" s="33">
+      <c r="B53" s="34">
         <v>15.12</v>
       </c>
-      <c r="C53" s="33">
+      <c r="C53" s="34">
         <v>9.68</v>
       </c>
-      <c r="D53" s="33">
+      <c r="D53" s="34">
         <v>8.0</v>
       </c>
-      <c r="E53" s="33">
+      <c r="E53" s="34">
         <v>7.18</v>
       </c>
-      <c r="F53" s="33">
+      <c r="F53" s="34">
         <v>11.24</v>
       </c>
-      <c r="G53" s="33">
+      <c r="G53" s="34">
         <v>14.36</v>
       </c>
-      <c r="H53" s="33">
+      <c r="H53" s="34">
         <v>12.54</v>
       </c>
-      <c r="I53" s="33">
+      <c r="I53" s="34">
         <v>14.78</v>
       </c>
-      <c r="J53" s="33">
+      <c r="J53" s="34">
         <v>14.06</v>
       </c>
-      <c r="K53" s="33">
+      <c r="K53" s="34">
         <v>10.73</v>
       </c>
-      <c r="L53" s="33">
+      <c r="L53" s="34">
         <v>12.74</v>
       </c>
-      <c r="M53" s="33">
+      <c r="M53" s="34">
         <v>7.8</v>
       </c>
-      <c r="N53" s="33">
+      <c r="N53" s="34">
         <v>9.3</v>
       </c>
-      <c r="O53" s="33">
+      <c r="O53" s="34">
         <v>7.23</v>
       </c>
-      <c r="P53" s="33">
+      <c r="P53" s="34">
         <v>7.83</v>
       </c>
-      <c r="Q53" s="33">
+      <c r="Q53" s="34">
         <v>16.82</v>
       </c>
-      <c r="R53" s="33">
+      <c r="R53" s="34">
         <v>7.57</v>
       </c>
-      <c r="S53" s="33">
+      <c r="S53" s="34">
         <v>4.86</v>
       </c>
-      <c r="T53" s="33">
+      <c r="T53" s="34">
         <v>10.83</v>
       </c>
-      <c r="U53" s="33">
+      <c r="U53" s="34">
         <v>11.23</v>
       </c>
-      <c r="V53" s="33">
+      <c r="V53" s="34">
         <v>21.26</v>
       </c>
-      <c r="W53" s="33">
+      <c r="W53" s="34">
         <v>11.53</v>
       </c>
-      <c r="X53" s="33">
+      <c r="X53" s="34">
         <v>29.0</v>
       </c>
-      <c r="Y53" s="33">
+      <c r="Y53" s="34">
         <v>8.71</v>
       </c>
-      <c r="Z53" s="33">
+      <c r="Z53" s="34">
         <v>10.09</v>
       </c>
-      <c r="AA53" s="33">
+      <c r="AA53" s="34">
         <v>8.99</v>
       </c>
-      <c r="AB53" s="33">
+      <c r="AB53" s="34">
         <v>6.61</v>
       </c>
-      <c r="AC53" s="33">
+      <c r="AC53" s="34">
         <v>8.47</v>
       </c>
-      <c r="AD53" s="33">
+      <c r="AD53" s="34">
         <v>13.75</v>
       </c>
-      <c r="AE53" s="33">
+      <c r="AE53" s="34">
         <v>11.01</v>
       </c>
-      <c r="AF53" s="33">
+      <c r="AF53" s="34">
         <v>12.42</v>
       </c>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="30" t="s">
+      <c r="A54" s="31" t="s">
         <v>403</v>
       </c>
-      <c r="B54" s="33">
+      <c r="B54" s="34">
         <v>10.53</v>
       </c>
-      <c r="C54" s="33">
+      <c r="C54" s="34">
         <v>9.62</v>
       </c>
-      <c r="D54" s="33">
+      <c r="D54" s="34">
         <v>10.01</v>
       </c>
-      <c r="E54" s="33">
+      <c r="E54" s="34">
         <v>11.57</v>
       </c>
-      <c r="F54" s="33">
+      <c r="F54" s="34">
         <v>13.22</v>
       </c>
-      <c r="G54" s="33">
+      <c r="G54" s="34">
         <v>13.33</v>
       </c>
-      <c r="H54" s="33">
+      <c r="H54" s="34">
         <v>12.96</v>
       </c>
-      <c r="I54" s="33">
+      <c r="I54" s="34">
         <v>12.2</v>
       </c>
-      <c r="J54" s="33">
+      <c r="J54" s="34">
         <v>11.23</v>
       </c>
-      <c r="K54" s="33">
+      <c r="K54" s="34">
         <v>10.21</v>
       </c>
-      <c r="L54" s="33">
+      <c r="L54" s="34">
         <v>9.81</v>
       </c>
-      <c r="M54" s="33">
+      <c r="M54" s="34">
         <v>8.73</v>
       </c>
-      <c r="N54" s="33">
+      <c r="N54" s="34">
         <v>8.83</v>
       </c>
-      <c r="O54" s="33">
+      <c r="O54" s="34">
         <v>7.39</v>
       </c>
-      <c r="P54" s="33">
+      <c r="P54" s="34">
         <v>8.19</v>
       </c>
-      <c r="Q54" s="33">
+      <c r="Q54" s="34">
         <v>8.67</v>
       </c>
-      <c r="R54" s="33">
+      <c r="R54" s="34">
         <v>8.9</v>
       </c>
-      <c r="S54" s="33">
+      <c r="S54" s="34">
         <v>9.51</v>
       </c>
-      <c r="T54" s="33">
+      <c r="T54" s="34">
         <v>13.06</v>
       </c>
-      <c r="U54" s="33">
+      <c r="U54" s="34">
         <v>13.57</v>
       </c>
-      <c r="V54" s="33">
+      <c r="V54" s="34">
         <v>14.09</v>
       </c>
-      <c r="W54" s="33">
+      <c r="W54" s="34">
         <v>10.83</v>
       </c>
-      <c r="X54" s="33">
+      <c r="X54" s="34">
         <v>9.23</v>
       </c>
-      <c r="Y54" s="33">
+      <c r="Y54" s="34">
         <v>8.27</v>
       </c>
-      <c r="Z54" s="33">
+      <c r="Z54" s="34">
         <v>9.26</v>
       </c>
-      <c r="AA54" s="33">
+      <c r="AA54" s="34">
         <v>9.54</v>
       </c>
-      <c r="AB54" s="33">
+      <c r="AB54" s="34">
         <v>10.07</v>
       </c>
-      <c r="AC54" s="31"/>
-      <c r="AD54" s="31"/>
-      <c r="AE54" s="31"/>
-      <c r="AF54" s="31"/>
+      <c r="AC54" s="32"/>
+      <c r="AD54" s="32"/>
+      <c r="AE54" s="32"/>
+      <c r="AF54" s="32"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="28" t="s">
+      <c r="A55" s="29" t="s">
         <v>404</v>
       </c>
-      <c r="B55" s="29"/>
-      <c r="C55" s="29"/>
-      <c r="D55" s="29"/>
-      <c r="E55" s="29"/>
-      <c r="F55" s="29"/>
-      <c r="G55" s="29"/>
-      <c r="H55" s="29"/>
-      <c r="I55" s="29"/>
-      <c r="J55" s="29"/>
-      <c r="K55" s="29"/>
-      <c r="L55" s="29"/>
-      <c r="M55" s="29"/>
-      <c r="N55" s="29"/>
-      <c r="O55" s="29"/>
-      <c r="P55" s="29"/>
-      <c r="Q55" s="29"/>
-      <c r="R55" s="29"/>
-      <c r="S55" s="29"/>
-      <c r="T55" s="29"/>
-      <c r="U55" s="29"/>
-      <c r="V55" s="29"/>
-      <c r="W55" s="29"/>
-      <c r="X55" s="29"/>
-      <c r="Y55" s="29"/>
-      <c r="Z55" s="29"/>
-      <c r="AA55" s="29"/>
-      <c r="AB55" s="29"/>
-      <c r="AC55" s="29"/>
-      <c r="AD55" s="29"/>
-      <c r="AE55" s="29"/>
-      <c r="AF55" s="29"/>
+      <c r="B55" s="30"/>
+      <c r="C55" s="30"/>
+      <c r="D55" s="30"/>
+      <c r="E55" s="30"/>
+      <c r="F55" s="30"/>
+      <c r="G55" s="30"/>
+      <c r="H55" s="30"/>
+      <c r="I55" s="30"/>
+      <c r="J55" s="30"/>
+      <c r="K55" s="30"/>
+      <c r="L55" s="30"/>
+      <c r="M55" s="30"/>
+      <c r="N55" s="30"/>
+      <c r="O55" s="30"/>
+      <c r="P55" s="30"/>
+      <c r="Q55" s="30"/>
+      <c r="R55" s="30"/>
+      <c r="S55" s="30"/>
+      <c r="T55" s="30"/>
+      <c r="U55" s="30"/>
+      <c r="V55" s="30"/>
+      <c r="W55" s="30"/>
+      <c r="X55" s="30"/>
+      <c r="Y55" s="30"/>
+      <c r="Z55" s="30"/>
+      <c r="AA55" s="30"/>
+      <c r="AB55" s="30"/>
+      <c r="AC55" s="30"/>
+      <c r="AD55" s="30"/>
+      <c r="AE55" s="30"/>
+      <c r="AF55" s="30"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="30" t="s">
+      <c r="A56" s="31" t="s">
         <v>405</v>
       </c>
-      <c r="B56" s="33">
+      <c r="B56" s="34">
         <v>15.14</v>
       </c>
-      <c r="C56" s="33">
+      <c r="C56" s="34">
         <v>9.75</v>
       </c>
-      <c r="D56" s="33">
+      <c r="D56" s="34">
         <v>8.06</v>
       </c>
-      <c r="E56" s="33">
+      <c r="E56" s="34">
         <v>6.72</v>
       </c>
-      <c r="F56" s="33">
+      <c r="F56" s="34">
         <v>11.07</v>
       </c>
-      <c r="G56" s="33">
+      <c r="G56" s="34">
         <v>12.07</v>
       </c>
-      <c r="H56" s="33">
+      <c r="H56" s="34">
         <v>12.56</v>
       </c>
-      <c r="I56" s="33">
+      <c r="I56" s="34">
         <v>14.78</v>
       </c>
-      <c r="J56" s="33">
+      <c r="J56" s="34">
         <v>14.22</v>
       </c>
-      <c r="K56" s="33">
+      <c r="K56" s="34">
         <v>10.75</v>
       </c>
-      <c r="L56" s="33">
+      <c r="L56" s="34">
         <v>12.68</v>
       </c>
-      <c r="M56" s="33">
+      <c r="M56" s="34">
         <v>7.8</v>
       </c>
-      <c r="N56" s="33">
+      <c r="N56" s="34">
         <v>9.41</v>
       </c>
-      <c r="O56" s="33">
+      <c r="O56" s="34">
         <v>7.3</v>
       </c>
-      <c r="P56" s="33">
+      <c r="P56" s="34">
         <v>7.84</v>
       </c>
-      <c r="Q56" s="33">
+      <c r="Q56" s="34">
         <v>25.93</v>
       </c>
-      <c r="R56" s="33">
+      <c r="R56" s="34">
         <v>7.57</v>
       </c>
-      <c r="S56" s="33">
+      <c r="S56" s="34">
         <v>4.86</v>
       </c>
-      <c r="T56" s="33">
+      <c r="T56" s="34">
         <v>10.83</v>
       </c>
-      <c r="U56" s="33">
+      <c r="U56" s="34">
         <v>11.23</v>
       </c>
-      <c r="V56" s="33">
+      <c r="V56" s="34">
         <v>21.26</v>
       </c>
-      <c r="W56" s="33">
+      <c r="W56" s="34">
         <v>11.53</v>
       </c>
-      <c r="X56" s="33">
+      <c r="X56" s="34">
         <v>29.0</v>
       </c>
-      <c r="Y56" s="33">
+      <c r="Y56" s="34">
         <v>8.71</v>
       </c>
-      <c r="Z56" s="33">
+      <c r="Z56" s="34">
         <v>10.09</v>
       </c>
-      <c r="AA56" s="33">
+      <c r="AA56" s="34">
         <v>8.99</v>
       </c>
-      <c r="AB56" s="33">
+      <c r="AB56" s="34">
         <v>6.61</v>
       </c>
-      <c r="AC56" s="33">
+      <c r="AC56" s="34">
         <v>8.47</v>
       </c>
-      <c r="AD56" s="33">
+      <c r="AD56" s="34">
         <v>13.75</v>
       </c>
-      <c r="AE56" s="33">
+      <c r="AE56" s="34">
         <v>11.01</v>
       </c>
-      <c r="AF56" s="33">
+      <c r="AF56" s="34">
         <v>12.42</v>
       </c>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="30" t="s">
+      <c r="A57" s="31" t="s">
         <v>406</v>
       </c>
-      <c r="B57" s="33">
+      <c r="B57" s="34">
         <v>1.6</v>
       </c>
-      <c r="C57" s="33">
+      <c r="C57" s="34">
         <v>1.4</v>
       </c>
-      <c r="D57" s="33">
+      <c r="D57" s="34">
         <v>1.36</v>
       </c>
-      <c r="E57" s="33">
+      <c r="E57" s="34">
         <v>1.4</v>
       </c>
-      <c r="F57" s="33">
+      <c r="F57" s="34">
         <v>1.52</v>
       </c>
-      <c r="G57" s="33">
+      <c r="G57" s="34">
         <v>1.5</v>
       </c>
-      <c r="H57" s="33">
+      <c r="H57" s="34">
         <v>1.57</v>
       </c>
-      <c r="I57" s="33">
+      <c r="I57" s="34">
         <v>1.51</v>
       </c>
-      <c r="J57" s="33">
+      <c r="J57" s="34">
         <v>1.36</v>
       </c>
-      <c r="K57" s="33">
+      <c r="K57" s="34">
         <v>1.21</v>
       </c>
-      <c r="L57" s="33">
+      <c r="L57" s="34">
         <v>1.07</v>
       </c>
-      <c r="M57" s="33">
+      <c r="M57" s="34">
         <v>0.71</v>
       </c>
-      <c r="N57" s="33">
+      <c r="N57" s="34">
         <v>0.66</v>
       </c>
-      <c r="O57" s="33">
+      <c r="O57" s="34">
         <v>0.66</v>
       </c>
-      <c r="P57" s="33">
+      <c r="P57" s="34">
         <v>0.83</v>
       </c>
-      <c r="Q57" s="33">
+      <c r="Q57" s="34">
         <v>0.96</v>
       </c>
-      <c r="R57" s="33">
+      <c r="R57" s="34">
         <v>1.08</v>
       </c>
-      <c r="S57" s="33">
+      <c r="S57" s="34">
         <v>1.06</v>
       </c>
-      <c r="T57" s="33">
+      <c r="T57" s="34">
         <v>1.02</v>
       </c>
-      <c r="U57" s="33">
+      <c r="U57" s="34">
         <v>0.79</v>
       </c>
-      <c r="V57" s="33">
+      <c r="V57" s="34">
         <v>0.65</v>
       </c>
-      <c r="W57" s="33">
+      <c r="W57" s="34">
         <v>0.59</v>
       </c>
-      <c r="X57" s="33">
+      <c r="X57" s="34">
         <v>0.64</v>
       </c>
-      <c r="Y57" s="33">
+      <c r="Y57" s="34">
         <v>0.73</v>
       </c>
-      <c r="Z57" s="33">
+      <c r="Z57" s="34">
         <v>0.94</v>
       </c>
-      <c r="AA57" s="33">
+      <c r="AA57" s="34">
         <v>1.2</v>
       </c>
-      <c r="AB57" s="33">
+      <c r="AB57" s="34">
         <v>1.34</v>
       </c>
-      <c r="AC57" s="31"/>
-      <c r="AD57" s="31"/>
-      <c r="AE57" s="31"/>
-      <c r="AF57" s="31"/>
+      <c r="AC57" s="32"/>
+      <c r="AD57" s="32"/>
+      <c r="AE57" s="32"/>
+      <c r="AF57" s="32"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="28" t="s">
+      <c r="A58" s="29" t="s">
         <v>407</v>
       </c>
-      <c r="B58" s="29"/>
-      <c r="C58" s="29"/>
-      <c r="D58" s="29"/>
-      <c r="E58" s="29"/>
-      <c r="F58" s="29"/>
-      <c r="G58" s="29"/>
-      <c r="H58" s="29"/>
-      <c r="I58" s="29"/>
-      <c r="J58" s="29"/>
-      <c r="K58" s="29"/>
-      <c r="L58" s="29"/>
-      <c r="M58" s="29"/>
-      <c r="N58" s="29"/>
-      <c r="O58" s="29"/>
-      <c r="P58" s="29"/>
-      <c r="Q58" s="29"/>
-      <c r="R58" s="29"/>
-      <c r="S58" s="29"/>
-      <c r="T58" s="29"/>
-      <c r="U58" s="29"/>
-      <c r="V58" s="29"/>
-      <c r="W58" s="29"/>
-      <c r="X58" s="29"/>
-      <c r="Y58" s="29"/>
-      <c r="Z58" s="29"/>
-      <c r="AA58" s="29"/>
-      <c r="AB58" s="29"/>
-      <c r="AC58" s="29"/>
-      <c r="AD58" s="29"/>
-      <c r="AE58" s="29"/>
-      <c r="AF58" s="29"/>
+      <c r="B58" s="30"/>
+      <c r="C58" s="30"/>
+      <c r="D58" s="30"/>
+      <c r="E58" s="30"/>
+      <c r="F58" s="30"/>
+      <c r="G58" s="30"/>
+      <c r="H58" s="30"/>
+      <c r="I58" s="30"/>
+      <c r="J58" s="30"/>
+      <c r="K58" s="30"/>
+      <c r="L58" s="30"/>
+      <c r="M58" s="30"/>
+      <c r="N58" s="30"/>
+      <c r="O58" s="30"/>
+      <c r="P58" s="30"/>
+      <c r="Q58" s="30"/>
+      <c r="R58" s="30"/>
+      <c r="S58" s="30"/>
+      <c r="T58" s="30"/>
+      <c r="U58" s="30"/>
+      <c r="V58" s="30"/>
+      <c r="W58" s="30"/>
+      <c r="X58" s="30"/>
+      <c r="Y58" s="30"/>
+      <c r="Z58" s="30"/>
+      <c r="AA58" s="30"/>
+      <c r="AB58" s="30"/>
+      <c r="AC58" s="30"/>
+      <c r="AD58" s="30"/>
+      <c r="AE58" s="30"/>
+      <c r="AF58" s="30"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="30" t="s">
+      <c r="A59" s="31" t="s">
         <v>408</v>
       </c>
-      <c r="B59" s="33">
+      <c r="B59" s="34">
         <v>1.74</v>
       </c>
-      <c r="C59" s="33">
+      <c r="C59" s="34">
         <v>3.15</v>
       </c>
-      <c r="D59" s="33">
+      <c r="D59" s="34">
         <v>0.14</v>
       </c>
-      <c r="E59" s="33">
+      <c r="E59" s="34">
         <v>0.64</v>
       </c>
-      <c r="F59" s="33">
+      <c r="F59" s="34">
         <v>0.44</v>
       </c>
-      <c r="G59" s="33">
+      <c r="G59" s="34">
         <v>2.75</v>
       </c>
-      <c r="H59" s="33">
+      <c r="H59" s="34">
         <v>1.64</v>
       </c>
-      <c r="I59" s="33">
+      <c r="I59" s="34">
         <v>0.59</v>
       </c>
-      <c r="J59" s="36">
+      <c r="J59" s="37">
         <v>-1.25</v>
       </c>
-      <c r="K59" s="36">
+      <c r="K59" s="37">
         <v>-0.61</v>
       </c>
-      <c r="L59" s="33">
+      <c r="L59" s="34">
         <v>0.29</v>
       </c>
-      <c r="M59" s="33">
+      <c r="M59" s="34">
         <v>0.11</v>
       </c>
-      <c r="N59" s="33">
+      <c r="N59" s="34">
         <v>0.28</v>
       </c>
-      <c r="O59" s="33">
+      <c r="O59" s="34">
         <v>0.51</v>
       </c>
-      <c r="P59" s="33">
+      <c r="P59" s="34">
         <v>0.08</v>
       </c>
-      <c r="Q59" s="36">
+      <c r="Q59" s="37">
         <v>-0.25</v>
       </c>
-      <c r="R59" s="36">
+      <c r="R59" s="37">
         <v>-0.3</v>
       </c>
-      <c r="S59" s="33">
+      <c r="S59" s="34">
         <v>0.12</v>
       </c>
-      <c r="T59" s="33">
+      <c r="T59" s="34">
         <v>0.18</v>
       </c>
-      <c r="U59" s="33">
+      <c r="U59" s="34">
         <v>0.11</v>
       </c>
-      <c r="V59" s="36">
+      <c r="V59" s="37">
         <v>-6.91</v>
       </c>
-      <c r="W59" s="33">
+      <c r="W59" s="34">
         <v>0.04</v>
       </c>
-      <c r="X59" s="36">
+      <c r="X59" s="37">
         <v>-0.4</v>
       </c>
-      <c r="Y59" s="33">
+      <c r="Y59" s="34">
         <v>0.23</v>
       </c>
-      <c r="Z59" s="36">
+      <c r="Z59" s="37">
         <v>-0.19</v>
       </c>
-      <c r="AA59" s="36">
+      <c r="AA59" s="37">
         <v>-0.51</v>
       </c>
-      <c r="AB59" s="33">
+      <c r="AB59" s="34">
         <v>0.18</v>
       </c>
-      <c r="AC59" s="33">
+      <c r="AC59" s="34">
         <v>1.94</v>
       </c>
-      <c r="AD59" s="36">
+      <c r="AD59" s="37">
         <v>-0.82</v>
       </c>
-      <c r="AE59" s="33">
+      <c r="AE59" s="34">
         <v>0.21</v>
       </c>
-      <c r="AF59" s="31"/>
+      <c r="AF59" s="32"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="30" t="s">
+      <c r="A60" s="31" t="s">
         <v>409</v>
       </c>
-      <c r="B60" s="33">
+      <c r="B60" s="34">
         <v>0.54</v>
       </c>
-      <c r="C60" s="33">
+      <c r="C60" s="34">
         <v>0.51</v>
       </c>
-      <c r="D60" s="33">
+      <c r="D60" s="34">
         <v>0.51</v>
       </c>
-      <c r="E60" s="33">
+      <c r="E60" s="34">
         <v>0.79</v>
       </c>
-      <c r="F60" s="33">
+      <c r="F60" s="34">
         <v>1.39</v>
       </c>
-      <c r="G60" s="33">
+      <c r="G60" s="34">
         <v>18.92</v>
       </c>
-      <c r="H60" s="33">
+      <c r="H60" s="34">
         <v>1.78</v>
       </c>
-      <c r="I60" s="33">
+      <c r="I60" s="34">
         <v>0.69</v>
       </c>
-      <c r="J60" s="33">
+      <c r="J60" s="34">
         <v>0.59</v>
       </c>
-      <c r="K60" s="33">
+      <c r="K60" s="34">
         <v>0.4</v>
       </c>
-      <c r="L60" s="33">
+      <c r="L60" s="34">
         <v>0.2</v>
       </c>
-      <c r="M60" s="33">
+      <c r="M60" s="34">
         <v>0.85</v>
       </c>
-      <c r="N60" s="36">
+      <c r="N60" s="37">
         <v>-1.38</v>
       </c>
-      <c r="O60" s="36">
+      <c r="O60" s="37">
         <v>-1.43</v>
       </c>
-      <c r="P60" s="33">
+      <c r="P60" s="34">
         <v>5.9</v>
       </c>
-      <c r="Q60" s="33">
+      <c r="Q60" s="34">
         <v>3.57</v>
       </c>
-      <c r="R60" s="33">
+      <c r="R60" s="34">
         <v>0.32</v>
       </c>
-      <c r="S60" s="33">
+      <c r="S60" s="34">
         <v>0.13</v>
       </c>
-      <c r="T60" s="33">
+      <c r="T60" s="34">
         <v>0.51</v>
       </c>
-      <c r="U60" s="33">
+      <c r="U60" s="34">
         <v>0.62</v>
       </c>
-      <c r="V60" s="36">
+      <c r="V60" s="37">
         <v>-1.46</v>
       </c>
-      <c r="W60" s="36">
+      <c r="W60" s="37">
         <v>-0.86</v>
       </c>
-      <c r="X60" s="36">
+      <c r="X60" s="37">
         <v>-0.33</v>
       </c>
-      <c r="Y60" s="36">
+      <c r="Y60" s="37">
         <v>-1.49</v>
       </c>
-      <c r="Z60" s="36">
+      <c r="Z60" s="37">
         <v>-0.63</v>
       </c>
-      <c r="AA60" s="33">
+      <c r="AA60" s="34">
         <v>1.14</v>
       </c>
-      <c r="AB60" s="31"/>
-      <c r="AC60" s="31"/>
-      <c r="AD60" s="31"/>
-      <c r="AE60" s="31"/>
-      <c r="AF60" s="31"/>
+      <c r="AB60" s="32"/>
+      <c r="AC60" s="32"/>
+      <c r="AD60" s="32"/>
+      <c r="AE60" s="32"/>
+      <c r="AF60" s="32"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="28" t="s">
+      <c r="A61" s="29" t="s">
         <v>410</v>
       </c>
-      <c r="B61" s="29"/>
-      <c r="C61" s="29"/>
-      <c r="D61" s="29"/>
-      <c r="E61" s="29"/>
-      <c r="F61" s="29"/>
-      <c r="G61" s="29"/>
-      <c r="H61" s="29"/>
-      <c r="I61" s="29"/>
-      <c r="J61" s="29"/>
-      <c r="K61" s="29"/>
-      <c r="L61" s="29"/>
-      <c r="M61" s="29"/>
-      <c r="N61" s="29"/>
-      <c r="O61" s="29"/>
-      <c r="P61" s="29"/>
-      <c r="Q61" s="29"/>
-      <c r="R61" s="29"/>
-      <c r="S61" s="29"/>
-      <c r="T61" s="29"/>
-      <c r="U61" s="29"/>
-      <c r="V61" s="29"/>
-      <c r="W61" s="29"/>
-      <c r="X61" s="29"/>
-      <c r="Y61" s="29"/>
-      <c r="Z61" s="29"/>
-      <c r="AA61" s="29"/>
-      <c r="AB61" s="29"/>
-      <c r="AC61" s="29"/>
-      <c r="AD61" s="29"/>
-      <c r="AE61" s="29"/>
-      <c r="AF61" s="29"/>
+      <c r="B61" s="30"/>
+      <c r="C61" s="30"/>
+      <c r="D61" s="30"/>
+      <c r="E61" s="30"/>
+      <c r="F61" s="30"/>
+      <c r="G61" s="30"/>
+      <c r="H61" s="30"/>
+      <c r="I61" s="30"/>
+      <c r="J61" s="30"/>
+      <c r="K61" s="30"/>
+      <c r="L61" s="30"/>
+      <c r="M61" s="30"/>
+      <c r="N61" s="30"/>
+      <c r="O61" s="30"/>
+      <c r="P61" s="30"/>
+      <c r="Q61" s="30"/>
+      <c r="R61" s="30"/>
+      <c r="S61" s="30"/>
+      <c r="T61" s="30"/>
+      <c r="U61" s="30"/>
+      <c r="V61" s="30"/>
+      <c r="W61" s="30"/>
+      <c r="X61" s="30"/>
+      <c r="Y61" s="30"/>
+      <c r="Z61" s="30"/>
+      <c r="AA61" s="30"/>
+      <c r="AB61" s="30"/>
+      <c r="AC61" s="30"/>
+      <c r="AD61" s="30"/>
+      <c r="AE61" s="30"/>
+      <c r="AF61" s="30"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="30" t="s">
+      <c r="A62" s="31" t="s">
         <v>411</v>
       </c>
-      <c r="B62" s="33">
+      <c r="B62" s="34">
         <v>0.55</v>
       </c>
-      <c r="C62" s="33">
+      <c r="C62" s="34">
         <v>0.38</v>
       </c>
-      <c r="D62" s="33">
+      <c r="D62" s="34">
         <v>0.38</v>
       </c>
-      <c r="E62" s="33">
+      <c r="E62" s="34">
         <v>0.26</v>
       </c>
-      <c r="F62" s="33">
+      <c r="F62" s="34">
         <v>0.32</v>
       </c>
-      <c r="G62" s="33">
+      <c r="G62" s="34">
         <v>0.31</v>
       </c>
-      <c r="H62" s="33">
+      <c r="H62" s="34">
         <v>0.32</v>
       </c>
-      <c r="I62" s="33">
+      <c r="I62" s="34">
         <v>0.41</v>
       </c>
-      <c r="J62" s="33">
+      <c r="J62" s="34">
         <v>0.36</v>
       </c>
-      <c r="K62" s="33">
+      <c r="K62" s="34">
         <v>0.33</v>
       </c>
-      <c r="L62" s="33">
+      <c r="L62" s="34">
         <v>0.44</v>
       </c>
-      <c r="M62" s="33">
+      <c r="M62" s="34">
         <v>0.27</v>
       </c>
-      <c r="N62" s="33">
+      <c r="N62" s="34">
         <v>0.27</v>
       </c>
-      <c r="O62" s="33">
+      <c r="O62" s="34">
         <v>0.15</v>
       </c>
-      <c r="P62" s="33">
+      <c r="P62" s="34">
         <v>0.17</v>
       </c>
-      <c r="Q62" s="33">
+      <c r="Q62" s="34">
         <v>0.23</v>
       </c>
-      <c r="R62" s="33">
+      <c r="R62" s="34">
         <v>0.27</v>
       </c>
-      <c r="S62" s="33">
+      <c r="S62" s="34">
         <v>0.25</v>
       </c>
-      <c r="T62" s="33">
+      <c r="T62" s="34">
         <v>0.46</v>
       </c>
-      <c r="U62" s="33">
+      <c r="U62" s="34">
         <v>0.39</v>
       </c>
-      <c r="V62" s="33">
+      <c r="V62" s="34">
         <v>0.35</v>
       </c>
-      <c r="W62" s="33">
+      <c r="W62" s="34">
         <v>0.25</v>
       </c>
-      <c r="X62" s="33">
+      <c r="X62" s="34">
         <v>0.18</v>
       </c>
-      <c r="Y62" s="33">
+      <c r="Y62" s="34">
         <v>0.23</v>
       </c>
-      <c r="Z62" s="33">
+      <c r="Z62" s="34">
         <v>0.28</v>
       </c>
-      <c r="AA62" s="33">
+      <c r="AA62" s="34">
         <v>0.31</v>
       </c>
-      <c r="AB62" s="33">
+      <c r="AB62" s="34">
         <v>0.26</v>
       </c>
-      <c r="AC62" s="33">
+      <c r="AC62" s="34">
         <v>0.26</v>
       </c>
-      <c r="AD62" s="33">
+      <c r="AD62" s="34">
         <v>0.44</v>
       </c>
-      <c r="AE62" s="33">
+      <c r="AE62" s="34">
         <v>0.46</v>
       </c>
-      <c r="AF62" s="33">
+      <c r="AF62" s="34">
         <v>0.42</v>
       </c>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="30" t="s">
+      <c r="A63" s="31" t="s">
         <v>412</v>
       </c>
-      <c r="B63" s="33">
+      <c r="B63" s="34">
         <v>0.39</v>
       </c>
-      <c r="C63" s="33">
+      <c r="C63" s="34">
         <v>0.34</v>
       </c>
-      <c r="D63" s="33">
+      <c r="D63" s="34">
         <v>0.32</v>
       </c>
-      <c r="E63" s="33">
+      <c r="E63" s="34">
         <v>0.32</v>
       </c>
-      <c r="F63" s="33">
+      <c r="F63" s="34">
         <v>0.34</v>
       </c>
-      <c r="G63" s="33">
+      <c r="G63" s="34">
         <v>0.35</v>
       </c>
-      <c r="H63" s="33">
+      <c r="H63" s="34">
         <v>0.37</v>
       </c>
-      <c r="I63" s="33">
+      <c r="I63" s="34">
         <v>0.37</v>
       </c>
-      <c r="J63" s="33">
+      <c r="J63" s="34">
         <v>0.34</v>
       </c>
-      <c r="K63" s="33">
+      <c r="K63" s="34">
         <v>0.3</v>
       </c>
-      <c r="L63" s="33">
+      <c r="L63" s="34">
         <v>0.28</v>
       </c>
-      <c r="M63" s="33">
+      <c r="M63" s="34">
         <v>0.22</v>
       </c>
-      <c r="N63" s="33">
+      <c r="N63" s="34">
         <v>0.21</v>
       </c>
-      <c r="O63" s="33">
+      <c r="O63" s="34">
         <v>0.21</v>
       </c>
-      <c r="P63" s="33">
+      <c r="P63" s="34">
         <v>0.27</v>
       </c>
-      <c r="Q63" s="33">
+      <c r="Q63" s="34">
         <v>0.31</v>
       </c>
-      <c r="R63" s="33">
+      <c r="R63" s="34">
         <v>0.34</v>
       </c>
-      <c r="S63" s="33">
+      <c r="S63" s="34">
         <v>0.34</v>
       </c>
-      <c r="T63" s="33">
+      <c r="T63" s="34">
         <v>0.34</v>
       </c>
-      <c r="U63" s="33">
+      <c r="U63" s="34">
         <v>0.29</v>
       </c>
-      <c r="V63" s="33">
+      <c r="V63" s="34">
         <v>0.26</v>
       </c>
-      <c r="W63" s="33">
+      <c r="W63" s="34">
         <v>0.25</v>
       </c>
-      <c r="X63" s="33">
+      <c r="X63" s="34">
         <v>0.25</v>
       </c>
-      <c r="Y63" s="33">
+      <c r="Y63" s="34">
         <v>0.27</v>
       </c>
-      <c r="Z63" s="33">
+      <c r="Z63" s="34">
         <v>0.3</v>
       </c>
-      <c r="AA63" s="33">
+      <c r="AA63" s="34">
         <v>0.34</v>
       </c>
-      <c r="AB63" s="33">
+      <c r="AB63" s="34">
         <v>0.36</v>
       </c>
-      <c r="AC63" s="31"/>
-      <c r="AD63" s="31"/>
-      <c r="AE63" s="31"/>
-      <c r="AF63" s="31"/>
+      <c r="AC63" s="32"/>
+      <c r="AD63" s="32"/>
+      <c r="AE63" s="32"/>
+      <c r="AF63" s="32"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="28" t="s">
+      <c r="A64" s="29" t="s">
         <v>413</v>
       </c>
-      <c r="B64" s="29"/>
-      <c r="C64" s="29"/>
-      <c r="D64" s="29"/>
-      <c r="E64" s="29"/>
-      <c r="F64" s="29"/>
-      <c r="G64" s="29"/>
-      <c r="H64" s="29"/>
-      <c r="I64" s="29"/>
-      <c r="J64" s="29"/>
-      <c r="K64" s="29"/>
-      <c r="L64" s="29"/>
-      <c r="M64" s="29"/>
-      <c r="N64" s="29"/>
-      <c r="O64" s="29"/>
-      <c r="P64" s="29"/>
-      <c r="Q64" s="29"/>
-      <c r="R64" s="29"/>
-      <c r="S64" s="29"/>
-      <c r="T64" s="29"/>
-      <c r="U64" s="29"/>
-      <c r="V64" s="29"/>
-      <c r="W64" s="29"/>
-      <c r="X64" s="29"/>
-      <c r="Y64" s="29"/>
-      <c r="Z64" s="29"/>
-      <c r="AA64" s="29"/>
-      <c r="AB64" s="29"/>
-      <c r="AC64" s="29"/>
-      <c r="AD64" s="29"/>
-      <c r="AE64" s="29"/>
-      <c r="AF64" s="29"/>
+      <c r="B64" s="30"/>
+      <c r="C64" s="30"/>
+      <c r="D64" s="30"/>
+      <c r="E64" s="30"/>
+      <c r="F64" s="30"/>
+      <c r="G64" s="30"/>
+      <c r="H64" s="30"/>
+      <c r="I64" s="30"/>
+      <c r="J64" s="30"/>
+      <c r="K64" s="30"/>
+      <c r="L64" s="30"/>
+      <c r="M64" s="30"/>
+      <c r="N64" s="30"/>
+      <c r="O64" s="30"/>
+      <c r="P64" s="30"/>
+      <c r="Q64" s="30"/>
+      <c r="R64" s="30"/>
+      <c r="S64" s="30"/>
+      <c r="T64" s="30"/>
+      <c r="U64" s="30"/>
+      <c r="V64" s="30"/>
+      <c r="W64" s="30"/>
+      <c r="X64" s="30"/>
+      <c r="Y64" s="30"/>
+      <c r="Z64" s="30"/>
+      <c r="AA64" s="30"/>
+      <c r="AB64" s="30"/>
+      <c r="AC64" s="30"/>
+      <c r="AD64" s="30"/>
+      <c r="AE64" s="30"/>
+      <c r="AF64" s="30"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="30" t="s">
+      <c r="A65" s="31" t="s">
         <v>414</v>
       </c>
-      <c r="B65" s="33">
+      <c r="B65" s="34">
         <v>6.0</v>
       </c>
-      <c r="C65" s="33">
+      <c r="C65" s="34">
         <v>4.41</v>
       </c>
-      <c r="D65" s="33">
+      <c r="D65" s="34">
         <v>4.13</v>
       </c>
-      <c r="E65" s="33">
+      <c r="E65" s="34">
         <v>3.39</v>
       </c>
-      <c r="F65" s="33">
+      <c r="F65" s="34">
         <v>3.79</v>
       </c>
-      <c r="G65" s="33">
+      <c r="G65" s="34">
         <v>3.2</v>
       </c>
-      <c r="H65" s="33">
+      <c r="H65" s="34">
         <v>4.59</v>
       </c>
-      <c r="I65" s="33">
+      <c r="I65" s="34">
         <v>5.8</v>
       </c>
-      <c r="J65" s="33">
+      <c r="J65" s="34">
         <v>5.53</v>
       </c>
-      <c r="K65" s="33">
+      <c r="K65" s="34">
         <v>4.62</v>
       </c>
-      <c r="L65" s="33">
+      <c r="L65" s="34">
         <v>5.71</v>
       </c>
-      <c r="M65" s="33">
+      <c r="M65" s="34">
         <v>3.61</v>
       </c>
-      <c r="N65" s="33">
+      <c r="N65" s="34">
         <v>4.03</v>
       </c>
-      <c r="O65" s="33">
+      <c r="O65" s="34">
         <v>2.13</v>
       </c>
-      <c r="P65" s="33">
+      <c r="P65" s="34">
         <v>2.73</v>
       </c>
-      <c r="Q65" s="33">
+      <c r="Q65" s="34">
         <v>4.05</v>
       </c>
-      <c r="R65" s="33">
+      <c r="R65" s="34">
         <v>3.53</v>
       </c>
-      <c r="S65" s="33">
+      <c r="S65" s="34">
         <v>3.03</v>
       </c>
-      <c r="T65" s="33">
+      <c r="T65" s="34">
         <v>6.1</v>
       </c>
-      <c r="U65" s="33">
+      <c r="U65" s="34">
         <v>5.88</v>
       </c>
-      <c r="V65" s="33">
+      <c r="V65" s="34">
         <v>6.26</v>
       </c>
-      <c r="W65" s="33">
+      <c r="W65" s="34">
         <v>4.12</v>
       </c>
-      <c r="X65" s="33">
+      <c r="X65" s="34">
         <v>3.64</v>
       </c>
-      <c r="Y65" s="33">
+      <c r="Y65" s="34">
         <v>3.78</v>
       </c>
-      <c r="Z65" s="33">
+      <c r="Z65" s="34">
         <v>4.76</v>
       </c>
-      <c r="AA65" s="33">
+      <c r="AA65" s="34">
         <v>4.41</v>
       </c>
-      <c r="AB65" s="33">
+      <c r="AB65" s="34">
         <v>3.41</v>
       </c>
-      <c r="AC65" s="33">
+      <c r="AC65" s="34">
         <v>3.15</v>
       </c>
-      <c r="AD65" s="33">
+      <c r="AD65" s="34">
         <v>5.64</v>
       </c>
-      <c r="AE65" s="33">
+      <c r="AE65" s="34">
         <v>5.13</v>
       </c>
-      <c r="AF65" s="33">
+      <c r="AF65" s="34">
         <v>5.0</v>
       </c>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="30" t="s">
+      <c r="A66" s="31" t="s">
         <v>415</v>
       </c>
-      <c r="B66" s="33">
+      <c r="B66" s="34">
         <v>4.48</v>
       </c>
-      <c r="C66" s="33">
+      <c r="C66" s="34">
         <v>3.85</v>
       </c>
-      <c r="D66" s="33">
+      <c r="D66" s="34">
         <v>3.8</v>
       </c>
-      <c r="E66" s="33">
+      <c r="E66" s="34">
         <v>3.99</v>
       </c>
-      <c r="F66" s="33">
+      <c r="F66" s="34">
         <v>4.38</v>
       </c>
-      <c r="G66" s="33">
+      <c r="G66" s="34">
         <v>4.58</v>
       </c>
-      <c r="H66" s="33">
+      <c r="H66" s="34">
         <v>5.24</v>
       </c>
-      <c r="I66" s="33">
+      <c r="I66" s="34">
         <v>5.13</v>
       </c>
-      <c r="J66" s="33">
+      <c r="J66" s="34">
         <v>4.8</v>
       </c>
-      <c r="K66" s="33">
+      <c r="K66" s="34">
         <v>4.22</v>
       </c>
-      <c r="L66" s="33">
+      <c r="L66" s="34">
         <v>3.91</v>
       </c>
-      <c r="M66" s="33">
+      <c r="M66" s="34">
         <v>3.29</v>
       </c>
-      <c r="N66" s="33">
+      <c r="N66" s="34">
         <v>3.23</v>
       </c>
-      <c r="O66" s="33">
+      <c r="O66" s="34">
         <v>2.98</v>
       </c>
-      <c r="P66" s="33">
+      <c r="P66" s="34">
         <v>3.78</v>
       </c>
-      <c r="Q66" s="33">
+      <c r="Q66" s="34">
         <v>4.34</v>
       </c>
-      <c r="R66" s="33">
+      <c r="R66" s="34">
         <v>4.62</v>
       </c>
-      <c r="S66" s="33">
+      <c r="S66" s="34">
         <v>4.85</v>
       </c>
-      <c r="T66" s="33">
+      <c r="T66" s="34">
         <v>5.41</v>
       </c>
-      <c r="U66" s="33">
+      <c r="U66" s="34">
         <v>4.86</v>
       </c>
-      <c r="V66" s="33">
+      <c r="V66" s="34">
         <v>4.55</v>
       </c>
-      <c r="W66" s="33">
+      <c r="W66" s="34">
         <v>4.13</v>
       </c>
-      <c r="X66" s="33">
+      <c r="X66" s="34">
         <v>3.97</v>
       </c>
-      <c r="Y66" s="33">
+      <c r="Y66" s="34">
         <v>3.85</v>
       </c>
-      <c r="Z66" s="33">
+      <c r="Z66" s="34">
         <v>4.2</v>
       </c>
-      <c r="AA66" s="33">
+      <c r="AA66" s="34">
         <v>4.28</v>
       </c>
-      <c r="AB66" s="33">
+      <c r="AB66" s="34">
         <v>4.35</v>
       </c>
-      <c r="AC66" s="31"/>
-      <c r="AD66" s="31"/>
-      <c r="AE66" s="31"/>
-      <c r="AF66" s="31"/>
+      <c r="AC66" s="32"/>
+      <c r="AD66" s="32"/>
+      <c r="AE66" s="32"/>
+      <c r="AF66" s="32"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="28" t="s">
+      <c r="A67" s="29" t="s">
         <v>416</v>
       </c>
-      <c r="B67" s="29"/>
-      <c r="C67" s="29"/>
-      <c r="D67" s="29"/>
-      <c r="E67" s="29"/>
-      <c r="F67" s="29"/>
-      <c r="G67" s="29"/>
-      <c r="H67" s="29"/>
-      <c r="I67" s="29"/>
-      <c r="J67" s="29"/>
-      <c r="K67" s="29"/>
-      <c r="L67" s="29"/>
-      <c r="M67" s="29"/>
-      <c r="N67" s="29"/>
-      <c r="O67" s="29"/>
-      <c r="P67" s="29"/>
-      <c r="Q67" s="29"/>
-      <c r="R67" s="29"/>
-      <c r="S67" s="29"/>
-      <c r="T67" s="29"/>
-      <c r="U67" s="29"/>
-      <c r="V67" s="29"/>
-      <c r="W67" s="29"/>
-      <c r="X67" s="29"/>
-      <c r="Y67" s="29"/>
-      <c r="Z67" s="29"/>
-      <c r="AA67" s="29"/>
-      <c r="AB67" s="29"/>
-      <c r="AC67" s="29"/>
-      <c r="AD67" s="29"/>
-      <c r="AE67" s="29"/>
-      <c r="AF67" s="29"/>
+      <c r="B67" s="30"/>
+      <c r="C67" s="30"/>
+      <c r="D67" s="30"/>
+      <c r="E67" s="30"/>
+      <c r="F67" s="30"/>
+      <c r="G67" s="30"/>
+      <c r="H67" s="30"/>
+      <c r="I67" s="30"/>
+      <c r="J67" s="30"/>
+      <c r="K67" s="30"/>
+      <c r="L67" s="30"/>
+      <c r="M67" s="30"/>
+      <c r="N67" s="30"/>
+      <c r="O67" s="30"/>
+      <c r="P67" s="30"/>
+      <c r="Q67" s="30"/>
+      <c r="R67" s="30"/>
+      <c r="S67" s="30"/>
+      <c r="T67" s="30"/>
+      <c r="U67" s="30"/>
+      <c r="V67" s="30"/>
+      <c r="W67" s="30"/>
+      <c r="X67" s="30"/>
+      <c r="Y67" s="30"/>
+      <c r="Z67" s="30"/>
+      <c r="AA67" s="30"/>
+      <c r="AB67" s="30"/>
+      <c r="AC67" s="30"/>
+      <c r="AD67" s="30"/>
+      <c r="AE67" s="30"/>
+      <c r="AF67" s="30"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="30" t="s">
+      <c r="A68" s="31" t="s">
         <v>417</v>
       </c>
-      <c r="B68" s="33">
+      <c r="B68" s="34">
         <v>4.5</v>
       </c>
-      <c r="C68" s="33">
+      <c r="C68" s="34">
         <v>4.22</v>
       </c>
-      <c r="D68" s="33">
+      <c r="D68" s="34">
         <v>6.9</v>
       </c>
-      <c r="E68" s="33">
+      <c r="E68" s="34">
         <v>8.1</v>
       </c>
-      <c r="F68" s="33">
+      <c r="F68" s="34">
         <v>9.85</v>
       </c>
-      <c r="G68" s="33">
+      <c r="G68" s="34">
         <v>2.61</v>
       </c>
-      <c r="H68" s="33">
+      <c r="H68" s="34">
         <v>4.55</v>
       </c>
-      <c r="I68" s="33">
+      <c r="I68" s="34">
         <v>6.57</v>
       </c>
-      <c r="J68" s="33">
+      <c r="J68" s="34">
         <v>8.2</v>
       </c>
-      <c r="K68" s="33">
+      <c r="K68" s="34">
         <v>8.18</v>
       </c>
-      <c r="L68" s="33">
+      <c r="L68" s="34">
         <v>3.99</v>
       </c>
-      <c r="M68" s="33">
+      <c r="M68" s="34">
         <v>3.7</v>
       </c>
-      <c r="N68" s="33">
+      <c r="N68" s="34">
         <v>48.06</v>
       </c>
-      <c r="O68" s="33">
+      <c r="O68" s="34">
         <v>2.65</v>
       </c>
-      <c r="P68" s="33">
+      <c r="P68" s="34">
         <v>3.12</v>
       </c>
-      <c r="Q68" s="33">
+      <c r="Q68" s="34">
         <v>4.28</v>
       </c>
-      <c r="R68" s="33">
+      <c r="R68" s="34">
         <v>2.85</v>
       </c>
-      <c r="S68" s="33">
+      <c r="S68" s="34">
         <v>3.41</v>
       </c>
-      <c r="T68" s="33">
+      <c r="T68" s="34">
         <v>8.28</v>
       </c>
-      <c r="U68" s="33">
+      <c r="U68" s="34">
         <v>12.43</v>
       </c>
-      <c r="V68" s="33">
+      <c r="V68" s="34">
         <v>7.82</v>
       </c>
-      <c r="W68" s="33">
+      <c r="W68" s="34">
         <v>5.84</v>
       </c>
-      <c r="X68" s="33">
+      <c r="X68" s="34">
         <v>3.47</v>
       </c>
-      <c r="Y68" s="33">
+      <c r="Y68" s="34">
         <v>3.57</v>
       </c>
-      <c r="Z68" s="31"/>
-      <c r="AA68" s="33">
+      <c r="Z68" s="32"/>
+      <c r="AA68" s="34">
         <v>4.13</v>
       </c>
-      <c r="AB68" s="33">
+      <c r="AB68" s="34">
         <v>4.45</v>
       </c>
-      <c r="AC68" s="33">
+      <c r="AC68" s="34">
         <v>4.39</v>
       </c>
-      <c r="AD68" s="33">
+      <c r="AD68" s="34">
         <v>9.89</v>
       </c>
-      <c r="AE68" s="33">
+      <c r="AE68" s="34">
         <v>7.36</v>
       </c>
-      <c r="AF68" s="33">
+      <c r="AF68" s="34">
         <v>6.31</v>
       </c>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="30" t="s">
+      <c r="A69" s="31" t="s">
         <v>418</v>
       </c>
-      <c r="B69" s="33">
+      <c r="B69" s="34">
         <v>5.47</v>
       </c>
-      <c r="C69" s="33">
+      <c r="C69" s="34">
         <v>5.14</v>
       </c>
-      <c r="D69" s="33">
+      <c r="D69" s="34">
         <v>5.41</v>
       </c>
-      <c r="E69" s="33">
+      <c r="E69" s="34">
         <v>5.24</v>
       </c>
-      <c r="F69" s="33">
+      <c r="F69" s="34">
         <v>5.19</v>
       </c>
-      <c r="G69" s="33">
+      <c r="G69" s="34">
         <v>4.97</v>
       </c>
-      <c r="H69" s="33">
+      <c r="H69" s="34">
         <v>5.68</v>
       </c>
-      <c r="I69" s="33">
+      <c r="I69" s="34">
         <v>5.64</v>
       </c>
-      <c r="J69" s="33">
+      <c r="J69" s="34">
         <v>6.02</v>
       </c>
-      <c r="K69" s="33">
+      <c r="K69" s="34">
         <v>5.11</v>
       </c>
-      <c r="L69" s="33">
+      <c r="L69" s="34">
         <v>4.33</v>
       </c>
-      <c r="M69" s="33">
+      <c r="M69" s="34">
         <v>4.56</v>
       </c>
-      <c r="N69" s="33">
+      <c r="N69" s="34">
         <v>4.37</v>
       </c>
-      <c r="O69" s="33">
+      <c r="O69" s="34">
         <v>3.16</v>
       </c>
-      <c r="P69" s="33">
+      <c r="P69" s="34">
         <v>4.02</v>
       </c>
-      <c r="Q69" s="33">
+      <c r="Q69" s="34">
         <v>4.91</v>
       </c>
-      <c r="R69" s="33">
+      <c r="R69" s="34">
         <v>5.35</v>
       </c>
-      <c r="S69" s="33">
+      <c r="S69" s="34">
         <v>6.54</v>
       </c>
-      <c r="T69" s="33">
+      <c r="T69" s="34">
         <v>7.44</v>
       </c>
-      <c r="U69" s="33">
+      <c r="U69" s="34">
         <v>6.18</v>
       </c>
-      <c r="V69" s="33">
+      <c r="V69" s="34">
         <v>7.16</v>
       </c>
-      <c r="W69" s="33">
+      <c r="W69" s="34">
         <v>6.0</v>
       </c>
-      <c r="X69" s="33">
+      <c r="X69" s="34">
         <v>5.65</v>
       </c>
-      <c r="Y69" s="33">
+      <c r="Y69" s="34">
         <v>5.96</v>
       </c>
-      <c r="Z69" s="33">
+      <c r="Z69" s="34">
         <v>7.73</v>
       </c>
-      <c r="AA69" s="33">
+      <c r="AA69" s="34">
         <v>5.57</v>
       </c>
-      <c r="AB69" s="33">
+      <c r="AB69" s="34">
         <v>6.15</v>
       </c>
-      <c r="AC69" s="31"/>
-      <c r="AD69" s="31"/>
-      <c r="AE69" s="31"/>
-      <c r="AF69" s="31"/>
+      <c r="AC69" s="32"/>
+      <c r="AD69" s="32"/>
+      <c r="AE69" s="32"/>
+      <c r="AF69" s="32"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="28" t="s">
+      <c r="A70" s="29" t="s">
         <v>419</v>
       </c>
-      <c r="B70" s="29"/>
-      <c r="C70" s="29"/>
-      <c r="D70" s="29"/>
-      <c r="E70" s="29"/>
-      <c r="F70" s="29"/>
-      <c r="G70" s="29"/>
-      <c r="H70" s="29"/>
-      <c r="I70" s="29"/>
-      <c r="J70" s="29"/>
-      <c r="K70" s="29"/>
-      <c r="L70" s="29"/>
-      <c r="M70" s="29"/>
-      <c r="N70" s="29"/>
-      <c r="O70" s="29"/>
-      <c r="P70" s="29"/>
-      <c r="Q70" s="29"/>
-      <c r="R70" s="29"/>
-      <c r="S70" s="29"/>
-      <c r="T70" s="29"/>
-      <c r="U70" s="29"/>
-      <c r="V70" s="29"/>
-      <c r="W70" s="29"/>
-      <c r="X70" s="29"/>
-      <c r="Y70" s="29"/>
-      <c r="Z70" s="29"/>
-      <c r="AA70" s="29"/>
-      <c r="AB70" s="29"/>
-      <c r="AC70" s="29"/>
-      <c r="AD70" s="29"/>
-      <c r="AE70" s="29"/>
-      <c r="AF70" s="29"/>
+      <c r="B70" s="30"/>
+      <c r="C70" s="30"/>
+      <c r="D70" s="30"/>
+      <c r="E70" s="30"/>
+      <c r="F70" s="30"/>
+      <c r="G70" s="30"/>
+      <c r="H70" s="30"/>
+      <c r="I70" s="30"/>
+      <c r="J70" s="30"/>
+      <c r="K70" s="30"/>
+      <c r="L70" s="30"/>
+      <c r="M70" s="30"/>
+      <c r="N70" s="30"/>
+      <c r="O70" s="30"/>
+      <c r="P70" s="30"/>
+      <c r="Q70" s="30"/>
+      <c r="R70" s="30"/>
+      <c r="S70" s="30"/>
+      <c r="T70" s="30"/>
+      <c r="U70" s="30"/>
+      <c r="V70" s="30"/>
+      <c r="W70" s="30"/>
+      <c r="X70" s="30"/>
+      <c r="Y70" s="30"/>
+      <c r="Z70" s="30"/>
+      <c r="AA70" s="30"/>
+      <c r="AB70" s="30"/>
+      <c r="AC70" s="30"/>
+      <c r="AD70" s="30"/>
+      <c r="AE70" s="30"/>
+      <c r="AF70" s="30"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="30" t="s">
+      <c r="A71" s="31" t="s">
         <v>420</v>
       </c>
-      <c r="B71" s="33">
+      <c r="B71" s="34">
         <v>6.64</v>
       </c>
-      <c r="C71" s="33">
+      <c r="C71" s="34">
         <v>7.37</v>
       </c>
-      <c r="D71" s="33">
+      <c r="D71" s="34">
         <v>41.13</v>
       </c>
-      <c r="E71" s="31"/>
-      <c r="F71" s="31"/>
-      <c r="G71" s="33">
+      <c r="E71" s="32"/>
+      <c r="F71" s="32"/>
+      <c r="G71" s="34">
         <v>3.92</v>
       </c>
-      <c r="H71" s="33">
+      <c r="H71" s="34">
         <v>9.17</v>
       </c>
-      <c r="I71" s="33">
+      <c r="I71" s="34">
         <v>17.36</v>
       </c>
-      <c r="J71" s="31"/>
-      <c r="K71" s="31"/>
-      <c r="L71" s="33">
+      <c r="J71" s="32"/>
+      <c r="K71" s="32"/>
+      <c r="L71" s="34">
         <v>6.35</v>
       </c>
-      <c r="M71" s="33">
+      <c r="M71" s="34">
         <v>7.31</v>
       </c>
-      <c r="N71" s="31"/>
-      <c r="O71" s="33">
+      <c r="N71" s="32"/>
+      <c r="O71" s="34">
         <v>16.25</v>
       </c>
-      <c r="P71" s="33">
+      <c r="P71" s="34">
         <v>30.57</v>
       </c>
-      <c r="Q71" s="31"/>
-      <c r="R71" s="33">
+      <c r="Q71" s="32"/>
+      <c r="R71" s="34">
         <v>10.07</v>
       </c>
-      <c r="S71" s="33">
+      <c r="S71" s="34">
         <v>58.06</v>
       </c>
-      <c r="T71" s="33">
+      <c r="T71" s="34">
         <v>8.28</v>
       </c>
-      <c r="U71" s="31"/>
-      <c r="V71" s="31"/>
-      <c r="W71" s="31"/>
-      <c r="X71" s="33">
+      <c r="U71" s="32"/>
+      <c r="V71" s="32"/>
+      <c r="W71" s="32"/>
+      <c r="X71" s="34">
         <v>5.12</v>
       </c>
-      <c r="Y71" s="33">
+      <c r="Y71" s="34">
         <v>10.66</v>
       </c>
-      <c r="Z71" s="31"/>
-      <c r="AA71" s="33">
+      <c r="Z71" s="32"/>
+      <c r="AA71" s="34">
         <v>38.97</v>
       </c>
-      <c r="AB71" s="33">
+      <c r="AB71" s="34">
         <v>38.02</v>
       </c>
-      <c r="AC71" s="32">
+      <c r="AC71" s="33">
         <v>553.01</v>
       </c>
-      <c r="AD71" s="31"/>
-      <c r="AE71" s="33">
+      <c r="AD71" s="32"/>
+      <c r="AE71" s="34">
         <v>49.33</v>
       </c>
-      <c r="AF71" s="31"/>
+      <c r="AF71" s="32"/>
     </row>
     <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="30" t="s">
+      <c r="A72" s="31" t="s">
         <v>421</v>
       </c>
-      <c r="B72" s="33">
+      <c r="B72" s="34">
         <v>14.45</v>
       </c>
-      <c r="C72" s="33">
+      <c r="C72" s="34">
         <v>16.45</v>
       </c>
-      <c r="D72" s="33">
+      <c r="D72" s="34">
         <v>22.59</v>
       </c>
-      <c r="E72" s="33">
+      <c r="E72" s="34">
         <v>18.55</v>
       </c>
-      <c r="F72" s="33">
+      <c r="F72" s="34">
         <v>14.98</v>
       </c>
-      <c r="G72" s="33">
+      <c r="G72" s="34">
         <v>13.81</v>
       </c>
-      <c r="H72" s="33">
+      <c r="H72" s="34">
         <v>18.32</v>
       </c>
-      <c r="I72" s="33">
+      <c r="I72" s="34">
         <v>19.17</v>
       </c>
-      <c r="J72" s="33">
+      <c r="J72" s="34">
         <v>36.81</v>
       </c>
-      <c r="K72" s="33">
+      <c r="K72" s="34">
         <v>23.16</v>
       </c>
-      <c r="L72" s="33">
+      <c r="L72" s="34">
         <v>12.83</v>
       </c>
-      <c r="M72" s="32">
+      <c r="M72" s="33">
         <v>113.02</v>
       </c>
-      <c r="N72" s="31"/>
-      <c r="O72" s="33">
+      <c r="N72" s="32"/>
+      <c r="O72" s="34">
         <v>31.02</v>
       </c>
-      <c r="P72" s="33">
+      <c r="P72" s="34">
         <v>18.42</v>
       </c>
-      <c r="Q72" s="33">
+      <c r="Q72" s="34">
         <v>36.07</v>
       </c>
-      <c r="R72" s="33">
+      <c r="R72" s="34">
         <v>34.52</v>
       </c>
-      <c r="S72" s="32">
+      <c r="S72" s="33">
         <v>103.9</v>
       </c>
-      <c r="T72" s="33">
+      <c r="T72" s="34">
         <v>39.51</v>
       </c>
-      <c r="U72" s="31"/>
-      <c r="V72" s="31"/>
-      <c r="W72" s="31"/>
-      <c r="X72" s="31"/>
-      <c r="Y72" s="31"/>
-      <c r="Z72" s="31"/>
-      <c r="AA72" s="32">
+      <c r="U72" s="32"/>
+      <c r="V72" s="32"/>
+      <c r="W72" s="32"/>
+      <c r="X72" s="32"/>
+      <c r="Y72" s="32"/>
+      <c r="Z72" s="32"/>
+      <c r="AA72" s="33">
         <v>184.59</v>
       </c>
-      <c r="AB72" s="31"/>
-      <c r="AC72" s="31"/>
-      <c r="AD72" s="31"/>
-      <c r="AE72" s="31"/>
-      <c r="AF72" s="31"/>
+      <c r="AB72" s="32"/>
+      <c r="AC72" s="32"/>
+      <c r="AD72" s="32"/>
+      <c r="AE72" s="32"/>
+      <c r="AF72" s="32"/>
     </row>
     <row r="73" ht="15.75" customHeight="1"/>
     <row r="74" ht="15.75" customHeight="1"/>

--- a/data/cox_xlsx/PAALb.CO.xlsx
+++ b/data/cox_xlsx/PAALb.CO.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="424">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -792,10 +792,16 @@
     <t>Current liabilities</t>
   </si>
   <si>
+    <t>Mortgage debt and credit institutions LT</t>
+  </si>
+  <si>
     <t>Provisions</t>
   </si>
   <si>
     <t>Other payables</t>
+  </si>
+  <si>
+    <t>Credit institutions LT</t>
   </si>
   <si>
     <t>Company Tax</t>
@@ -1416,7 +1422,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1497,6 +1503,9 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="7" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="9" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -13541,8 +13550,8 @@
       </c>
     </row>
     <row r="90" ht="15.0" customHeight="1">
-      <c r="A90" s="14" t="s">
-        <v>247</v>
+      <c r="A90" s="27" t="s">
+        <v>257</v>
       </c>
       <c r="B90" s="16">
         <v>113.0</v>
@@ -13610,7 +13619,7 @@
     </row>
     <row r="91" ht="15.0" customHeight="1">
       <c r="A91" s="14" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B91" s="16">
         <v>434.74</v>
@@ -13678,7 +13687,7 @@
     </row>
     <row r="92" ht="15.0" customHeight="1">
       <c r="A92" s="14" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B92" s="21">
         <v>83.18</v>
@@ -13803,8 +13812,8 @@
       </c>
     </row>
     <row r="94" ht="15.0" customHeight="1">
-      <c r="A94" s="14" t="s">
-        <v>248</v>
+      <c r="A94" s="27" t="s">
+        <v>260</v>
       </c>
       <c r="B94" s="16">
         <v>973.05</v>
@@ -13872,7 +13881,7 @@
     </row>
     <row r="95" ht="15.0" customHeight="1">
       <c r="A95" s="14" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B95" s="15"/>
       <c r="C95" s="15"/>
@@ -13940,7 +13949,7 @@
     </row>
     <row r="97" ht="15.0" customHeight="1">
       <c r="A97" s="17" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B97" s="19">
         <v>3575.19</v>
@@ -14008,7 +14017,7 @@
     </row>
     <row r="98" ht="15.0" customHeight="1">
       <c r="A98" s="17" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B98" s="18">
         <v>16042.85</v>
@@ -14076,7 +14085,7 @@
     </row>
     <row r="99" ht="15.0" customHeight="1">
       <c r="A99" s="14" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B99" s="21">
         <v>61.21</v>
@@ -14136,7 +14145,7 @@
     </row>
     <row r="100" ht="15.0" customHeight="1">
       <c r="A100" s="14" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B100" s="15"/>
       <c r="C100" s="15"/>
@@ -14172,7 +14181,7 @@
     </row>
     <row r="101" ht="15.0" customHeight="1">
       <c r="A101" s="14" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B101" s="15"/>
       <c r="C101" s="15"/>
@@ -14208,7 +14217,7 @@
     </row>
     <row r="102" ht="15.0" customHeight="1">
       <c r="A102" s="14" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B102" s="23">
         <v>-178.92</v>
@@ -14276,7 +14285,7 @@
     </row>
     <row r="103" ht="15.0" customHeight="1">
       <c r="A103" s="14" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B103" s="21">
         <v>39.24</v>
@@ -14344,7 +14353,7 @@
     </row>
     <row r="104" ht="15.0" customHeight="1">
       <c r="A104" s="14" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B104" s="16">
         <v>8351.01</v>
@@ -14408,7 +14417,7 @@
     </row>
     <row r="105" ht="15.0" customHeight="1">
       <c r="A105" s="14" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B105" s="16">
         <v>368.82</v>
@@ -14476,7 +14485,7 @@
     </row>
     <row r="106" ht="15.0" customHeight="1">
       <c r="A106" s="14" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B106" s="15"/>
       <c r="C106" s="15"/>
@@ -14506,7 +14515,7 @@
     </row>
     <row r="107" ht="15.0" customHeight="1">
       <c r="A107" s="17" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B107" s="19">
         <v>8641.36</v>
@@ -14574,7 +14583,7 @@
     </row>
     <row r="108" ht="15.0" customHeight="1">
       <c r="A108" s="14" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B108" s="21">
         <v>81.61</v>
@@ -14636,7 +14645,7 @@
     </row>
     <row r="109" ht="15.0" customHeight="1">
       <c r="A109" s="17" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B109" s="24">
         <v>81.61</v>
@@ -14694,7 +14703,7 @@
     </row>
     <row r="110" ht="15.0" customHeight="1">
       <c r="A110" s="17" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B110" s="19">
         <v>8722.97</v>
@@ -14762,7 +14771,7 @@
     </row>
     <row r="111" ht="15.0" customHeight="1">
       <c r="A111" s="17" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B111" s="18">
         <v>24765.82</v>
@@ -14830,7 +14839,7 @@
     </row>
     <row r="112" ht="15.0" customHeight="1">
       <c r="A112" s="14" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B112" s="21">
         <v>18.79</v>
@@ -14898,7 +14907,7 @@
     </row>
     <row r="113" ht="15.0" customHeight="1">
       <c r="A113" s="14" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B113" s="21">
         <v>19.58</v>
@@ -14966,7 +14975,7 @@
     </row>
     <row r="114" ht="15.0" customHeight="1">
       <c r="A114" s="14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B114" s="21">
         <v>0.79</v>
@@ -15034,7 +15043,7 @@
     </row>
     <row r="115" ht="15.0" customHeight="1">
       <c r="A115" s="14" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B115" s="16">
         <v>2917.6</v>
@@ -15092,7 +15101,7 @@
     </row>
     <row r="116" ht="15.0" customHeight="1">
       <c r="A116" s="14" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B116" s="15"/>
       <c r="C116" s="15"/>
@@ -15120,7 +15129,7 @@
     </row>
     <row r="117" ht="15.0" customHeight="1">
       <c r="A117" s="14" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B117" s="15"/>
       <c r="C117" s="15"/>
@@ -15152,7 +15161,7 @@
     </row>
     <row r="118" ht="15.0" customHeight="1">
       <c r="A118" s="14" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B118" s="15"/>
       <c r="C118" s="15"/>
@@ -15186,7 +15195,7 @@
     </row>
     <row r="119" ht="15.0" customHeight="1">
       <c r="A119" s="14" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B119" s="16">
         <v>182.06</v>
@@ -15248,7 +15257,7 @@
     </row>
     <row r="120" ht="15.0" customHeight="1">
       <c r="A120" s="14" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B120" s="21">
         <v>15.69</v>
@@ -15314,7 +15323,7 @@
     </row>
     <row r="121" ht="15.0" customHeight="1">
       <c r="A121" s="14" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B121" s="16">
         <v>1006.01</v>
@@ -15380,7 +15389,7 @@
     </row>
     <row r="122" ht="15.0" customHeight="1">
       <c r="A122" s="14" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B122" s="21">
         <v>76.9</v>
@@ -15446,7 +15455,7 @@
     </row>
     <row r="123" ht="15.0" customHeight="1">
       <c r="A123" s="14" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B123" s="16">
         <v>1401.51</v>
@@ -15480,7 +15489,7 @@
     </row>
     <row r="124" ht="15.0" customHeight="1">
       <c r="A124" s="14" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B124" s="16">
         <v>387.65</v>
@@ -15514,7 +15523,7 @@
     </row>
     <row r="125" ht="15.0" customHeight="1">
       <c r="A125" s="14" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B125" s="16">
         <v>792.57</v>
@@ -15548,7 +15557,7 @@
     </row>
     <row r="126" ht="15.0" customHeight="1">
       <c r="A126" s="14" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B126" s="16">
         <v>221.29</v>
@@ -15582,7 +15591,7 @@
     </row>
     <row r="127" ht="15.0" customHeight="1">
       <c r="A127" s="14" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B127" s="21">
         <v>17.44</v>
@@ -15650,7 +15659,7 @@
     </row>
     <row r="128" ht="15.0" customHeight="1">
       <c r="A128" s="14" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B128" s="21">
         <v>0.79</v>
@@ -15718,7 +15727,7 @@
     </row>
     <row r="129" ht="15.0" customHeight="1">
       <c r="A129" s="14" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B129" s="21">
         <v>0.93</v>
@@ -15786,7 +15795,7 @@
     </row>
     <row r="130" ht="15.0" customHeight="1">
       <c r="A130" s="14" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B130" s="21">
         <v>18.23</v>
@@ -15854,7 +15863,7 @@
     </row>
     <row r="131" ht="15.0" customHeight="1">
       <c r="A131" s="14" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B131" s="21">
         <v>0.03</v>
@@ -15922,7 +15931,7 @@
     </row>
     <row r="132" ht="15.0" customHeight="1">
       <c r="A132" s="14" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B132" s="21">
         <v>0.03</v>
@@ -15990,7 +15999,7 @@
     </row>
     <row r="133" ht="15.0" customHeight="1">
       <c r="A133" s="14" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B133" s="21">
         <v>0.07</v>
@@ -16944,7 +16953,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -17317,67 +17326,67 @@
         <v>43</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -17450,7 +17459,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -17612,7 +17621,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B21" s="16">
         <v>1432.95</v>
@@ -17650,7 +17659,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B22" s="23">
         <v>-186.77</v>
@@ -17714,7 +17723,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
@@ -17776,7 +17785,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B24" s="23">
         <v>-138.12</v>
@@ -17828,7 +17837,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B25" s="22">
         <v>-48.65</v>
@@ -17864,7 +17873,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B26" s="15"/>
       <c r="C26" s="15"/>
@@ -17920,7 +17929,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B27" s="16">
         <v>1626.0</v>
@@ -18038,7 +18047,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B29" s="16">
         <v>659.19</v>
@@ -18170,7 +18179,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B31" s="16">
         <v>580.71</v>
@@ -18236,7 +18245,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B32" s="15"/>
       <c r="C32" s="15"/>
@@ -18264,7 +18273,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B33" s="16">
         <v>117.71</v>
@@ -18330,7 +18339,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B34" s="22">
         <v>-81.61</v>
@@ -18396,7 +18405,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B35" s="23">
         <v>-379.82</v>
@@ -18464,7 +18473,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B36" s="15"/>
       <c r="C36" s="15"/>
@@ -18520,7 +18529,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B37" s="15"/>
       <c r="C37" s="15"/>
@@ -18550,7 +18559,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B38" s="15"/>
       <c r="C38" s="15"/>
@@ -18582,7 +18591,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B39" s="15"/>
       <c r="C39" s="15">
@@ -18616,7 +18625,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="17" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B40" s="19">
         <v>4375.76</v>
@@ -18684,7 +18693,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B41" s="23">
         <v>-331.16</v>
@@ -18752,7 +18761,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B42" s="21">
         <v>4.71</v>
@@ -18780,7 +18789,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B43" s="23">
         <v>-1332.5</v>
@@ -18832,7 +18841,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B44" s="16">
         <v>120.85</v>
@@ -18898,7 +18907,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B45" s="15"/>
       <c r="C45" s="15"/>
@@ -18944,7 +18953,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="14" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B46" s="23">
         <v>-249.55</v>
@@ -18984,7 +18993,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B47" s="22">
         <v>-76.91</v>
@@ -19050,7 +19059,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B48" s="16">
         <v>273.09</v>
@@ -19118,7 +19127,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B50" s="15"/>
       <c r="C50" s="15"/>
@@ -19158,7 +19167,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B51" s="15"/>
       <c r="C51" s="15"/>
@@ -19198,7 +19207,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B52" s="15"/>
       <c r="C52" s="15"/>
@@ -19236,7 +19245,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B53" s="15"/>
       <c r="C53" s="15"/>
@@ -19276,7 +19285,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B54" s="15"/>
       <c r="C54" s="15"/>
@@ -19308,7 +19317,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B55" s="15"/>
       <c r="C55" s="15"/>
@@ -19344,7 +19353,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B56" s="15"/>
       <c r="C56" s="15"/>
@@ -19376,7 +19385,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B57" s="15"/>
       <c r="C57" s="15"/>
@@ -19406,7 +19415,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B58" s="15"/>
       <c r="C58" s="15"/>
@@ -19434,75 +19443,75 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="17" t="s">
-        <v>332</v>
-      </c>
-      <c r="B59" s="27">
+        <v>334</v>
+      </c>
+      <c r="B59" s="28">
         <v>-1591.47</v>
       </c>
-      <c r="C59" s="27">
+      <c r="C59" s="28">
         <v>-1233.77</v>
       </c>
-      <c r="D59" s="27">
+      <c r="D59" s="28">
         <v>-1228.35</v>
       </c>
-      <c r="E59" s="27">
+      <c r="E59" s="28">
         <v>-1555.44</v>
       </c>
-      <c r="F59" s="27">
+      <c r="F59" s="28">
         <v>-941.56</v>
       </c>
-      <c r="G59" s="27">
+      <c r="G59" s="28">
         <v>-946.34</v>
       </c>
-      <c r="H59" s="27">
+      <c r="H59" s="28">
         <v>-868.22</v>
       </c>
-      <c r="I59" s="27">
+      <c r="I59" s="28">
         <v>-506.14</v>
       </c>
-      <c r="J59" s="27">
+      <c r="J59" s="28">
         <v>-604.81</v>
       </c>
-      <c r="K59" s="27">
+      <c r="K59" s="28">
         <v>-963.73</v>
       </c>
-      <c r="L59" s="27">
+      <c r="L59" s="28">
         <v>-735.53</v>
       </c>
-      <c r="M59" s="27">
+      <c r="M59" s="28">
         <v>-282.58</v>
       </c>
-      <c r="N59" s="27">
+      <c r="N59" s="28">
         <v>-376.77</v>
       </c>
-      <c r="O59" s="27">
+      <c r="O59" s="28">
         <v>-287.89</v>
       </c>
-      <c r="P59" s="27">
+      <c r="P59" s="28">
         <v>-452.55</v>
       </c>
-      <c r="Q59" s="27">
+      <c r="Q59" s="28">
         <v>-235.46</v>
       </c>
-      <c r="R59" s="27">
+      <c r="R59" s="28">
         <v>-323.05</v>
       </c>
-      <c r="S59" s="27">
+      <c r="S59" s="28">
         <v>-338.1</v>
       </c>
-      <c r="T59" s="27">
+      <c r="T59" s="28">
         <v>-186.9</v>
       </c>
-      <c r="U59" s="27">
+      <c r="U59" s="28">
         <v>-300.73</v>
       </c>
-      <c r="V59" s="27">
+      <c r="V59" s="28">
         <v>-139.27</v>
       </c>
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B60" s="15"/>
       <c r="C60" s="15"/>
@@ -19540,7 +19549,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B61" s="22">
         <v>-10.99</v>
@@ -19602,7 +19611,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B62" s="23">
         <v>-326.46</v>
@@ -19668,7 +19677,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="14" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B63" s="23">
         <v>-447.31</v>
@@ -19706,7 +19715,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B64" s="15"/>
       <c r="C64" s="15"/>
@@ -19736,7 +19745,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B65" s="15"/>
       <c r="C65" s="15"/>
@@ -19766,7 +19775,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="14" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B66" s="15"/>
       <c r="C66" s="15"/>
@@ -19796,7 +19805,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B67" s="22">
         <v>-53.36</v>
@@ -19824,7 +19833,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B68" s="15"/>
       <c r="C68" s="15"/>
@@ -19854,7 +19863,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="14" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B69" s="23">
         <v>-265.24</v>
@@ -19900,7 +19909,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="14" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B70" s="23">
         <v>-357.85</v>
@@ -19936,12 +19945,12 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="17" t="s">
-        <v>342</v>
-      </c>
-      <c r="B71" s="27">
+        <v>344</v>
+      </c>
+      <c r="B71" s="28">
         <v>-1461.2</v>
       </c>
-      <c r="C71" s="27">
+      <c r="C71" s="28">
         <v>-2138.11</v>
       </c>
       <c r="D71" s="25">
@@ -19950,25 +19959,25 @@
       <c r="E71" s="19">
         <v>705.19</v>
       </c>
-      <c r="F71" s="27">
+      <c r="F71" s="28">
         <v>-601.7</v>
       </c>
-      <c r="G71" s="27">
+      <c r="G71" s="28">
         <v>-448.57</v>
       </c>
-      <c r="H71" s="27">
+      <c r="H71" s="28">
         <v>-305.67</v>
       </c>
-      <c r="I71" s="27">
+      <c r="I71" s="28">
         <v>-154.65</v>
       </c>
-      <c r="J71" s="27">
+      <c r="J71" s="28">
         <v>-118.92</v>
       </c>
       <c r="K71" s="25">
         <v>-96.69</v>
       </c>
-      <c r="L71" s="27">
+      <c r="L71" s="28">
         <v>-107.14</v>
       </c>
       <c r="M71" s="25">
@@ -20004,7 +20013,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B72" s="16">
         <v>607.37</v>
@@ -20072,7 +20081,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="14" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B73" s="21">
         <v>12.56</v>
@@ -20124,7 +20133,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="14" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B74" s="16">
         <v>1942.97</v>
@@ -20192,7 +20201,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="14" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B75" s="15"/>
       <c r="C75" s="15"/>
@@ -20220,21 +20229,21 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="17" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B76" s="19">
         <v>1335.64</v>
       </c>
-      <c r="C76" s="27">
+      <c r="C76" s="28">
         <v>-298.34</v>
       </c>
       <c r="D76" s="19">
         <v>387.59</v>
       </c>
-      <c r="E76" s="27">
+      <c r="E76" s="28">
         <v>-169.25</v>
       </c>
-      <c r="F76" s="27">
+      <c r="F76" s="28">
         <v>-881.66</v>
       </c>
       <c r="G76" s="19">
@@ -20246,10 +20255,10 @@
       <c r="I76" s="19">
         <v>323.04</v>
       </c>
-      <c r="J76" s="27">
+      <c r="J76" s="28">
         <v>-118.04</v>
       </c>
-      <c r="K76" s="27">
+      <c r="K76" s="28">
         <v>-540.88</v>
       </c>
       <c r="L76" s="19">
@@ -20258,7 +20267,7 @@
       <c r="M76" s="19">
         <v>359.62</v>
       </c>
-      <c r="N76" s="27">
+      <c r="N76" s="28">
         <v>-358.51</v>
       </c>
       <c r="O76" s="24">
@@ -20288,7 +20297,7 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="14" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B77" s="15"/>
       <c r="C77" s="15"/>
@@ -20309,7 +20318,7 @@
       <c r="R77" s="15"/>
       <c r="S77" s="15"/>
       <c r="T77" s="15"/>
-      <c r="U77" s="28">
+      <c r="U77" s="29">
         <v>0.0</v>
       </c>
       <c r="V77" s="15"/>
@@ -21258,7 +21267,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -21432,34 +21441,34 @@
         <v>38</v>
       </c>
       <c r="W11" s="7" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="X11" s="7" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Y11" s="7" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Z11" s="7" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AA11" s="7" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AB11" s="7" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AC11" s="7" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AD11" s="7" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AE11" s="7" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AF11" s="7" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1" outlineLevel="1">
@@ -21954,7 +21963,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -22056,3933 +22065,3933 @@
         <v>69</v>
       </c>
       <c r="W19" s="13" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="X19" s="13" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Y19" s="13" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Z19" s="13" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AA19" s="13" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AB19" s="13" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AC19" s="13" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AD19" s="13" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AE19" s="13" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AF19" s="13" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="29" t="s">
-        <v>371</v>
-      </c>
-      <c r="B20" s="30"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="30"/>
-      <c r="I20" s="30"/>
-      <c r="J20" s="30"/>
-      <c r="K20" s="30"/>
-      <c r="L20" s="30"/>
-      <c r="M20" s="30"/>
-      <c r="N20" s="30"/>
-      <c r="O20" s="30"/>
-      <c r="P20" s="30"/>
-      <c r="Q20" s="30"/>
-      <c r="R20" s="30"/>
-      <c r="S20" s="30"/>
-      <c r="T20" s="30"/>
-      <c r="U20" s="30"/>
-      <c r="V20" s="30"/>
-      <c r="W20" s="30"/>
-      <c r="X20" s="30"/>
-      <c r="Y20" s="30"/>
-      <c r="Z20" s="30"/>
-      <c r="AA20" s="30"/>
-      <c r="AB20" s="30"/>
-      <c r="AC20" s="30"/>
-      <c r="AD20" s="30"/>
-      <c r="AE20" s="30"/>
-      <c r="AF20" s="30"/>
+      <c r="A20" s="30" t="s">
+        <v>373</v>
+      </c>
+      <c r="B20" s="31"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="31"/>
+      <c r="H20" s="31"/>
+      <c r="I20" s="31"/>
+      <c r="J20" s="31"/>
+      <c r="K20" s="31"/>
+      <c r="L20" s="31"/>
+      <c r="M20" s="31"/>
+      <c r="N20" s="31"/>
+      <c r="O20" s="31"/>
+      <c r="P20" s="31"/>
+      <c r="Q20" s="31"/>
+      <c r="R20" s="31"/>
+      <c r="S20" s="31"/>
+      <c r="T20" s="31"/>
+      <c r="U20" s="31"/>
+      <c r="V20" s="31"/>
+      <c r="W20" s="31"/>
+      <c r="X20" s="31"/>
+      <c r="Y20" s="31"/>
+      <c r="Z20" s="31"/>
+      <c r="AA20" s="31"/>
+      <c r="AB20" s="31"/>
+      <c r="AC20" s="31"/>
+      <c r="AD20" s="31"/>
+      <c r="AE20" s="31"/>
+      <c r="AF20" s="31"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="31" t="s">
-        <v>371</v>
-      </c>
-      <c r="B21" s="32">
+      <c r="A21" s="32" t="s">
+        <v>373</v>
+      </c>
+      <c r="B21" s="33">
         <v>19693.17</v>
       </c>
-      <c r="C21" s="32">
+      <c r="C21" s="33">
         <v>13170.89</v>
       </c>
-      <c r="D21" s="32">
+      <c r="D21" s="33">
         <v>11589.26</v>
       </c>
-      <c r="E21" s="33">
+      <c r="E21" s="34">
         <v>6762.7</v>
       </c>
-      <c r="F21" s="33">
+      <c r="F21" s="34">
         <v>6276.3</v>
       </c>
-      <c r="G21" s="33">
+      <c r="G21" s="34">
         <v>6114.62</v>
       </c>
-      <c r="H21" s="33">
+      <c r="H21" s="34">
         <v>5675.19</v>
       </c>
-      <c r="I21" s="33">
+      <c r="I21" s="34">
         <v>6367.1</v>
       </c>
-      <c r="J21" s="33">
+      <c r="J21" s="34">
         <v>5101.79</v>
       </c>
-      <c r="K21" s="33">
+      <c r="K21" s="34">
         <v>4094.97</v>
       </c>
-      <c r="L21" s="33">
+      <c r="L21" s="34">
         <v>5723.97</v>
       </c>
-      <c r="M21" s="33">
+      <c r="M21" s="34">
         <v>2467.25</v>
       </c>
-      <c r="N21" s="33">
+      <c r="N21" s="34">
         <v>2146.32</v>
       </c>
-      <c r="O21" s="33">
+      <c r="O21" s="34">
         <v>981.08</v>
       </c>
-      <c r="P21" s="33">
+      <c r="P21" s="34">
         <v>1089.14</v>
       </c>
-      <c r="Q21" s="33">
+      <c r="Q21" s="34">
         <v>1052.02</v>
       </c>
-      <c r="R21" s="33">
+      <c r="R21" s="34">
         <v>1501.54</v>
       </c>
-      <c r="S21" s="33">
+      <c r="S21" s="34">
         <v>1473.91</v>
       </c>
-      <c r="T21" s="33">
+      <c r="T21" s="34">
         <v>2047.17</v>
       </c>
-      <c r="U21" s="33">
+      <c r="U21" s="34">
         <v>1627.05</v>
       </c>
-      <c r="V21" s="33">
+      <c r="V21" s="34">
         <v>1276.55</v>
       </c>
-      <c r="W21" s="33">
+      <c r="W21" s="34">
         <v>842.47</v>
       </c>
-      <c r="X21" s="33">
+      <c r="X21" s="34">
         <v>617.89</v>
       </c>
-      <c r="Y21" s="33">
+      <c r="Y21" s="34">
         <v>692.09</v>
       </c>
-      <c r="Z21" s="33">
+      <c r="Z21" s="34">
         <v>753.74</v>
       </c>
-      <c r="AA21" s="33">
+      <c r="AA21" s="34">
         <v>837.03</v>
       </c>
-      <c r="AB21" s="33">
+      <c r="AB21" s="34">
         <v>739.03</v>
       </c>
-      <c r="AC21" s="33">
+      <c r="AC21" s="34">
         <v>678.76</v>
       </c>
-      <c r="AD21" s="33">
+      <c r="AD21" s="34">
         <v>949.43</v>
       </c>
-      <c r="AE21" s="33">
+      <c r="AE21" s="34">
         <v>916.36</v>
       </c>
-      <c r="AF21" s="33">
+      <c r="AF21" s="34">
         <v>672.72</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="31" t="s">
-        <v>372</v>
-      </c>
-      <c r="B22" s="32">
+      <c r="A22" s="32" t="s">
+        <v>374</v>
+      </c>
+      <c r="B22" s="33">
         <v>11890.74</v>
       </c>
-      <c r="C22" s="33">
+      <c r="C22" s="34">
         <v>9292.11</v>
       </c>
-      <c r="D22" s="33">
+      <c r="D22" s="34">
         <v>7698.58</v>
       </c>
-      <c r="E22" s="33">
+      <c r="E22" s="34">
         <v>6538.28</v>
       </c>
-      <c r="F22" s="33">
+      <c r="F22" s="34">
         <v>6020.41</v>
       </c>
-      <c r="G22" s="33">
+      <c r="G22" s="34">
         <v>6139.0</v>
       </c>
-      <c r="H22" s="33">
+      <c r="H22" s="34">
         <v>5634.5</v>
       </c>
-      <c r="I22" s="33">
+      <c r="I22" s="34">
         <v>4869.11</v>
       </c>
-      <c r="J22" s="33">
+      <c r="J22" s="34">
         <v>4082.75</v>
       </c>
-      <c r="K22" s="33">
+      <c r="K22" s="34">
         <v>3161.04</v>
       </c>
-      <c r="L22" s="33">
+      <c r="L22" s="34">
         <v>2741.11</v>
       </c>
-      <c r="M22" s="33">
+      <c r="M22" s="34">
         <v>1577.72</v>
       </c>
-      <c r="N22" s="33">
+      <c r="N22" s="34">
         <v>1373.44</v>
       </c>
-      <c r="O22" s="33">
+      <c r="O22" s="34">
         <v>1117.07</v>
       </c>
-      <c r="P22" s="33">
+      <c r="P22" s="34">
         <v>1403.72</v>
       </c>
-      <c r="Q22" s="33">
+      <c r="Q22" s="34">
         <v>1520.85</v>
       </c>
-      <c r="R22" s="33">
+      <c r="R22" s="34">
         <v>1659.52</v>
       </c>
-      <c r="S22" s="33">
+      <c r="S22" s="34">
         <v>1494.37</v>
       </c>
-      <c r="T22" s="33">
+      <c r="T22" s="34">
         <v>1231.47</v>
       </c>
-      <c r="U22" s="33">
+      <c r="U22" s="34">
         <v>1042.77</v>
       </c>
-      <c r="V22" s="33">
+      <c r="V22" s="34">
         <v>826.68</v>
       </c>
-      <c r="W22" s="33">
+      <c r="W22" s="34">
         <v>780.49</v>
       </c>
-      <c r="X22" s="33">
+      <c r="X22" s="34">
         <v>753.8</v>
       </c>
-      <c r="Y22" s="33">
+      <c r="Y22" s="34">
         <v>674.84</v>
       </c>
-      <c r="Z22" s="33">
+      <c r="Z22" s="34">
         <v>788.89</v>
       </c>
-      <c r="AA22" s="33">
+      <c r="AA22" s="34">
         <v>806.58</v>
       </c>
-      <c r="AB22" s="33">
+      <c r="AB22" s="34">
         <v>787.24</v>
       </c>
-      <c r="AC22" s="32"/>
-      <c r="AD22" s="32"/>
-      <c r="AE22" s="32"/>
-      <c r="AF22" s="32"/>
+      <c r="AC22" s="33"/>
+      <c r="AD22" s="33"/>
+      <c r="AE22" s="33"/>
+      <c r="AF22" s="33"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="29" t="s">
-        <v>373</v>
-      </c>
-      <c r="B23" s="30"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="30"/>
-      <c r="I23" s="30"/>
-      <c r="J23" s="30"/>
-      <c r="K23" s="30"/>
-      <c r="L23" s="30"/>
-      <c r="M23" s="30"/>
-      <c r="N23" s="30"/>
-      <c r="O23" s="30"/>
-      <c r="P23" s="30"/>
-      <c r="Q23" s="30"/>
-      <c r="R23" s="30"/>
-      <c r="S23" s="30"/>
-      <c r="T23" s="30"/>
-      <c r="U23" s="30"/>
-      <c r="V23" s="30"/>
-      <c r="W23" s="30"/>
-      <c r="X23" s="30"/>
-      <c r="Y23" s="30"/>
-      <c r="Z23" s="30"/>
-      <c r="AA23" s="30"/>
-      <c r="AB23" s="30"/>
-      <c r="AC23" s="30"/>
-      <c r="AD23" s="30"/>
-      <c r="AE23" s="30"/>
-      <c r="AF23" s="30"/>
+      <c r="A23" s="30" t="s">
+        <v>375</v>
+      </c>
+      <c r="B23" s="31"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
+      <c r="M23" s="31"/>
+      <c r="N23" s="31"/>
+      <c r="O23" s="31"/>
+      <c r="P23" s="31"/>
+      <c r="Q23" s="31"/>
+      <c r="R23" s="31"/>
+      <c r="S23" s="31"/>
+      <c r="T23" s="31"/>
+      <c r="U23" s="31"/>
+      <c r="V23" s="31"/>
+      <c r="W23" s="31"/>
+      <c r="X23" s="31"/>
+      <c r="Y23" s="31"/>
+      <c r="Z23" s="31"/>
+      <c r="AA23" s="31"/>
+      <c r="AB23" s="31"/>
+      <c r="AC23" s="31"/>
+      <c r="AD23" s="31"/>
+      <c r="AE23" s="31"/>
+      <c r="AF23" s="31"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="31" t="s">
-        <v>373</v>
-      </c>
-      <c r="B24" s="32">
+      <c r="A24" s="32" t="s">
+        <v>375</v>
+      </c>
+      <c r="B24" s="33">
         <v>19650.8</v>
       </c>
-      <c r="C24" s="32">
+      <c r="C24" s="33">
         <v>11614.67</v>
       </c>
-      <c r="D24" s="33">
+      <c r="D24" s="34">
         <v>9356.27</v>
       </c>
-      <c r="E24" s="33">
+      <c r="E24" s="34">
         <v>5103.94</v>
       </c>
-      <c r="F24" s="33">
+      <c r="F24" s="34">
         <v>6813.44</v>
       </c>
-      <c r="G24" s="33">
+      <c r="G24" s="34">
         <v>7490.86</v>
       </c>
-      <c r="H24" s="33">
+      <c r="H24" s="34">
         <v>6285.9</v>
       </c>
-      <c r="I24" s="33">
+      <c r="I24" s="34">
         <v>6568.34</v>
       </c>
-      <c r="J24" s="33">
+      <c r="J24" s="34">
         <v>4986.14</v>
       </c>
-      <c r="K24" s="33">
+      <c r="K24" s="34">
         <v>4088.03</v>
       </c>
-      <c r="L24" s="33">
+      <c r="L24" s="34">
         <v>6263.52</v>
       </c>
-      <c r="M24" s="33">
+      <c r="M24" s="34">
         <v>2270.91</v>
       </c>
-      <c r="N24" s="33">
+      <c r="N24" s="34">
         <v>1581.83</v>
       </c>
-      <c r="O24" s="33">
+      <c r="O24" s="34">
         <v>833.54</v>
       </c>
-      <c r="P24" s="33">
+      <c r="P24" s="34">
         <v>845.24</v>
       </c>
-      <c r="Q24" s="33">
+      <c r="Q24" s="34">
         <v>944.6</v>
       </c>
-      <c r="R24" s="33">
+      <c r="R24" s="34">
         <v>1399.41</v>
       </c>
-      <c r="S24" s="33">
+      <c r="S24" s="34">
         <v>1168.39</v>
       </c>
-      <c r="T24" s="33">
+      <c r="T24" s="34">
         <v>1702.26</v>
       </c>
-      <c r="U24" s="33">
+      <c r="U24" s="34">
         <v>1191.16</v>
       </c>
-      <c r="V24" s="33">
+      <c r="V24" s="34">
         <v>1040.0</v>
       </c>
-      <c r="W24" s="33">
+      <c r="W24" s="34">
         <v>616.96</v>
       </c>
-      <c r="X24" s="33">
+      <c r="X24" s="34">
         <v>419.42</v>
       </c>
-      <c r="Y24" s="33">
+      <c r="Y24" s="34">
         <v>418.9</v>
       </c>
-      <c r="Z24" s="33">
+      <c r="Z24" s="34">
         <v>389.01</v>
       </c>
-      <c r="AA24" s="33">
+      <c r="AA24" s="34">
         <v>742.45</v>
       </c>
-      <c r="AB24" s="33">
+      <c r="AB24" s="34">
         <v>680.43</v>
       </c>
-      <c r="AC24" s="33">
+      <c r="AC24" s="34">
         <v>669.7</v>
       </c>
-      <c r="AD24" s="33">
+      <c r="AD24" s="34">
         <v>942.84</v>
       </c>
-      <c r="AE24" s="33">
+      <c r="AE24" s="34">
         <v>955.61</v>
       </c>
-      <c r="AF24" s="33">
+      <c r="AF24" s="34">
         <v>715.77</v>
       </c>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="31" t="s">
-        <v>374</v>
-      </c>
-      <c r="B25" s="32">
+      <c r="A25" s="32" t="s">
+        <v>376</v>
+      </c>
+      <c r="B25" s="33">
         <v>10870.44</v>
       </c>
-      <c r="C25" s="33">
+      <c r="C25" s="34">
         <v>8571.74</v>
       </c>
-      <c r="D25" s="33">
+      <c r="D25" s="34">
         <v>7444.46</v>
       </c>
-      <c r="E25" s="33">
+      <c r="E25" s="34">
         <v>6766.16</v>
       </c>
-      <c r="F25" s="33">
+      <c r="F25" s="34">
         <v>6526.55</v>
       </c>
-      <c r="G25" s="33">
+      <c r="G25" s="34">
         <v>6567.47</v>
       </c>
-      <c r="H25" s="33">
+      <c r="H25" s="34">
         <v>5885.3</v>
       </c>
-      <c r="I25" s="33">
+      <c r="I25" s="34">
         <v>4946.27</v>
       </c>
-      <c r="J25" s="33">
+      <c r="J25" s="34">
         <v>3988.73</v>
       </c>
-      <c r="K25" s="33">
+      <c r="K25" s="34">
         <v>3057.37</v>
       </c>
-      <c r="L25" s="33">
+      <c r="L25" s="34">
         <v>2573.95</v>
       </c>
-      <c r="M25" s="33">
+      <c r="M25" s="34">
         <v>1320.84</v>
       </c>
-      <c r="N25" s="33">
+      <c r="N25" s="34">
         <v>1136.09</v>
       </c>
-      <c r="O25" s="33">
+      <c r="O25" s="34">
         <v>950.01</v>
       </c>
-      <c r="P25" s="33">
+      <c r="P25" s="34">
         <v>1186.04</v>
       </c>
-      <c r="Q25" s="33">
+      <c r="Q25" s="34">
         <v>1264.8</v>
       </c>
-      <c r="R25" s="33">
+      <c r="R25" s="34">
         <v>1360.74</v>
       </c>
-      <c r="S25" s="33">
+      <c r="S25" s="34">
         <v>1177.84</v>
       </c>
-      <c r="T25" s="33">
+      <c r="T25" s="34">
         <v>956.78</v>
       </c>
-      <c r="U25" s="33">
+      <c r="U25" s="34">
         <v>759.21</v>
       </c>
-      <c r="V25" s="33">
+      <c r="V25" s="34">
         <v>569.64</v>
       </c>
-      <c r="W25" s="33">
+      <c r="W25" s="34">
         <v>538.35</v>
       </c>
-      <c r="X25" s="33">
+      <c r="X25" s="34">
         <v>547.13</v>
       </c>
-      <c r="Y25" s="33">
+      <c r="Y25" s="34">
         <v>524.88</v>
       </c>
-      <c r="Z25" s="33">
+      <c r="Z25" s="34">
         <v>682.16</v>
       </c>
-      <c r="AA25" s="33">
+      <c r="AA25" s="34">
         <v>780.82</v>
       </c>
-      <c r="AB25" s="33">
+      <c r="AB25" s="34">
         <v>788.58</v>
       </c>
-      <c r="AC25" s="32"/>
-      <c r="AD25" s="32"/>
-      <c r="AE25" s="32"/>
-      <c r="AF25" s="32"/>
+      <c r="AC25" s="33"/>
+      <c r="AD25" s="33"/>
+      <c r="AE25" s="33"/>
+      <c r="AF25" s="33"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="29" t="s">
-        <v>375</v>
-      </c>
-      <c r="B26" s="30"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="30"/>
-      <c r="H26" s="30"/>
-      <c r="I26" s="30"/>
-      <c r="J26" s="30"/>
-      <c r="K26" s="30"/>
-      <c r="L26" s="30"/>
-      <c r="M26" s="30"/>
-      <c r="N26" s="30"/>
-      <c r="O26" s="30"/>
-      <c r="P26" s="30"/>
-      <c r="Q26" s="30"/>
-      <c r="R26" s="30"/>
-      <c r="S26" s="30"/>
-      <c r="T26" s="30"/>
-      <c r="U26" s="30"/>
-      <c r="V26" s="30"/>
-      <c r="W26" s="30"/>
-      <c r="X26" s="30"/>
-      <c r="Y26" s="30"/>
-      <c r="Z26" s="30"/>
-      <c r="AA26" s="30"/>
-      <c r="AB26" s="30"/>
-      <c r="AC26" s="30"/>
-      <c r="AD26" s="30"/>
-      <c r="AE26" s="30"/>
-      <c r="AF26" s="30"/>
+      <c r="A26" s="30" t="s">
+        <v>377</v>
+      </c>
+      <c r="B26" s="31"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
+      <c r="M26" s="31"/>
+      <c r="N26" s="31"/>
+      <c r="O26" s="31"/>
+      <c r="P26" s="31"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="31"/>
+      <c r="S26" s="31"/>
+      <c r="T26" s="31"/>
+      <c r="U26" s="31"/>
+      <c r="V26" s="31"/>
+      <c r="W26" s="31"/>
+      <c r="X26" s="31"/>
+      <c r="Y26" s="31"/>
+      <c r="Z26" s="31"/>
+      <c r="AA26" s="31"/>
+      <c r="AB26" s="31"/>
+      <c r="AC26" s="31"/>
+      <c r="AD26" s="31"/>
+      <c r="AE26" s="31"/>
+      <c r="AF26" s="31"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="31" t="s">
-        <v>376</v>
-      </c>
-      <c r="B27" s="33">
+      <c r="A27" s="32" t="s">
+        <v>378</v>
+      </c>
+      <c r="B27" s="34">
         <v>1076.64</v>
       </c>
-      <c r="C27" s="33">
+      <c r="C27" s="34">
         <v>636.35</v>
       </c>
-      <c r="D27" s="33">
+      <c r="D27" s="34">
         <v>490.83</v>
       </c>
-      <c r="E27" s="33">
+      <c r="E27" s="34">
         <v>267.75</v>
       </c>
-      <c r="F27" s="33">
+      <c r="F27" s="34">
         <v>357.44</v>
       </c>
-      <c r="G27" s="33">
+      <c r="G27" s="34">
         <v>392.97</v>
       </c>
-      <c r="H27" s="33">
+      <c r="H27" s="34">
         <v>294.74</v>
       </c>
-      <c r="I27" s="33">
+      <c r="I27" s="34">
         <v>307.98</v>
       </c>
-      <c r="J27" s="33">
+      <c r="J27" s="34">
         <v>233.79</v>
       </c>
-      <c r="K27" s="33">
+      <c r="K27" s="34">
         <v>191.68</v>
       </c>
-      <c r="L27" s="33">
+      <c r="L27" s="34">
         <v>292.21</v>
       </c>
-      <c r="M27" s="33">
+      <c r="M27" s="34">
         <v>105.94</v>
       </c>
-      <c r="N27" s="34">
+      <c r="N27" s="35">
         <v>74.26</v>
       </c>
-      <c r="O27" s="34">
+      <c r="O27" s="35">
         <v>39.13</v>
       </c>
-      <c r="P27" s="34">
+      <c r="P27" s="35">
         <v>39.68</v>
       </c>
-      <c r="Q27" s="34">
+      <c r="Q27" s="35">
         <v>44.35</v>
       </c>
-      <c r="R27" s="34">
+      <c r="R27" s="35">
         <v>65.7</v>
       </c>
-      <c r="S27" s="34">
+      <c r="S27" s="35">
         <v>54.85</v>
       </c>
-      <c r="T27" s="34">
+      <c r="T27" s="35">
         <v>79.92</v>
       </c>
-      <c r="U27" s="34">
+      <c r="U27" s="35">
         <v>55.92</v>
       </c>
-      <c r="V27" s="34">
+      <c r="V27" s="35">
         <v>48.83</v>
       </c>
-      <c r="W27" s="34">
+      <c r="W27" s="35">
         <v>28.97</v>
       </c>
-      <c r="X27" s="34">
+      <c r="X27" s="35">
         <v>19.69</v>
       </c>
-      <c r="Y27" s="34">
+      <c r="Y27" s="35">
         <v>19.67</v>
       </c>
-      <c r="Z27" s="34">
+      <c r="Z27" s="35">
         <v>18.26</v>
       </c>
-      <c r="AA27" s="34">
+      <c r="AA27" s="35">
         <v>34.86</v>
       </c>
-      <c r="AB27" s="34">
+      <c r="AB27" s="35">
         <v>31.94</v>
       </c>
-      <c r="AC27" s="34">
+      <c r="AC27" s="35">
         <v>31.44</v>
       </c>
-      <c r="AD27" s="34">
+      <c r="AD27" s="35">
         <v>44.26</v>
       </c>
-      <c r="AE27" s="34">
+      <c r="AE27" s="35">
         <v>44.86</v>
       </c>
-      <c r="AF27" s="34">
+      <c r="AF27" s="35">
         <v>34.0</v>
       </c>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="31" t="s">
-        <v>377</v>
-      </c>
-      <c r="B28" s="33">
+      <c r="A28" s="32" t="s">
+        <v>379</v>
+      </c>
+      <c r="B28" s="34">
         <v>584.81</v>
       </c>
-      <c r="C28" s="33">
+      <c r="C28" s="34">
         <v>455.09</v>
       </c>
-      <c r="D28" s="33">
+      <c r="D28" s="34">
         <v>382.55</v>
       </c>
-      <c r="E28" s="33">
+      <c r="E28" s="34">
         <v>339.1</v>
       </c>
-      <c r="F28" s="33">
+      <c r="F28" s="34">
         <v>321.35</v>
       </c>
-      <c r="G28" s="33">
+      <c r="G28" s="34">
         <v>316.29</v>
       </c>
-      <c r="H28" s="33">
+      <c r="H28" s="34">
         <v>275.65</v>
       </c>
-      <c r="I28" s="33">
+      <c r="I28" s="34">
         <v>231.51</v>
       </c>
-      <c r="J28" s="33">
+      <c r="J28" s="34">
         <v>186.63</v>
       </c>
-      <c r="K28" s="33">
+      <c r="K28" s="34">
         <v>142.99</v>
       </c>
-      <c r="L28" s="33">
+      <c r="L28" s="34">
         <v>120.31</v>
       </c>
-      <c r="M28" s="34">
+      <c r="M28" s="35">
         <v>61.88</v>
       </c>
-      <c r="N28" s="34">
+      <c r="N28" s="35">
         <v>53.34</v>
       </c>
-      <c r="O28" s="34">
+      <c r="O28" s="35">
         <v>44.6</v>
       </c>
-      <c r="P28" s="34">
+      <c r="P28" s="35">
         <v>55.68</v>
       </c>
-      <c r="Q28" s="34">
+      <c r="Q28" s="35">
         <v>59.38</v>
       </c>
-      <c r="R28" s="34">
+      <c r="R28" s="35">
         <v>63.88</v>
       </c>
-      <c r="S28" s="34">
+      <c r="S28" s="35">
         <v>55.3</v>
       </c>
-      <c r="T28" s="34">
+      <c r="T28" s="35">
         <v>44.92</v>
       </c>
-      <c r="U28" s="34">
+      <c r="U28" s="35">
         <v>35.64</v>
       </c>
-      <c r="V28" s="34">
+      <c r="V28" s="35">
         <v>26.74</v>
       </c>
-      <c r="W28" s="34">
+      <c r="W28" s="35">
         <v>25.27</v>
       </c>
-      <c r="X28" s="34">
+      <c r="X28" s="35">
         <v>25.69</v>
       </c>
-      <c r="Y28" s="34">
+      <c r="Y28" s="35">
         <v>24.64</v>
       </c>
-      <c r="Z28" s="34">
+      <c r="Z28" s="35">
         <v>32.03</v>
       </c>
-      <c r="AA28" s="34">
+      <c r="AA28" s="35">
         <v>36.66</v>
       </c>
-      <c r="AB28" s="34">
+      <c r="AB28" s="35">
         <v>37.1</v>
       </c>
-      <c r="AC28" s="32"/>
-      <c r="AD28" s="32"/>
-      <c r="AE28" s="32"/>
-      <c r="AF28" s="32"/>
+      <c r="AC28" s="33"/>
+      <c r="AD28" s="33"/>
+      <c r="AE28" s="33"/>
+      <c r="AF28" s="33"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="29" t="s">
-        <v>378</v>
-      </c>
-      <c r="B29" s="30"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
-      <c r="H29" s="30"/>
-      <c r="I29" s="30"/>
-      <c r="J29" s="30"/>
-      <c r="K29" s="30"/>
-      <c r="L29" s="30"/>
-      <c r="M29" s="30"/>
-      <c r="N29" s="30"/>
-      <c r="O29" s="30"/>
-      <c r="P29" s="30"/>
-      <c r="Q29" s="30"/>
-      <c r="R29" s="30"/>
-      <c r="S29" s="30"/>
-      <c r="T29" s="30"/>
-      <c r="U29" s="30"/>
-      <c r="V29" s="30"/>
-      <c r="W29" s="30"/>
-      <c r="X29" s="30"/>
-      <c r="Y29" s="30"/>
-      <c r="Z29" s="30"/>
-      <c r="AA29" s="30"/>
-      <c r="AB29" s="30"/>
-      <c r="AC29" s="30"/>
-      <c r="AD29" s="30"/>
-      <c r="AE29" s="30"/>
-      <c r="AF29" s="30"/>
+      <c r="A29" s="30" t="s">
+        <v>380</v>
+      </c>
+      <c r="B29" s="31"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="31"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="31"/>
+      <c r="J29" s="31"/>
+      <c r="K29" s="31"/>
+      <c r="L29" s="31"/>
+      <c r="M29" s="31"/>
+      <c r="N29" s="31"/>
+      <c r="O29" s="31"/>
+      <c r="P29" s="31"/>
+      <c r="Q29" s="31"/>
+      <c r="R29" s="31"/>
+      <c r="S29" s="31"/>
+      <c r="T29" s="31"/>
+      <c r="U29" s="31"/>
+      <c r="V29" s="31"/>
+      <c r="W29" s="31"/>
+      <c r="X29" s="31"/>
+      <c r="Y29" s="31"/>
+      <c r="Z29" s="31"/>
+      <c r="AA29" s="31"/>
+      <c r="AB29" s="31"/>
+      <c r="AC29" s="31"/>
+      <c r="AD29" s="31"/>
+      <c r="AE29" s="31"/>
+      <c r="AF29" s="31"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="31" t="s">
-        <v>379</v>
-      </c>
-      <c r="B30" s="35">
+      <c r="A30" s="32" t="s">
+        <v>381</v>
+      </c>
+      <c r="B30" s="36">
         <v>14.26</v>
       </c>
-      <c r="C30" s="35">
+      <c r="C30" s="36">
         <v>14.55</v>
       </c>
-      <c r="D30" s="35">
+      <c r="D30" s="36">
         <v>2.93</v>
       </c>
-      <c r="E30" s="36">
+      <c r="E30" s="37">
         <v>-8.53</v>
       </c>
-      <c r="F30" s="36">
+      <c r="F30" s="37">
         <v>-5.18</v>
       </c>
-      <c r="G30" s="35">
+      <c r="G30" s="36">
         <v>19.54</v>
       </c>
-      <c r="H30" s="35">
+      <c r="H30" s="36">
         <v>10.32</v>
       </c>
-      <c r="I30" s="35">
+      <c r="I30" s="36">
         <v>5.76</v>
       </c>
-      <c r="J30" s="36">
+      <c r="J30" s="37">
         <v>-1.75</v>
       </c>
-      <c r="K30" s="36">
+      <c r="K30" s="37">
         <v>-7.33</v>
       </c>
-      <c r="L30" s="35">
+      <c r="L30" s="36">
         <v>15.13</v>
       </c>
-      <c r="M30" s="35">
+      <c r="M30" s="36">
         <v>15.64</v>
       </c>
-      <c r="N30" s="36">
+      <c r="N30" s="37">
         <v>-19.73</v>
       </c>
-      <c r="O30" s="35">
+      <c r="O30" s="36">
         <v>7.59</v>
       </c>
-      <c r="P30" s="35">
+      <c r="P30" s="36">
         <v>4.41</v>
       </c>
-      <c r="Q30" s="36">
+      <c r="Q30" s="37">
         <v>-7.85</v>
       </c>
-      <c r="R30" s="35">
+      <c r="R30" s="36">
         <v>10.97</v>
       </c>
-      <c r="S30" s="35">
+      <c r="S30" s="36">
         <v>2.24</v>
       </c>
-      <c r="T30" s="35">
+      <c r="T30" s="36">
         <v>14.96</v>
       </c>
-      <c r="U30" s="36">
+      <c r="U30" s="37">
         <v>-12.59</v>
       </c>
-      <c r="V30" s="36">
+      <c r="V30" s="37">
         <v>-5.39</v>
       </c>
-      <c r="W30" s="36">
+      <c r="W30" s="37">
         <v>-3.15</v>
       </c>
-      <c r="X30" s="35">
+      <c r="X30" s="36">
         <v>32.22</v>
       </c>
-      <c r="Y30" s="35">
+      <c r="Y30" s="36">
         <v>17.04</v>
       </c>
-      <c r="Z30" s="35"/>
-      <c r="AA30" s="35">
+      <c r="Z30" s="36"/>
+      <c r="AA30" s="36">
         <v>3.16</v>
       </c>
-      <c r="AB30" s="35">
+      <c r="AB30" s="36">
         <v>3.11</v>
       </c>
-      <c r="AC30" s="35">
+      <c r="AC30" s="36">
         <v>0.18</v>
       </c>
-      <c r="AD30" s="36">
+      <c r="AD30" s="37">
         <v>-3.92</v>
       </c>
-      <c r="AE30" s="35">
+      <c r="AE30" s="36">
         <v>1.94</v>
       </c>
-      <c r="AF30" s="36">
+      <c r="AF30" s="37">
         <v>-1.41</v>
       </c>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="31" t="s">
-        <v>380</v>
-      </c>
-      <c r="B31" s="35">
+      <c r="A31" s="32" t="s">
+        <v>382</v>
+      </c>
+      <c r="B31" s="36">
         <v>7.33</v>
       </c>
-      <c r="C31" s="35">
+      <c r="C31" s="36">
         <v>6.3</v>
       </c>
-      <c r="D31" s="35">
+      <c r="D31" s="36">
         <v>4.37</v>
       </c>
-      <c r="E31" s="35">
+      <c r="E31" s="36">
         <v>5.05</v>
       </c>
-      <c r="F31" s="35">
+      <c r="F31" s="36">
         <v>6.13</v>
       </c>
-      <c r="G31" s="35">
+      <c r="G31" s="36">
         <v>6.9</v>
       </c>
-      <c r="H31" s="35">
+      <c r="H31" s="36">
         <v>5.46</v>
       </c>
-      <c r="I31" s="35">
+      <c r="I31" s="36">
         <v>5.36</v>
       </c>
-      <c r="J31" s="35">
+      <c r="J31" s="36">
         <v>2.92</v>
       </c>
-      <c r="K31" s="35">
+      <c r="K31" s="36">
         <v>4.68</v>
       </c>
-      <c r="L31" s="35">
+      <c r="L31" s="36">
         <v>8.71</v>
       </c>
-      <c r="M31" s="35">
+      <c r="M31" s="36">
         <v>1.12</v>
       </c>
-      <c r="N31" s="36">
+      <c r="N31" s="37">
         <v>-2.31</v>
       </c>
-      <c r="O31" s="35">
+      <c r="O31" s="36">
         <v>3.93</v>
       </c>
-      <c r="P31" s="35">
+      <c r="P31" s="36">
         <v>6.62</v>
       </c>
-      <c r="Q31" s="35">
+      <c r="Q31" s="36">
         <v>3.43</v>
       </c>
-      <c r="R31" s="35">
+      <c r="R31" s="36">
         <v>3.63</v>
       </c>
-      <c r="S31" s="35">
+      <c r="S31" s="36">
         <v>1.22</v>
       </c>
-      <c r="T31" s="35">
+      <c r="T31" s="36">
         <v>3.53</v>
       </c>
-      <c r="U31" s="36">
+      <c r="U31" s="37">
         <v>-0.31</v>
       </c>
-      <c r="V31" s="35"/>
-      <c r="W31" s="35"/>
-      <c r="X31" s="35"/>
-      <c r="Y31" s="35"/>
-      <c r="Z31" s="35"/>
-      <c r="AA31" s="35">
+      <c r="V31" s="36"/>
+      <c r="W31" s="36"/>
+      <c r="X31" s="36"/>
+      <c r="Y31" s="36"/>
+      <c r="Z31" s="36"/>
+      <c r="AA31" s="36">
         <v>0.65</v>
       </c>
-      <c r="AB31" s="36">
+      <c r="AB31" s="37">
         <v>-0.2</v>
       </c>
-      <c r="AC31" s="35"/>
-      <c r="AD31" s="35"/>
-      <c r="AE31" s="35"/>
-      <c r="AF31" s="35"/>
+      <c r="AC31" s="36"/>
+      <c r="AD31" s="36"/>
+      <c r="AE31" s="36"/>
+      <c r="AF31" s="36"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="29" t="s">
-        <v>381</v>
-      </c>
-      <c r="B32" s="30"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="30"/>
-      <c r="I32" s="30"/>
-      <c r="J32" s="30"/>
-      <c r="K32" s="30"/>
-      <c r="L32" s="30"/>
-      <c r="M32" s="30"/>
-      <c r="N32" s="30"/>
-      <c r="O32" s="30"/>
-      <c r="P32" s="30"/>
-      <c r="Q32" s="30"/>
-      <c r="R32" s="30"/>
-      <c r="S32" s="30"/>
-      <c r="T32" s="30"/>
-      <c r="U32" s="30"/>
-      <c r="V32" s="30"/>
-      <c r="W32" s="30"/>
-      <c r="X32" s="30"/>
-      <c r="Y32" s="30"/>
-      <c r="Z32" s="30"/>
-      <c r="AA32" s="30"/>
-      <c r="AB32" s="30"/>
-      <c r="AC32" s="30"/>
-      <c r="AD32" s="30"/>
-      <c r="AE32" s="30"/>
-      <c r="AF32" s="30"/>
+      <c r="A32" s="30" t="s">
+        <v>383</v>
+      </c>
+      <c r="B32" s="31"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="31"/>
+      <c r="I32" s="31"/>
+      <c r="J32" s="31"/>
+      <c r="K32" s="31"/>
+      <c r="L32" s="31"/>
+      <c r="M32" s="31"/>
+      <c r="N32" s="31"/>
+      <c r="O32" s="31"/>
+      <c r="P32" s="31"/>
+      <c r="Q32" s="31"/>
+      <c r="R32" s="31"/>
+      <c r="S32" s="31"/>
+      <c r="T32" s="31"/>
+      <c r="U32" s="31"/>
+      <c r="V32" s="31"/>
+      <c r="W32" s="31"/>
+      <c r="X32" s="31"/>
+      <c r="Y32" s="31"/>
+      <c r="Z32" s="31"/>
+      <c r="AA32" s="31"/>
+      <c r="AB32" s="31"/>
+      <c r="AC32" s="31"/>
+      <c r="AD32" s="31"/>
+      <c r="AE32" s="31"/>
+      <c r="AF32" s="31"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="31" t="s">
-        <v>382</v>
-      </c>
-      <c r="B33" s="35">
+      <c r="A33" s="32" t="s">
+        <v>384</v>
+      </c>
+      <c r="B33" s="36">
         <v>1.6</v>
       </c>
-      <c r="C33" s="35">
+      <c r="C33" s="36">
         <v>2.48</v>
       </c>
-      <c r="D33" s="35">
+      <c r="D33" s="36">
         <v>2.47</v>
       </c>
-      <c r="E33" s="35">
+      <c r="E33" s="36">
         <v>4.29</v>
       </c>
-      <c r="F33" s="35">
+      <c r="F33" s="36">
         <v>2.48</v>
       </c>
-      <c r="G33" s="35">
+      <c r="G33" s="36">
         <v>2.06</v>
       </c>
-      <c r="H33" s="35">
+      <c r="H33" s="36">
         <v>2.25</v>
       </c>
-      <c r="I33" s="35">
+      <c r="I33" s="36">
         <v>1.65</v>
       </c>
-      <c r="J33" s="35">
+      <c r="J33" s="36">
         <v>2.16</v>
       </c>
-      <c r="K33" s="35">
+      <c r="K33" s="36">
         <v>1.89</v>
       </c>
-      <c r="L33" s="35">
+      <c r="L33" s="36">
         <v>0.65</v>
       </c>
-      <c r="M33" s="35">
+      <c r="M33" s="36">
         <v>1.03</v>
       </c>
-      <c r="N33" s="35">
+      <c r="N33" s="36">
         <v>1.47</v>
       </c>
-      <c r="O33" s="35">
+      <c r="O33" s="36">
         <v>1.21</v>
       </c>
-      <c r="P33" s="35">
+      <c r="P33" s="36">
         <v>0.92</v>
       </c>
-      <c r="Q33" s="35">
+      <c r="Q33" s="36">
         <v>0.84</v>
       </c>
-      <c r="R33" s="35">
+      <c r="R33" s="36">
         <v>0.6</v>
       </c>
-      <c r="S33" s="35">
+      <c r="S33" s="36">
         <v>0.7</v>
       </c>
-      <c r="T33" s="35">
+      <c r="T33" s="36">
         <v>0.45</v>
       </c>
-      <c r="U33" s="35">
+      <c r="U33" s="36">
         <v>0.34</v>
       </c>
-      <c r="V33" s="35">
+      <c r="V33" s="36">
         <v>0.37</v>
       </c>
-      <c r="W33" s="35">
+      <c r="W33" s="36">
         <v>0.67</v>
       </c>
-      <c r="X33" s="35">
+      <c r="X33" s="36">
         <v>0.97</v>
       </c>
-      <c r="Y33" s="35">
+      <c r="Y33" s="36">
         <v>0.86</v>
       </c>
-      <c r="Z33" s="35">
+      <c r="Z33" s="36">
         <v>1.03</v>
       </c>
-      <c r="AA33" s="35">
+      <c r="AA33" s="36">
         <v>0.55</v>
       </c>
-      <c r="AB33" s="35">
+      <c r="AB33" s="36">
         <v>0.62</v>
       </c>
-      <c r="AC33" s="35">
+      <c r="AC33" s="36">
         <v>0.56</v>
       </c>
-      <c r="AD33" s="35">
+      <c r="AD33" s="36">
         <v>0.36</v>
       </c>
-      <c r="AE33" s="35">
+      <c r="AE33" s="36">
         <v>0.37</v>
       </c>
-      <c r="AF33" s="35">
+      <c r="AF33" s="36">
         <v>0.44</v>
       </c>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="31" t="s">
-        <v>383</v>
-      </c>
-      <c r="B34" s="35">
+      <c r="A34" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="B34" s="36">
         <v>2.33</v>
       </c>
-      <c r="C34" s="35">
+      <c r="C34" s="36">
         <v>2.63</v>
       </c>
-      <c r="D34" s="35">
+      <c r="D34" s="36">
         <v>2.61</v>
       </c>
-      <c r="E34" s="35">
+      <c r="E34" s="36">
         <v>2.45</v>
       </c>
-      <c r="F34" s="35">
+      <c r="F34" s="36">
         <v>2.12</v>
       </c>
-      <c r="G34" s="35">
+      <c r="G34" s="36">
         <v>2.0</v>
       </c>
-      <c r="H34" s="35">
+      <c r="H34" s="36">
         <v>1.69</v>
       </c>
-      <c r="I34" s="35">
+      <c r="I34" s="36">
         <v>1.48</v>
       </c>
-      <c r="J34" s="35">
+      <c r="J34" s="36">
         <v>1.42</v>
       </c>
-      <c r="K34" s="35">
+      <c r="K34" s="36">
         <v>1.18</v>
       </c>
-      <c r="L34" s="35">
+      <c r="L34" s="36">
         <v>0.92</v>
       </c>
-      <c r="M34" s="35">
+      <c r="M34" s="36">
         <v>1.12</v>
       </c>
-      <c r="N34" s="35">
+      <c r="N34" s="36">
         <v>1.03</v>
       </c>
-      <c r="O34" s="35">
+      <c r="O34" s="36">
         <v>0.82</v>
       </c>
-      <c r="P34" s="35">
+      <c r="P34" s="36">
         <v>0.66</v>
       </c>
-      <c r="Q34" s="35">
+      <c r="Q34" s="36">
         <v>0.56</v>
       </c>
-      <c r="R34" s="35">
+      <c r="R34" s="36">
         <v>0.49</v>
       </c>
-      <c r="S34" s="35">
+      <c r="S34" s="36">
         <v>0.48</v>
       </c>
-      <c r="T34" s="35">
+      <c r="T34" s="36">
         <v>0.48</v>
       </c>
-      <c r="U34" s="35">
+      <c r="U34" s="36">
         <v>0.54</v>
       </c>
-      <c r="V34" s="35">
+      <c r="V34" s="36">
         <v>0.68</v>
       </c>
-      <c r="W34" s="35">
+      <c r="W34" s="36">
         <v>0.77</v>
       </c>
-      <c r="X34" s="35">
+      <c r="X34" s="36">
         <v>0.76</v>
       </c>
-      <c r="Y34" s="35">
+      <c r="Y34" s="36">
         <v>0.68</v>
       </c>
-      <c r="Z34" s="35">
+      <c r="Z34" s="36">
         <v>0.57</v>
       </c>
-      <c r="AA34" s="35">
+      <c r="AA34" s="36">
         <v>0.47</v>
       </c>
-      <c r="AB34" s="35">
+      <c r="AB34" s="36">
         <v>0.45</v>
       </c>
-      <c r="AC34" s="35"/>
-      <c r="AD34" s="35"/>
-      <c r="AE34" s="35"/>
-      <c r="AF34" s="35"/>
+      <c r="AC34" s="36"/>
+      <c r="AD34" s="36"/>
+      <c r="AE34" s="36"/>
+      <c r="AF34" s="36"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="31" t="s">
-        <v>384</v>
-      </c>
-      <c r="B35" s="35">
+      <c r="A35" s="32" t="s">
+        <v>386</v>
+      </c>
+      <c r="B35" s="36">
         <v>1.6</v>
       </c>
-      <c r="C35" s="35">
+      <c r="C35" s="36">
         <v>2.48</v>
       </c>
-      <c r="D35" s="35">
+      <c r="D35" s="36">
         <v>2.47</v>
       </c>
-      <c r="E35" s="35">
+      <c r="E35" s="36">
         <v>4.29</v>
       </c>
-      <c r="F35" s="35">
+      <c r="F35" s="36">
         <v>2.48</v>
       </c>
-      <c r="G35" s="35">
+      <c r="G35" s="36">
         <v>2.06</v>
       </c>
-      <c r="H35" s="35">
+      <c r="H35" s="36">
         <v>2.25</v>
       </c>
-      <c r="I35" s="35">
+      <c r="I35" s="36">
         <v>1.65</v>
       </c>
-      <c r="J35" s="35">
+      <c r="J35" s="36">
         <v>2.16</v>
       </c>
-      <c r="K35" s="35">
+      <c r="K35" s="36">
         <v>1.89</v>
       </c>
-      <c r="L35" s="35">
+      <c r="L35" s="36">
         <v>0.65</v>
       </c>
-      <c r="M35" s="35">
+      <c r="M35" s="36">
         <v>1.03</v>
       </c>
-      <c r="N35" s="35">
+      <c r="N35" s="36">
         <v>1.47</v>
       </c>
-      <c r="O35" s="35">
+      <c r="O35" s="36">
         <v>1.21</v>
       </c>
-      <c r="P35" s="35">
+      <c r="P35" s="36">
         <v>1.28</v>
       </c>
-      <c r="Q35" s="35">
+      <c r="Q35" s="36">
         <v>1.16</v>
       </c>
-      <c r="R35" s="35">
+      <c r="R35" s="36">
         <v>0.83</v>
       </c>
-      <c r="S35" s="35">
+      <c r="S35" s="36">
         <v>0.97</v>
       </c>
-      <c r="T35" s="35">
+      <c r="T35" s="36">
         <v>0.62</v>
       </c>
-      <c r="U35" s="35">
+      <c r="U35" s="36">
         <v>0.48</v>
       </c>
-      <c r="V35" s="35">
+      <c r="V35" s="36">
         <v>0.52</v>
       </c>
-      <c r="W35" s="35">
+      <c r="W35" s="36">
         <v>0.93</v>
       </c>
-      <c r="X35" s="35">
+      <c r="X35" s="36">
         <v>1.35</v>
       </c>
-      <c r="Y35" s="35">
+      <c r="Y35" s="36">
         <v>1.2</v>
       </c>
-      <c r="Z35" s="35">
+      <c r="Z35" s="36">
         <v>1.43</v>
       </c>
-      <c r="AA35" s="35">
+      <c r="AA35" s="36">
         <v>0.74</v>
       </c>
-      <c r="AB35" s="35">
+      <c r="AB35" s="36">
         <v>0.83</v>
       </c>
-      <c r="AC35" s="35">
+      <c r="AC35" s="36">
         <v>0.74</v>
       </c>
-      <c r="AD35" s="35">
+      <c r="AD35" s="36">
         <v>0.48</v>
       </c>
-      <c r="AE35" s="35">
+      <c r="AE35" s="36">
         <v>0.5</v>
       </c>
-      <c r="AF35" s="35">
+      <c r="AF35" s="36">
         <v>0.62</v>
       </c>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="31" t="s">
-        <v>385</v>
-      </c>
-      <c r="B36" s="35">
+      <c r="A36" s="32" t="s">
+        <v>387</v>
+      </c>
+      <c r="B36" s="36">
         <v>2.33</v>
       </c>
-      <c r="C36" s="35">
+      <c r="C36" s="36">
         <v>2.63</v>
       </c>
-      <c r="D36" s="35">
+      <c r="D36" s="36">
         <v>2.61</v>
       </c>
-      <c r="E36" s="35">
+      <c r="E36" s="36">
         <v>2.45</v>
       </c>
-      <c r="F36" s="35">
+      <c r="F36" s="36">
         <v>2.12</v>
       </c>
-      <c r="G36" s="35">
+      <c r="G36" s="36">
         <v>2.0</v>
       </c>
-      <c r="H36" s="35">
+      <c r="H36" s="36">
         <v>1.69</v>
       </c>
-      <c r="I36" s="35">
+      <c r="I36" s="36">
         <v>1.48</v>
       </c>
-      <c r="J36" s="35">
+      <c r="J36" s="36">
         <v>1.42</v>
       </c>
-      <c r="K36" s="35">
+      <c r="K36" s="36">
         <v>1.18</v>
       </c>
-      <c r="L36" s="35">
+      <c r="L36" s="36">
         <v>0.95</v>
       </c>
-      <c r="M36" s="35">
+      <c r="M36" s="36">
         <v>1.21</v>
       </c>
-      <c r="N36" s="35">
+      <c r="N36" s="36">
         <v>1.19</v>
       </c>
-      <c r="O36" s="35">
+      <c r="O36" s="36">
         <v>1.06</v>
       </c>
-      <c r="P36" s="35">
+      <c r="P36" s="36">
         <v>0.91</v>
       </c>
-      <c r="Q36" s="35">
+      <c r="Q36" s="36">
         <v>0.78</v>
       </c>
-      <c r="R36" s="35">
+      <c r="R36" s="36">
         <v>0.68</v>
       </c>
-      <c r="S36" s="35">
+      <c r="S36" s="36">
         <v>0.67</v>
       </c>
-      <c r="T36" s="35">
+      <c r="T36" s="36">
         <v>0.66</v>
       </c>
-      <c r="U36" s="35">
+      <c r="U36" s="36">
         <v>0.75</v>
       </c>
-      <c r="V36" s="35">
+      <c r="V36" s="36">
         <v>0.95</v>
       </c>
-      <c r="W36" s="35">
+      <c r="W36" s="36">
         <v>1.06</v>
       </c>
-      <c r="X36" s="35">
+      <c r="X36" s="36">
         <v>1.03</v>
       </c>
-      <c r="Y36" s="35">
+      <c r="Y36" s="36">
         <v>0.93</v>
       </c>
-      <c r="Z36" s="35">
+      <c r="Z36" s="36">
         <v>0.76</v>
       </c>
-      <c r="AA36" s="35">
+      <c r="AA36" s="36">
         <v>0.63</v>
       </c>
-      <c r="AB36" s="35">
+      <c r="AB36" s="36">
         <v>0.61</v>
       </c>
-      <c r="AC36" s="35"/>
-      <c r="AD36" s="35"/>
-      <c r="AE36" s="35"/>
-      <c r="AF36" s="35"/>
+      <c r="AC36" s="36"/>
+      <c r="AD36" s="36"/>
+      <c r="AE36" s="36"/>
+      <c r="AF36" s="36"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="29" t="s">
-        <v>386</v>
-      </c>
-      <c r="B37" s="30"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="30"/>
-      <c r="F37" s="30"/>
-      <c r="G37" s="30"/>
-      <c r="H37" s="30"/>
-      <c r="I37" s="30"/>
-      <c r="J37" s="30"/>
-      <c r="K37" s="30"/>
-      <c r="L37" s="30"/>
-      <c r="M37" s="30"/>
-      <c r="N37" s="30"/>
-      <c r="O37" s="30"/>
-      <c r="P37" s="30"/>
-      <c r="Q37" s="30"/>
-      <c r="R37" s="30"/>
-      <c r="S37" s="30"/>
-      <c r="T37" s="30"/>
-      <c r="U37" s="30"/>
-      <c r="V37" s="30"/>
-      <c r="W37" s="30"/>
-      <c r="X37" s="30"/>
-      <c r="Y37" s="30"/>
-      <c r="Z37" s="30"/>
-      <c r="AA37" s="30"/>
-      <c r="AB37" s="30"/>
-      <c r="AC37" s="30"/>
-      <c r="AD37" s="30"/>
-      <c r="AE37" s="30"/>
-      <c r="AF37" s="30"/>
+      <c r="A37" s="30" t="s">
+        <v>388</v>
+      </c>
+      <c r="B37" s="31"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="31"/>
+      <c r="J37" s="31"/>
+      <c r="K37" s="31"/>
+      <c r="L37" s="31"/>
+      <c r="M37" s="31"/>
+      <c r="N37" s="31"/>
+      <c r="O37" s="31"/>
+      <c r="P37" s="31"/>
+      <c r="Q37" s="31"/>
+      <c r="R37" s="31"/>
+      <c r="S37" s="31"/>
+      <c r="T37" s="31"/>
+      <c r="U37" s="31"/>
+      <c r="V37" s="31"/>
+      <c r="W37" s="31"/>
+      <c r="X37" s="31"/>
+      <c r="Y37" s="31"/>
+      <c r="Z37" s="31"/>
+      <c r="AA37" s="31"/>
+      <c r="AB37" s="31"/>
+      <c r="AC37" s="31"/>
+      <c r="AD37" s="31"/>
+      <c r="AE37" s="31"/>
+      <c r="AF37" s="31"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="31" t="s">
-        <v>387</v>
-      </c>
-      <c r="B38" s="34">
+      <c r="A38" s="32" t="s">
+        <v>389</v>
+      </c>
+      <c r="B38" s="35">
         <v>2.34</v>
       </c>
-      <c r="C38" s="34">
+      <c r="C38" s="35">
         <v>1.55</v>
       </c>
-      <c r="D38" s="34">
+      <c r="D38" s="35">
         <v>1.41</v>
       </c>
-      <c r="E38" s="34">
+      <c r="E38" s="35">
         <v>0.95</v>
       </c>
-      <c r="F38" s="34">
+      <c r="F38" s="35">
         <v>1.43</v>
       </c>
-      <c r="G38" s="34">
+      <c r="G38" s="35">
         <v>1.62</v>
       </c>
-      <c r="H38" s="34">
+      <c r="H38" s="35">
         <v>1.44</v>
       </c>
-      <c r="I38" s="34">
+      <c r="I38" s="35">
         <v>1.7</v>
       </c>
-      <c r="J38" s="34">
+      <c r="J38" s="35">
         <v>1.4</v>
       </c>
-      <c r="K38" s="34">
+      <c r="K38" s="35">
         <v>1.3</v>
       </c>
-      <c r="L38" s="34">
+      <c r="L38" s="35">
         <v>2.07</v>
       </c>
-      <c r="M38" s="34">
+      <c r="M38" s="35">
         <v>1.02</v>
       </c>
-      <c r="N38" s="34">
+      <c r="N38" s="35">
         <v>0.81</v>
       </c>
-      <c r="O38" s="34">
+      <c r="O38" s="35">
         <v>0.51</v>
       </c>
-      <c r="P38" s="34">
+      <c r="P38" s="35">
         <v>0.52</v>
       </c>
-      <c r="Q38" s="34">
+      <c r="Q38" s="35">
         <v>0.6</v>
       </c>
-      <c r="R38" s="34">
+      <c r="R38" s="35">
         <v>0.89</v>
       </c>
-      <c r="S38" s="34">
+      <c r="S38" s="35">
         <v>0.82</v>
       </c>
-      <c r="T38" s="34">
+      <c r="T38" s="35">
         <v>1.53</v>
       </c>
-      <c r="U38" s="34">
+      <c r="U38" s="35">
         <v>1.14</v>
       </c>
-      <c r="V38" s="34">
+      <c r="V38" s="35">
         <v>1.16</v>
       </c>
-      <c r="W38" s="34">
+      <c r="W38" s="35">
         <v>0.64</v>
       </c>
-      <c r="X38" s="34">
+      <c r="X38" s="35">
         <v>0.46</v>
       </c>
-      <c r="Y38" s="34">
+      <c r="Y38" s="35">
         <v>0.52</v>
       </c>
-      <c r="Z38" s="34">
+      <c r="Z38" s="35">
         <v>0.46</v>
       </c>
-      <c r="AA38" s="34">
+      <c r="AA38" s="35">
         <v>0.92</v>
       </c>
-      <c r="AB38" s="34">
+      <c r="AB38" s="35">
         <v>0.9</v>
       </c>
-      <c r="AC38" s="34">
+      <c r="AC38" s="35">
         <v>0.97</v>
       </c>
-      <c r="AD38" s="34">
+      <c r="AD38" s="35">
         <v>1.68</v>
       </c>
-      <c r="AE38" s="34">
+      <c r="AE38" s="35">
         <v>1.83</v>
       </c>
-      <c r="AF38" s="34">
+      <c r="AF38" s="35">
         <v>1.59</v>
       </c>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="31" t="s">
-        <v>388</v>
-      </c>
-      <c r="B39" s="34">
+      <c r="A39" s="32" t="s">
+        <v>390</v>
+      </c>
+      <c r="B39" s="35">
         <v>1.6</v>
       </c>
-      <c r="C39" s="34">
+      <c r="C39" s="35">
         <v>1.4</v>
       </c>
-      <c r="D39" s="34">
+      <c r="D39" s="35">
         <v>1.36</v>
       </c>
-      <c r="E39" s="34">
+      <c r="E39" s="35">
         <v>1.4</v>
       </c>
-      <c r="F39" s="34">
+      <c r="F39" s="35">
         <v>1.52</v>
       </c>
-      <c r="G39" s="34">
+      <c r="G39" s="35">
         <v>1.5</v>
       </c>
-      <c r="H39" s="34">
+      <c r="H39" s="35">
         <v>1.57</v>
       </c>
-      <c r="I39" s="34">
+      <c r="I39" s="35">
         <v>1.51</v>
       </c>
-      <c r="J39" s="34">
+      <c r="J39" s="35">
         <v>1.36</v>
       </c>
-      <c r="K39" s="34">
+      <c r="K39" s="35">
         <v>1.21</v>
       </c>
-      <c r="L39" s="34">
+      <c r="L39" s="35">
         <v>1.07</v>
       </c>
-      <c r="M39" s="34">
+      <c r="M39" s="35">
         <v>0.71</v>
       </c>
-      <c r="N39" s="34">
+      <c r="N39" s="35">
         <v>0.66</v>
       </c>
-      <c r="O39" s="34">
+      <c r="O39" s="35">
         <v>0.66</v>
       </c>
-      <c r="P39" s="34">
+      <c r="P39" s="35">
         <v>0.83</v>
       </c>
-      <c r="Q39" s="34">
+      <c r="Q39" s="35">
         <v>0.96</v>
       </c>
-      <c r="R39" s="34">
+      <c r="R39" s="35">
         <v>1.08</v>
       </c>
-      <c r="S39" s="34">
+      <c r="S39" s="35">
         <v>1.06</v>
       </c>
-      <c r="T39" s="34">
+      <c r="T39" s="35">
         <v>1.02</v>
       </c>
-      <c r="U39" s="34">
+      <c r="U39" s="35">
         <v>0.79</v>
       </c>
-      <c r="V39" s="34">
+      <c r="V39" s="35">
         <v>0.65</v>
       </c>
-      <c r="W39" s="34">
+      <c r="W39" s="35">
         <v>0.59</v>
       </c>
-      <c r="X39" s="34">
+      <c r="X39" s="35">
         <v>0.64</v>
       </c>
-      <c r="Y39" s="34">
+      <c r="Y39" s="35">
         <v>0.73</v>
       </c>
-      <c r="Z39" s="34">
+      <c r="Z39" s="35">
         <v>0.94</v>
       </c>
-      <c r="AA39" s="34">
+      <c r="AA39" s="35">
         <v>1.2</v>
       </c>
-      <c r="AB39" s="34">
+      <c r="AB39" s="35">
         <v>1.34</v>
       </c>
-      <c r="AC39" s="32"/>
-      <c r="AD39" s="32"/>
-      <c r="AE39" s="32"/>
-      <c r="AF39" s="32"/>
+      <c r="AC39" s="33"/>
+      <c r="AD39" s="33"/>
+      <c r="AE39" s="33"/>
+      <c r="AF39" s="33"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="29" t="s">
-        <v>389</v>
-      </c>
-      <c r="B40" s="30"/>
-      <c r="C40" s="30"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="30"/>
-      <c r="G40" s="30"/>
-      <c r="H40" s="30"/>
-      <c r="I40" s="30"/>
-      <c r="J40" s="30"/>
-      <c r="K40" s="30"/>
-      <c r="L40" s="30"/>
-      <c r="M40" s="30"/>
-      <c r="N40" s="30"/>
-      <c r="O40" s="30"/>
-      <c r="P40" s="30"/>
-      <c r="Q40" s="30"/>
-      <c r="R40" s="30"/>
-      <c r="S40" s="30"/>
-      <c r="T40" s="30"/>
-      <c r="U40" s="30"/>
-      <c r="V40" s="30"/>
-      <c r="W40" s="30"/>
-      <c r="X40" s="30"/>
-      <c r="Y40" s="30"/>
-      <c r="Z40" s="30"/>
-      <c r="AA40" s="30"/>
-      <c r="AB40" s="30"/>
-      <c r="AC40" s="30"/>
-      <c r="AD40" s="30"/>
-      <c r="AE40" s="30"/>
-      <c r="AF40" s="30"/>
+      <c r="A40" s="30" t="s">
+        <v>391</v>
+      </c>
+      <c r="B40" s="31"/>
+      <c r="C40" s="31"/>
+      <c r="D40" s="31"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="31"/>
+      <c r="G40" s="31"/>
+      <c r="H40" s="31"/>
+      <c r="I40" s="31"/>
+      <c r="J40" s="31"/>
+      <c r="K40" s="31"/>
+      <c r="L40" s="31"/>
+      <c r="M40" s="31"/>
+      <c r="N40" s="31"/>
+      <c r="O40" s="31"/>
+      <c r="P40" s="31"/>
+      <c r="Q40" s="31"/>
+      <c r="R40" s="31"/>
+      <c r="S40" s="31"/>
+      <c r="T40" s="31"/>
+      <c r="U40" s="31"/>
+      <c r="V40" s="31"/>
+      <c r="W40" s="31"/>
+      <c r="X40" s="31"/>
+      <c r="Y40" s="31"/>
+      <c r="Z40" s="31"/>
+      <c r="AA40" s="31"/>
+      <c r="AB40" s="31"/>
+      <c r="AC40" s="31"/>
+      <c r="AD40" s="31"/>
+      <c r="AE40" s="31"/>
+      <c r="AF40" s="31"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="31" t="s">
-        <v>390</v>
-      </c>
-      <c r="B41" s="34">
+      <c r="A41" s="32" t="s">
+        <v>392</v>
+      </c>
+      <c r="B41" s="35">
         <v>2.73</v>
       </c>
-      <c r="C41" s="34">
+      <c r="C41" s="35">
         <v>1.8</v>
       </c>
-      <c r="D41" s="34">
+      <c r="D41" s="35">
         <v>1.67</v>
       </c>
-      <c r="E41" s="34">
+      <c r="E41" s="35">
         <v>1.16</v>
       </c>
-      <c r="F41" s="34">
+      <c r="F41" s="35">
         <v>1.58</v>
       </c>
-      <c r="G41" s="34">
+      <c r="G41" s="35">
         <v>1.78</v>
       </c>
-      <c r="H41" s="34">
+      <c r="H41" s="35">
         <v>1.63</v>
       </c>
-      <c r="I41" s="34">
+      <c r="I41" s="35">
         <v>1.96</v>
       </c>
-      <c r="J41" s="34">
+      <c r="J41" s="35">
         <v>1.64</v>
       </c>
-      <c r="K41" s="34">
+      <c r="K41" s="35">
         <v>1.49</v>
       </c>
-      <c r="L41" s="34">
+      <c r="L41" s="35">
         <v>2.24</v>
       </c>
-      <c r="M41" s="34">
+      <c r="M41" s="35">
         <v>1.11</v>
       </c>
-      <c r="N41" s="34">
+      <c r="N41" s="35">
         <v>0.9</v>
       </c>
-      <c r="O41" s="34">
+      <c r="O41" s="35">
         <v>0.55</v>
       </c>
-      <c r="P41" s="34">
+      <c r="P41" s="35">
         <v>0.52</v>
       </c>
-      <c r="Q41" s="34">
+      <c r="Q41" s="35">
         <v>0.61</v>
       </c>
-      <c r="R41" s="34">
+      <c r="R41" s="35">
         <v>0.92</v>
       </c>
-      <c r="S41" s="34">
+      <c r="S41" s="35">
         <v>0.86</v>
       </c>
-      <c r="T41" s="34">
+      <c r="T41" s="35">
         <v>1.61</v>
       </c>
-      <c r="U41" s="34">
+      <c r="U41" s="35">
         <v>1.25</v>
       </c>
-      <c r="V41" s="34">
+      <c r="V41" s="35">
         <v>1.24</v>
       </c>
-      <c r="W41" s="34">
+      <c r="W41" s="35">
         <v>0.65</v>
       </c>
-      <c r="X41" s="34">
+      <c r="X41" s="35">
         <v>0.47</v>
       </c>
-      <c r="Y41" s="34">
+      <c r="Y41" s="35">
         <v>0.54</v>
       </c>
-      <c r="Z41" s="34">
+      <c r="Z41" s="35">
         <v>0.48</v>
       </c>
-      <c r="AA41" s="34">
+      <c r="AA41" s="35">
         <v>0.98</v>
       </c>
-      <c r="AB41" s="34">
+      <c r="AB41" s="35">
         <v>0.94</v>
       </c>
-      <c r="AC41" s="34">
+      <c r="AC41" s="35">
         <v>1.03</v>
       </c>
-      <c r="AD41" s="34">
+      <c r="AD41" s="35">
         <v>1.8</v>
       </c>
-      <c r="AE41" s="34">
+      <c r="AE41" s="35">
         <v>1.83</v>
       </c>
-      <c r="AF41" s="34">
+      <c r="AF41" s="35">
         <v>1.59</v>
       </c>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="31" t="s">
-        <v>391</v>
-      </c>
-      <c r="B42" s="34">
+      <c r="A42" s="32" t="s">
+        <v>393</v>
+      </c>
+      <c r="B42" s="35">
         <v>1.87</v>
       </c>
-      <c r="C42" s="34">
+      <c r="C42" s="35">
         <v>1.61</v>
       </c>
-      <c r="D42" s="34">
+      <c r="D42" s="35">
         <v>1.56</v>
       </c>
-      <c r="E42" s="34">
+      <c r="E42" s="35">
         <v>1.6</v>
       </c>
-      <c r="F42" s="34">
+      <c r="F42" s="35">
         <v>1.71</v>
       </c>
-      <c r="G42" s="34">
+      <c r="G42" s="35">
         <v>1.71</v>
       </c>
-      <c r="H42" s="34">
+      <c r="H42" s="35">
         <v>1.78</v>
       </c>
-      <c r="I42" s="34">
+      <c r="I42" s="35">
         <v>1.71</v>
       </c>
-      <c r="J42" s="34">
+      <c r="J42" s="35">
         <v>1.52</v>
       </c>
-      <c r="K42" s="34">
+      <c r="K42" s="35">
         <v>1.33</v>
       </c>
-      <c r="L42" s="34">
+      <c r="L42" s="35">
         <v>1.15</v>
       </c>
-      <c r="M42" s="34">
+      <c r="M42" s="35">
         <v>0.76</v>
       </c>
-      <c r="N42" s="34">
+      <c r="N42" s="35">
         <v>0.7</v>
       </c>
-      <c r="O42" s="34">
+      <c r="O42" s="35">
         <v>0.68</v>
       </c>
-      <c r="P42" s="34">
+      <c r="P42" s="35">
         <v>0.86</v>
       </c>
-      <c r="Q42" s="34">
+      <c r="Q42" s="35">
         <v>1.0</v>
       </c>
-      <c r="R42" s="34">
+      <c r="R42" s="35">
         <v>1.14</v>
       </c>
-      <c r="S42" s="34">
+      <c r="S42" s="35">
         <v>1.12</v>
       </c>
-      <c r="T42" s="34">
+      <c r="T42" s="35">
         <v>1.07</v>
       </c>
-      <c r="U42" s="34">
+      <c r="U42" s="35">
         <v>0.84</v>
       </c>
-      <c r="V42" s="34">
+      <c r="V42" s="35">
         <v>0.68</v>
       </c>
-      <c r="W42" s="34">
+      <c r="W42" s="35">
         <v>0.62</v>
       </c>
-      <c r="X42" s="34">
+      <c r="X42" s="35">
         <v>0.67</v>
       </c>
-      <c r="Y42" s="34">
+      <c r="Y42" s="35">
         <v>0.77</v>
       </c>
-      <c r="Z42" s="34">
+      <c r="Z42" s="35">
         <v>0.99</v>
       </c>
-      <c r="AA42" s="34">
+      <c r="AA42" s="35">
         <v>1.26</v>
       </c>
-      <c r="AB42" s="34">
+      <c r="AB42" s="35">
         <v>1.39</v>
       </c>
-      <c r="AC42" s="32"/>
-      <c r="AD42" s="32"/>
-      <c r="AE42" s="32"/>
-      <c r="AF42" s="32"/>
+      <c r="AC42" s="33"/>
+      <c r="AD42" s="33"/>
+      <c r="AE42" s="33"/>
+      <c r="AF42" s="33"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="29" t="s">
-        <v>392</v>
-      </c>
-      <c r="B43" s="30"/>
-      <c r="C43" s="30"/>
-      <c r="D43" s="30"/>
-      <c r="E43" s="30"/>
-      <c r="F43" s="30"/>
-      <c r="G43" s="30"/>
-      <c r="H43" s="30"/>
-      <c r="I43" s="30"/>
-      <c r="J43" s="30"/>
-      <c r="K43" s="30"/>
-      <c r="L43" s="30"/>
-      <c r="M43" s="30"/>
-      <c r="N43" s="30"/>
-      <c r="O43" s="30"/>
-      <c r="P43" s="30"/>
-      <c r="Q43" s="30"/>
-      <c r="R43" s="30"/>
-      <c r="S43" s="30"/>
-      <c r="T43" s="30"/>
-      <c r="U43" s="30"/>
-      <c r="V43" s="30"/>
-      <c r="W43" s="30"/>
-      <c r="X43" s="30"/>
-      <c r="Y43" s="30"/>
-      <c r="Z43" s="30"/>
-      <c r="AA43" s="30"/>
-      <c r="AB43" s="30"/>
-      <c r="AC43" s="30"/>
-      <c r="AD43" s="30"/>
-      <c r="AE43" s="30"/>
-      <c r="AF43" s="30"/>
+      <c r="A43" s="30" t="s">
+        <v>394</v>
+      </c>
+      <c r="B43" s="31"/>
+      <c r="C43" s="31"/>
+      <c r="D43" s="31"/>
+      <c r="E43" s="31"/>
+      <c r="F43" s="31"/>
+      <c r="G43" s="31"/>
+      <c r="H43" s="31"/>
+      <c r="I43" s="31"/>
+      <c r="J43" s="31"/>
+      <c r="K43" s="31"/>
+      <c r="L43" s="31"/>
+      <c r="M43" s="31"/>
+      <c r="N43" s="31"/>
+      <c r="O43" s="31"/>
+      <c r="P43" s="31"/>
+      <c r="Q43" s="31"/>
+      <c r="R43" s="31"/>
+      <c r="S43" s="31"/>
+      <c r="T43" s="31"/>
+      <c r="U43" s="31"/>
+      <c r="V43" s="31"/>
+      <c r="W43" s="31"/>
+      <c r="X43" s="31"/>
+      <c r="Y43" s="31"/>
+      <c r="Z43" s="31"/>
+      <c r="AA43" s="31"/>
+      <c r="AB43" s="31"/>
+      <c r="AC43" s="31"/>
+      <c r="AD43" s="31"/>
+      <c r="AE43" s="31"/>
+      <c r="AF43" s="31"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="31" t="s">
-        <v>393</v>
-      </c>
-      <c r="B44" s="34">
+      <c r="A44" s="32" t="s">
+        <v>395</v>
+      </c>
+      <c r="B44" s="35">
         <v>0.59</v>
       </c>
-      <c r="C44" s="34">
+      <c r="C44" s="35">
         <v>0.36</v>
       </c>
-      <c r="D44" s="34">
+      <c r="D44" s="35">
         <v>0.31</v>
       </c>
-      <c r="E44" s="34">
+      <c r="E44" s="35">
         <v>0.2</v>
       </c>
-      <c r="F44" s="34">
+      <c r="F44" s="35">
         <v>0.36</v>
       </c>
-      <c r="G44" s="34">
+      <c r="G44" s="35">
         <v>0.41</v>
       </c>
-      <c r="H44" s="34">
+      <c r="H44" s="35">
         <v>0.34</v>
       </c>
-      <c r="I44" s="34">
+      <c r="I44" s="35">
         <v>0.41</v>
       </c>
-      <c r="J44" s="34">
+      <c r="J44" s="35">
         <v>0.34</v>
       </c>
-      <c r="K44" s="34">
+      <c r="K44" s="35">
         <v>0.31</v>
       </c>
-      <c r="L44" s="34">
+      <c r="L44" s="35">
         <v>0.46</v>
       </c>
-      <c r="M44" s="34">
+      <c r="M44" s="35">
         <v>0.23</v>
       </c>
-      <c r="N44" s="34">
+      <c r="N44" s="35">
         <v>0.19</v>
       </c>
-      <c r="O44" s="34">
+      <c r="O44" s="35">
         <v>0.12</v>
       </c>
-      <c r="P44" s="34">
+      <c r="P44" s="35">
         <v>0.12</v>
       </c>
-      <c r="Q44" s="34">
+      <c r="Q44" s="35">
         <v>0.2</v>
       </c>
-      <c r="R44" s="34">
+      <c r="R44" s="35">
         <v>0.25</v>
       </c>
-      <c r="S44" s="34">
+      <c r="S44" s="35">
         <v>0.19</v>
       </c>
-      <c r="T44" s="34">
+      <c r="T44" s="35">
         <v>0.37</v>
       </c>
-      <c r="U44" s="34">
+      <c r="U44" s="35">
         <v>0.28</v>
       </c>
-      <c r="V44" s="34">
+      <c r="V44" s="35">
         <v>0.28</v>
       </c>
-      <c r="W44" s="34">
+      <c r="W44" s="35">
         <v>0.17</v>
       </c>
-      <c r="X44" s="34">
+      <c r="X44" s="35">
         <v>0.11</v>
       </c>
-      <c r="Y44" s="34">
+      <c r="Y44" s="35">
         <v>0.13</v>
       </c>
-      <c r="Z44" s="34">
+      <c r="Z44" s="35">
         <v>0.13</v>
       </c>
-      <c r="AA44" s="34">
+      <c r="AA44" s="35">
         <v>0.25</v>
       </c>
-      <c r="AB44" s="34">
+      <c r="AB44" s="35">
         <v>0.22</v>
       </c>
-      <c r="AC44" s="34">
+      <c r="AC44" s="35">
         <v>0.26</v>
       </c>
-      <c r="AD44" s="34">
+      <c r="AD44" s="35">
         <v>0.44</v>
       </c>
-      <c r="AE44" s="34">
+      <c r="AE44" s="35">
         <v>0.48</v>
       </c>
-      <c r="AF44" s="34">
+      <c r="AF44" s="35">
         <v>0.46</v>
       </c>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="31" t="s">
-        <v>394</v>
-      </c>
-      <c r="B45" s="34">
+      <c r="A45" s="32" t="s">
+        <v>396</v>
+      </c>
+      <c r="B45" s="35">
         <v>0.37</v>
       </c>
-      <c r="C45" s="34">
+      <c r="C45" s="35">
         <v>0.32</v>
       </c>
-      <c r="D45" s="34">
+      <c r="D45" s="35">
         <v>0.32</v>
       </c>
-      <c r="E45" s="34">
+      <c r="E45" s="35">
         <v>0.33</v>
       </c>
-      <c r="F45" s="34">
+      <c r="F45" s="35">
         <v>0.37</v>
       </c>
-      <c r="G45" s="34">
+      <c r="G45" s="35">
         <v>0.36</v>
       </c>
-      <c r="H45" s="34">
+      <c r="H45" s="35">
         <v>0.37</v>
       </c>
-      <c r="I45" s="34">
+      <c r="I45" s="35">
         <v>0.36</v>
       </c>
-      <c r="J45" s="34">
+      <c r="J45" s="35">
         <v>0.32</v>
       </c>
-      <c r="K45" s="34">
+      <c r="K45" s="35">
         <v>0.28</v>
       </c>
-      <c r="L45" s="34">
+      <c r="L45" s="35">
         <v>0.25</v>
       </c>
-      <c r="M45" s="34">
+      <c r="M45" s="35">
         <v>0.18</v>
       </c>
-      <c r="N45" s="34">
+      <c r="N45" s="35">
         <v>0.17</v>
       </c>
-      <c r="O45" s="34">
+      <c r="O45" s="35">
         <v>0.17</v>
       </c>
-      <c r="P45" s="34">
+      <c r="P45" s="35">
         <v>0.22</v>
       </c>
-      <c r="Q45" s="34">
+      <c r="Q45" s="35">
         <v>0.25</v>
       </c>
-      <c r="R45" s="34">
+      <c r="R45" s="35">
         <v>0.27</v>
       </c>
-      <c r="S45" s="34">
+      <c r="S45" s="35">
         <v>0.26</v>
       </c>
-      <c r="T45" s="34">
+      <c r="T45" s="35">
         <v>0.25</v>
       </c>
-      <c r="U45" s="34">
+      <c r="U45" s="35">
         <v>0.19</v>
       </c>
-      <c r="V45" s="34">
+      <c r="V45" s="35">
         <v>0.16</v>
       </c>
-      <c r="W45" s="34">
+      <c r="W45" s="35">
         <v>0.15</v>
       </c>
-      <c r="X45" s="34">
+      <c r="X45" s="35">
         <v>0.16</v>
       </c>
-      <c r="Y45" s="34">
+      <c r="Y45" s="35">
         <v>0.19</v>
       </c>
-      <c r="Z45" s="34">
+      <c r="Z45" s="35">
         <v>0.25</v>
       </c>
-      <c r="AA45" s="34">
+      <c r="AA45" s="35">
         <v>0.31</v>
       </c>
-      <c r="AB45" s="34">
+      <c r="AB45" s="35">
         <v>0.35</v>
       </c>
-      <c r="AC45" s="32"/>
-      <c r="AD45" s="32"/>
-      <c r="AE45" s="32"/>
-      <c r="AF45" s="32"/>
+      <c r="AC45" s="33"/>
+      <c r="AD45" s="33"/>
+      <c r="AE45" s="33"/>
+      <c r="AF45" s="33"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="29" t="s">
-        <v>395</v>
-      </c>
-      <c r="B46" s="30"/>
-      <c r="C46" s="30"/>
-      <c r="D46" s="30"/>
-      <c r="E46" s="30"/>
-      <c r="F46" s="30"/>
-      <c r="G46" s="30"/>
-      <c r="H46" s="30"/>
-      <c r="I46" s="30"/>
-      <c r="J46" s="30"/>
-      <c r="K46" s="30"/>
-      <c r="L46" s="30"/>
-      <c r="M46" s="30"/>
-      <c r="N46" s="30"/>
-      <c r="O46" s="30"/>
-      <c r="P46" s="30"/>
-      <c r="Q46" s="30"/>
-      <c r="R46" s="30"/>
-      <c r="S46" s="30"/>
-      <c r="T46" s="30"/>
-      <c r="U46" s="30"/>
-      <c r="V46" s="30"/>
-      <c r="W46" s="30"/>
-      <c r="X46" s="30"/>
-      <c r="Y46" s="30"/>
-      <c r="Z46" s="30"/>
-      <c r="AA46" s="30"/>
-      <c r="AB46" s="30"/>
-      <c r="AC46" s="30"/>
-      <c r="AD46" s="30"/>
-      <c r="AE46" s="30"/>
-      <c r="AF46" s="30"/>
+      <c r="A46" s="30" t="s">
+        <v>397</v>
+      </c>
+      <c r="B46" s="31"/>
+      <c r="C46" s="31"/>
+      <c r="D46" s="31"/>
+      <c r="E46" s="31"/>
+      <c r="F46" s="31"/>
+      <c r="G46" s="31"/>
+      <c r="H46" s="31"/>
+      <c r="I46" s="31"/>
+      <c r="J46" s="31"/>
+      <c r="K46" s="31"/>
+      <c r="L46" s="31"/>
+      <c r="M46" s="31"/>
+      <c r="N46" s="31"/>
+      <c r="O46" s="31"/>
+      <c r="P46" s="31"/>
+      <c r="Q46" s="31"/>
+      <c r="R46" s="31"/>
+      <c r="S46" s="31"/>
+      <c r="T46" s="31"/>
+      <c r="U46" s="31"/>
+      <c r="V46" s="31"/>
+      <c r="W46" s="31"/>
+      <c r="X46" s="31"/>
+      <c r="Y46" s="31"/>
+      <c r="Z46" s="31"/>
+      <c r="AA46" s="31"/>
+      <c r="AB46" s="31"/>
+      <c r="AC46" s="31"/>
+      <c r="AD46" s="31"/>
+      <c r="AE46" s="31"/>
+      <c r="AF46" s="31"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="31" t="s">
-        <v>396</v>
-      </c>
-      <c r="B47" s="34">
+      <c r="A47" s="32" t="s">
+        <v>398</v>
+      </c>
+      <c r="B47" s="35">
         <v>7.01</v>
       </c>
-      <c r="C47" s="34">
+      <c r="C47" s="35">
         <v>6.87</v>
       </c>
-      <c r="D47" s="34">
+      <c r="D47" s="35">
         <v>34.07</v>
       </c>
-      <c r="E47" s="32"/>
-      <c r="F47" s="32"/>
-      <c r="G47" s="34">
+      <c r="E47" s="33"/>
+      <c r="F47" s="33"/>
+      <c r="G47" s="35">
         <v>5.12</v>
       </c>
-      <c r="H47" s="34">
+      <c r="H47" s="35">
         <v>9.69</v>
       </c>
-      <c r="I47" s="34">
+      <c r="I47" s="35">
         <v>17.36</v>
       </c>
-      <c r="J47" s="32"/>
-      <c r="K47" s="32"/>
-      <c r="L47" s="34">
+      <c r="J47" s="33"/>
+      <c r="K47" s="33"/>
+      <c r="L47" s="35">
         <v>6.61</v>
       </c>
-      <c r="M47" s="34">
+      <c r="M47" s="35">
         <v>6.4</v>
       </c>
-      <c r="N47" s="32"/>
-      <c r="O47" s="34">
+      <c r="N47" s="33"/>
+      <c r="O47" s="35">
         <v>13.17</v>
       </c>
-      <c r="P47" s="34">
+      <c r="P47" s="35">
         <v>22.7</v>
       </c>
-      <c r="Q47" s="32"/>
-      <c r="R47" s="34">
+      <c r="Q47" s="33"/>
+      <c r="R47" s="35">
         <v>9.12</v>
       </c>
-      <c r="S47" s="34">
+      <c r="S47" s="35">
         <v>44.71</v>
       </c>
-      <c r="T47" s="34">
+      <c r="T47" s="35">
         <v>6.69</v>
       </c>
-      <c r="U47" s="32"/>
-      <c r="V47" s="32"/>
-      <c r="W47" s="32"/>
-      <c r="X47" s="34">
+      <c r="U47" s="33"/>
+      <c r="V47" s="33"/>
+      <c r="W47" s="33"/>
+      <c r="X47" s="35">
         <v>3.1</v>
       </c>
-      <c r="Y47" s="34">
+      <c r="Y47" s="35">
         <v>5.87</v>
       </c>
-      <c r="Z47" s="32"/>
-      <c r="AA47" s="34">
+      <c r="Z47" s="33"/>
+      <c r="AA47" s="35">
         <v>31.61</v>
       </c>
-      <c r="AB47" s="34">
+      <c r="AB47" s="35">
         <v>32.15</v>
       </c>
-      <c r="AC47" s="33">
+      <c r="AC47" s="34">
         <v>545.64</v>
       </c>
-      <c r="AD47" s="32"/>
-      <c r="AE47" s="34">
+      <c r="AD47" s="33"/>
+      <c r="AE47" s="35">
         <v>51.44</v>
       </c>
-      <c r="AF47" s="32"/>
+      <c r="AF47" s="33"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="31" t="s">
-        <v>397</v>
-      </c>
-      <c r="B48" s="34">
+      <c r="A48" s="32" t="s">
+        <v>399</v>
+      </c>
+      <c r="B48" s="35">
         <v>13.64</v>
       </c>
-      <c r="C48" s="34">
+      <c r="C48" s="35">
         <v>15.87</v>
       </c>
-      <c r="D48" s="34">
+      <c r="D48" s="35">
         <v>22.89</v>
       </c>
-      <c r="E48" s="34">
+      <c r="E48" s="35">
         <v>19.81</v>
       </c>
-      <c r="F48" s="34">
+      <c r="F48" s="35">
         <v>16.31</v>
       </c>
-      <c r="G48" s="34">
+      <c r="G48" s="35">
         <v>14.49</v>
       </c>
-      <c r="H48" s="34">
+      <c r="H48" s="35">
         <v>18.31</v>
       </c>
-      <c r="I48" s="34">
+      <c r="I48" s="35">
         <v>18.65</v>
       </c>
-      <c r="J48" s="34">
+      <c r="J48" s="35">
         <v>34.29</v>
       </c>
-      <c r="K48" s="34">
+      <c r="K48" s="35">
         <v>21.35</v>
       </c>
-      <c r="L48" s="34">
+      <c r="L48" s="35">
         <v>11.48</v>
       </c>
-      <c r="M48" s="34">
+      <c r="M48" s="35">
         <v>88.98</v>
       </c>
-      <c r="N48" s="32"/>
-      <c r="O48" s="34">
+      <c r="N48" s="33"/>
+      <c r="O48" s="35">
         <v>25.43</v>
       </c>
-      <c r="P48" s="34">
+      <c r="P48" s="35">
         <v>15.1</v>
       </c>
-      <c r="Q48" s="34">
+      <c r="Q48" s="35">
         <v>29.18</v>
       </c>
-      <c r="R48" s="34">
+      <c r="R48" s="35">
         <v>27.54</v>
       </c>
-      <c r="S48" s="34">
+      <c r="S48" s="35">
         <v>81.73</v>
       </c>
-      <c r="T48" s="34">
+      <c r="T48" s="35">
         <v>28.36</v>
       </c>
-      <c r="U48" s="32"/>
-      <c r="V48" s="32"/>
-      <c r="W48" s="32"/>
-      <c r="X48" s="32"/>
-      <c r="Y48" s="32"/>
-      <c r="Z48" s="32"/>
-      <c r="AA48" s="33">
+      <c r="U48" s="33"/>
+      <c r="V48" s="33"/>
+      <c r="W48" s="33"/>
+      <c r="X48" s="33"/>
+      <c r="Y48" s="33"/>
+      <c r="Z48" s="33"/>
+      <c r="AA48" s="34">
         <v>152.87</v>
       </c>
-      <c r="AB48" s="32"/>
-      <c r="AC48" s="32"/>
-      <c r="AD48" s="32"/>
-      <c r="AE48" s="32"/>
-      <c r="AF48" s="32"/>
+      <c r="AB48" s="33"/>
+      <c r="AC48" s="33"/>
+      <c r="AD48" s="33"/>
+      <c r="AE48" s="33"/>
+      <c r="AF48" s="33"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="29" t="s">
-        <v>398</v>
-      </c>
-      <c r="B49" s="30"/>
-      <c r="C49" s="30"/>
-      <c r="D49" s="30"/>
-      <c r="E49" s="30"/>
-      <c r="F49" s="30"/>
-      <c r="G49" s="30"/>
-      <c r="H49" s="30"/>
-      <c r="I49" s="30"/>
-      <c r="J49" s="30"/>
-      <c r="K49" s="30"/>
-      <c r="L49" s="30"/>
-      <c r="M49" s="30"/>
-      <c r="N49" s="30"/>
-      <c r="O49" s="30"/>
-      <c r="P49" s="30"/>
-      <c r="Q49" s="30"/>
-      <c r="R49" s="30"/>
-      <c r="S49" s="30"/>
-      <c r="T49" s="30"/>
-      <c r="U49" s="30"/>
-      <c r="V49" s="30"/>
-      <c r="W49" s="30"/>
-      <c r="X49" s="30"/>
-      <c r="Y49" s="30"/>
-      <c r="Z49" s="30"/>
-      <c r="AA49" s="30"/>
-      <c r="AB49" s="30"/>
-      <c r="AC49" s="30"/>
-      <c r="AD49" s="30"/>
-      <c r="AE49" s="30"/>
-      <c r="AF49" s="30"/>
+      <c r="A49" s="30" t="s">
+        <v>400</v>
+      </c>
+      <c r="B49" s="31"/>
+      <c r="C49" s="31"/>
+      <c r="D49" s="31"/>
+      <c r="E49" s="31"/>
+      <c r="F49" s="31"/>
+      <c r="G49" s="31"/>
+      <c r="H49" s="31"/>
+      <c r="I49" s="31"/>
+      <c r="J49" s="31"/>
+      <c r="K49" s="31"/>
+      <c r="L49" s="31"/>
+      <c r="M49" s="31"/>
+      <c r="N49" s="31"/>
+      <c r="O49" s="31"/>
+      <c r="P49" s="31"/>
+      <c r="Q49" s="31"/>
+      <c r="R49" s="31"/>
+      <c r="S49" s="31"/>
+      <c r="T49" s="31"/>
+      <c r="U49" s="31"/>
+      <c r="V49" s="31"/>
+      <c r="W49" s="31"/>
+      <c r="X49" s="31"/>
+      <c r="Y49" s="31"/>
+      <c r="Z49" s="31"/>
+      <c r="AA49" s="31"/>
+      <c r="AB49" s="31"/>
+      <c r="AC49" s="31"/>
+      <c r="AD49" s="31"/>
+      <c r="AE49" s="31"/>
+      <c r="AF49" s="31"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="31" t="s">
-        <v>399</v>
-      </c>
-      <c r="B50" s="34">
+      <c r="A50" s="32" t="s">
+        <v>401</v>
+      </c>
+      <c r="B50" s="35">
         <v>7.32</v>
       </c>
-      <c r="C50" s="34">
+      <c r="C50" s="35">
         <v>4.78</v>
       </c>
-      <c r="D50" s="34">
+      <c r="D50" s="35">
         <v>4.01</v>
       </c>
-      <c r="E50" s="34">
+      <c r="E50" s="35">
         <v>3.08</v>
       </c>
-      <c r="F50" s="34">
+      <c r="F50" s="35">
         <v>5.03</v>
       </c>
-      <c r="G50" s="34">
+      <c r="G50" s="35">
         <v>5.11</v>
       </c>
-      <c r="H50" s="34">
+      <c r="H50" s="35">
         <v>5.67</v>
       </c>
-      <c r="I50" s="34">
+      <c r="I50" s="35">
         <v>6.82</v>
       </c>
-      <c r="J50" s="34">
+      <c r="J50" s="35">
         <v>6.1</v>
       </c>
-      <c r="K50" s="34">
+      <c r="K50" s="35">
         <v>5.21</v>
       </c>
-      <c r="L50" s="34">
+      <c r="L50" s="35">
         <v>7.01</v>
       </c>
-      <c r="M50" s="34">
+      <c r="M50" s="35">
         <v>3.72</v>
       </c>
-      <c r="N50" s="34">
+      <c r="N50" s="35">
         <v>3.27</v>
       </c>
-      <c r="O50" s="34">
+      <c r="O50" s="35">
         <v>2.02</v>
       </c>
-      <c r="P50" s="34">
+      <c r="P50" s="35">
         <v>2.26</v>
       </c>
-      <c r="Q50" s="34">
+      <c r="Q50" s="35">
         <v>4.06</v>
       </c>
-      <c r="R50" s="34">
+      <c r="R50" s="35">
         <v>3.73</v>
       </c>
-      <c r="S50" s="34">
+      <c r="S50" s="35">
         <v>2.84</v>
       </c>
-      <c r="T50" s="34">
+      <c r="T50" s="35">
         <v>5.38</v>
       </c>
-      <c r="U50" s="34">
+      <c r="U50" s="35">
         <v>4.57</v>
       </c>
-      <c r="V50" s="34">
+      <c r="V50" s="35">
         <v>5.55</v>
       </c>
-      <c r="W50" s="34">
+      <c r="W50" s="35">
         <v>3.16</v>
       </c>
-      <c r="X50" s="34">
+      <c r="X50" s="35">
         <v>2.65</v>
       </c>
-      <c r="Y50" s="34">
+      <c r="Y50" s="35">
         <v>2.43</v>
       </c>
-      <c r="Z50" s="34">
+      <c r="Z50" s="35">
         <v>2.26</v>
       </c>
-      <c r="AA50" s="34">
+      <c r="AA50" s="35">
         <v>3.8</v>
       </c>
-      <c r="AB50" s="34">
+      <c r="AB50" s="35">
         <v>3.15</v>
       </c>
-      <c r="AC50" s="34">
+      <c r="AC50" s="35">
         <v>3.84</v>
       </c>
-      <c r="AD50" s="34">
+      <c r="AD50" s="35">
         <v>6.79</v>
       </c>
-      <c r="AE50" s="34">
+      <c r="AE50" s="35">
         <v>6.6</v>
       </c>
-      <c r="AF50" s="34">
+      <c r="AF50" s="35">
         <v>6.64</v>
       </c>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="31" t="s">
-        <v>400</v>
-      </c>
-      <c r="B51" s="34">
+      <c r="A51" s="32" t="s">
+        <v>402</v>
+      </c>
+      <c r="B51" s="35">
         <v>5.01</v>
       </c>
-      <c r="C51" s="34">
+      <c r="C51" s="35">
         <v>4.37</v>
       </c>
-      <c r="D51" s="34">
+      <c r="D51" s="35">
         <v>4.43</v>
       </c>
-      <c r="E51" s="34">
+      <c r="E51" s="35">
         <v>4.92</v>
       </c>
-      <c r="F51" s="34">
+      <c r="F51" s="35">
         <v>5.63</v>
       </c>
-      <c r="G51" s="34">
+      <c r="G51" s="35">
         <v>5.73</v>
       </c>
-      <c r="H51" s="34">
+      <c r="H51" s="35">
         <v>6.17</v>
       </c>
-      <c r="I51" s="34">
+      <c r="I51" s="35">
         <v>5.88</v>
       </c>
-      <c r="J51" s="34">
+      <c r="J51" s="35">
         <v>5.26</v>
       </c>
-      <c r="K51" s="34">
+      <c r="K51" s="35">
         <v>4.57</v>
       </c>
-      <c r="L51" s="34">
+      <c r="L51" s="35">
         <v>4.07</v>
       </c>
-      <c r="M51" s="34">
+      <c r="M51" s="35">
         <v>3.04</v>
       </c>
-      <c r="N51" s="34">
+      <c r="N51" s="35">
         <v>2.95</v>
       </c>
-      <c r="O51" s="34">
+      <c r="O51" s="35">
         <v>2.85</v>
       </c>
-      <c r="P51" s="34">
+      <c r="P51" s="35">
         <v>3.56</v>
       </c>
-      <c r="Q51" s="34">
+      <c r="Q51" s="35">
         <v>4.04</v>
       </c>
-      <c r="R51" s="34">
+      <c r="R51" s="35">
         <v>4.22</v>
       </c>
-      <c r="S51" s="34">
+      <c r="S51" s="35">
         <v>4.21</v>
       </c>
-      <c r="T51" s="34">
+      <c r="T51" s="35">
         <v>4.48</v>
       </c>
-      <c r="U51" s="34">
+      <c r="U51" s="35">
         <v>3.77</v>
       </c>
-      <c r="V51" s="34">
+      <c r="V51" s="35">
         <v>3.26</v>
       </c>
-      <c r="W51" s="34">
+      <c r="W51" s="35">
         <v>2.89</v>
       </c>
-      <c r="X51" s="34">
+      <c r="X51" s="35">
         <v>2.89</v>
       </c>
-      <c r="Y51" s="34">
+      <c r="Y51" s="35">
         <v>3.1</v>
       </c>
-      <c r="Z51" s="34">
+      <c r="Z51" s="35">
         <v>3.84</v>
       </c>
-      <c r="AA51" s="34">
+      <c r="AA51" s="35">
         <v>4.61</v>
       </c>
-      <c r="AB51" s="34">
+      <c r="AB51" s="35">
         <v>5.09</v>
       </c>
-      <c r="AC51" s="32"/>
-      <c r="AD51" s="32"/>
-      <c r="AE51" s="32"/>
-      <c r="AF51" s="32"/>
+      <c r="AC51" s="33"/>
+      <c r="AD51" s="33"/>
+      <c r="AE51" s="33"/>
+      <c r="AF51" s="33"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="29" t="s">
-        <v>401</v>
-      </c>
-      <c r="B52" s="30"/>
-      <c r="C52" s="30"/>
-      <c r="D52" s="30"/>
-      <c r="E52" s="30"/>
-      <c r="F52" s="30"/>
-      <c r="G52" s="30"/>
-      <c r="H52" s="30"/>
-      <c r="I52" s="30"/>
-      <c r="J52" s="30"/>
-      <c r="K52" s="30"/>
-      <c r="L52" s="30"/>
-      <c r="M52" s="30"/>
-      <c r="N52" s="30"/>
-      <c r="O52" s="30"/>
-      <c r="P52" s="30"/>
-      <c r="Q52" s="30"/>
-      <c r="R52" s="30"/>
-      <c r="S52" s="30"/>
-      <c r="T52" s="30"/>
-      <c r="U52" s="30"/>
-      <c r="V52" s="30"/>
-      <c r="W52" s="30"/>
-      <c r="X52" s="30"/>
-      <c r="Y52" s="30"/>
-      <c r="Z52" s="30"/>
-      <c r="AA52" s="30"/>
-      <c r="AB52" s="30"/>
-      <c r="AC52" s="30"/>
-      <c r="AD52" s="30"/>
-      <c r="AE52" s="30"/>
-      <c r="AF52" s="30"/>
+      <c r="A52" s="30" t="s">
+        <v>403</v>
+      </c>
+      <c r="B52" s="31"/>
+      <c r="C52" s="31"/>
+      <c r="D52" s="31"/>
+      <c r="E52" s="31"/>
+      <c r="F52" s="31"/>
+      <c r="G52" s="31"/>
+      <c r="H52" s="31"/>
+      <c r="I52" s="31"/>
+      <c r="J52" s="31"/>
+      <c r="K52" s="31"/>
+      <c r="L52" s="31"/>
+      <c r="M52" s="31"/>
+      <c r="N52" s="31"/>
+      <c r="O52" s="31"/>
+      <c r="P52" s="31"/>
+      <c r="Q52" s="31"/>
+      <c r="R52" s="31"/>
+      <c r="S52" s="31"/>
+      <c r="T52" s="31"/>
+      <c r="U52" s="31"/>
+      <c r="V52" s="31"/>
+      <c r="W52" s="31"/>
+      <c r="X52" s="31"/>
+      <c r="Y52" s="31"/>
+      <c r="Z52" s="31"/>
+      <c r="AA52" s="31"/>
+      <c r="AB52" s="31"/>
+      <c r="AC52" s="31"/>
+      <c r="AD52" s="31"/>
+      <c r="AE52" s="31"/>
+      <c r="AF52" s="31"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="31" t="s">
-        <v>402</v>
-      </c>
-      <c r="B53" s="34">
+      <c r="A53" s="32" t="s">
+        <v>404</v>
+      </c>
+      <c r="B53" s="35">
         <v>15.12</v>
       </c>
-      <c r="C53" s="34">
+      <c r="C53" s="35">
         <v>9.68</v>
       </c>
-      <c r="D53" s="34">
+      <c r="D53" s="35">
         <v>8.0</v>
       </c>
-      <c r="E53" s="34">
+      <c r="E53" s="35">
         <v>7.18</v>
       </c>
-      <c r="F53" s="34">
+      <c r="F53" s="35">
         <v>11.24</v>
       </c>
-      <c r="G53" s="34">
+      <c r="G53" s="35">
         <v>14.36</v>
       </c>
-      <c r="H53" s="34">
+      <c r="H53" s="35">
         <v>12.54</v>
       </c>
-      <c r="I53" s="34">
+      <c r="I53" s="35">
         <v>14.78</v>
       </c>
-      <c r="J53" s="34">
+      <c r="J53" s="35">
         <v>14.06</v>
       </c>
-      <c r="K53" s="34">
+      <c r="K53" s="35">
         <v>10.73</v>
       </c>
-      <c r="L53" s="34">
+      <c r="L53" s="35">
         <v>12.74</v>
       </c>
-      <c r="M53" s="34">
+      <c r="M53" s="35">
         <v>7.8</v>
       </c>
-      <c r="N53" s="34">
+      <c r="N53" s="35">
         <v>9.3</v>
       </c>
-      <c r="O53" s="34">
+      <c r="O53" s="35">
         <v>7.23</v>
       </c>
-      <c r="P53" s="34">
+      <c r="P53" s="35">
         <v>7.83</v>
       </c>
-      <c r="Q53" s="34">
+      <c r="Q53" s="35">
         <v>16.82</v>
       </c>
-      <c r="R53" s="34">
+      <c r="R53" s="35">
         <v>7.57</v>
       </c>
-      <c r="S53" s="34">
+      <c r="S53" s="35">
         <v>4.86</v>
       </c>
-      <c r="T53" s="34">
+      <c r="T53" s="35">
         <v>10.83</v>
       </c>
-      <c r="U53" s="34">
+      <c r="U53" s="35">
         <v>11.23</v>
       </c>
-      <c r="V53" s="34">
+      <c r="V53" s="35">
         <v>21.26</v>
       </c>
-      <c r="W53" s="34">
+      <c r="W53" s="35">
         <v>11.53</v>
       </c>
-      <c r="X53" s="34">
+      <c r="X53" s="35">
         <v>29.0</v>
       </c>
-      <c r="Y53" s="34">
+      <c r="Y53" s="35">
         <v>8.71</v>
       </c>
-      <c r="Z53" s="34">
+      <c r="Z53" s="35">
         <v>10.09</v>
       </c>
-      <c r="AA53" s="34">
+      <c r="AA53" s="35">
         <v>8.99</v>
       </c>
-      <c r="AB53" s="34">
+      <c r="AB53" s="35">
         <v>6.61</v>
       </c>
-      <c r="AC53" s="34">
+      <c r="AC53" s="35">
         <v>8.47</v>
       </c>
-      <c r="AD53" s="34">
+      <c r="AD53" s="35">
         <v>13.75</v>
       </c>
-      <c r="AE53" s="34">
+      <c r="AE53" s="35">
         <v>11.01</v>
       </c>
-      <c r="AF53" s="34">
+      <c r="AF53" s="35">
         <v>12.42</v>
       </c>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="31" t="s">
-        <v>403</v>
-      </c>
-      <c r="B54" s="34">
+      <c r="A54" s="32" t="s">
+        <v>405</v>
+      </c>
+      <c r="B54" s="35">
         <v>10.53</v>
       </c>
-      <c r="C54" s="34">
+      <c r="C54" s="35">
         <v>9.62</v>
       </c>
-      <c r="D54" s="34">
+      <c r="D54" s="35">
         <v>10.01</v>
       </c>
-      <c r="E54" s="34">
+      <c r="E54" s="35">
         <v>11.57</v>
       </c>
-      <c r="F54" s="34">
+      <c r="F54" s="35">
         <v>13.22</v>
       </c>
-      <c r="G54" s="34">
+      <c r="G54" s="35">
         <v>13.33</v>
       </c>
-      <c r="H54" s="34">
+      <c r="H54" s="35">
         <v>12.96</v>
       </c>
-      <c r="I54" s="34">
+      <c r="I54" s="35">
         <v>12.2</v>
       </c>
-      <c r="J54" s="34">
+      <c r="J54" s="35">
         <v>11.23</v>
       </c>
-      <c r="K54" s="34">
+      <c r="K54" s="35">
         <v>10.21</v>
       </c>
-      <c r="L54" s="34">
+      <c r="L54" s="35">
         <v>9.81</v>
       </c>
-      <c r="M54" s="34">
+      <c r="M54" s="35">
         <v>8.73</v>
       </c>
-      <c r="N54" s="34">
+      <c r="N54" s="35">
         <v>8.83</v>
       </c>
-      <c r="O54" s="34">
+      <c r="O54" s="35">
         <v>7.39</v>
       </c>
-      <c r="P54" s="34">
+      <c r="P54" s="35">
         <v>8.19</v>
       </c>
-      <c r="Q54" s="34">
+      <c r="Q54" s="35">
         <v>8.67</v>
       </c>
-      <c r="R54" s="34">
+      <c r="R54" s="35">
         <v>8.9</v>
       </c>
-      <c r="S54" s="34">
+      <c r="S54" s="35">
         <v>9.51</v>
       </c>
-      <c r="T54" s="34">
+      <c r="T54" s="35">
         <v>13.06</v>
       </c>
-      <c r="U54" s="34">
+      <c r="U54" s="35">
         <v>13.57</v>
       </c>
-      <c r="V54" s="34">
+      <c r="V54" s="35">
         <v>14.09</v>
       </c>
-      <c r="W54" s="34">
+      <c r="W54" s="35">
         <v>10.83</v>
       </c>
-      <c r="X54" s="34">
+      <c r="X54" s="35">
         <v>9.23</v>
       </c>
-      <c r="Y54" s="34">
+      <c r="Y54" s="35">
         <v>8.27</v>
       </c>
-      <c r="Z54" s="34">
+      <c r="Z54" s="35">
         <v>9.26</v>
       </c>
-      <c r="AA54" s="34">
+      <c r="AA54" s="35">
         <v>9.54</v>
       </c>
-      <c r="AB54" s="34">
+      <c r="AB54" s="35">
         <v>10.07</v>
       </c>
-      <c r="AC54" s="32"/>
-      <c r="AD54" s="32"/>
-      <c r="AE54" s="32"/>
-      <c r="AF54" s="32"/>
+      <c r="AC54" s="33"/>
+      <c r="AD54" s="33"/>
+      <c r="AE54" s="33"/>
+      <c r="AF54" s="33"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="29" t="s">
-        <v>404</v>
-      </c>
-      <c r="B55" s="30"/>
-      <c r="C55" s="30"/>
-      <c r="D55" s="30"/>
-      <c r="E55" s="30"/>
-      <c r="F55" s="30"/>
-      <c r="G55" s="30"/>
-      <c r="H55" s="30"/>
-      <c r="I55" s="30"/>
-      <c r="J55" s="30"/>
-      <c r="K55" s="30"/>
-      <c r="L55" s="30"/>
-      <c r="M55" s="30"/>
-      <c r="N55" s="30"/>
-      <c r="O55" s="30"/>
-      <c r="P55" s="30"/>
-      <c r="Q55" s="30"/>
-      <c r="R55" s="30"/>
-      <c r="S55" s="30"/>
-      <c r="T55" s="30"/>
-      <c r="U55" s="30"/>
-      <c r="V55" s="30"/>
-      <c r="W55" s="30"/>
-      <c r="X55" s="30"/>
-      <c r="Y55" s="30"/>
-      <c r="Z55" s="30"/>
-      <c r="AA55" s="30"/>
-      <c r="AB55" s="30"/>
-      <c r="AC55" s="30"/>
-      <c r="AD55" s="30"/>
-      <c r="AE55" s="30"/>
-      <c r="AF55" s="30"/>
+      <c r="A55" s="30" t="s">
+        <v>406</v>
+      </c>
+      <c r="B55" s="31"/>
+      <c r="C55" s="31"/>
+      <c r="D55" s="31"/>
+      <c r="E55" s="31"/>
+      <c r="F55" s="31"/>
+      <c r="G55" s="31"/>
+      <c r="H55" s="31"/>
+      <c r="I55" s="31"/>
+      <c r="J55" s="31"/>
+      <c r="K55" s="31"/>
+      <c r="L55" s="31"/>
+      <c r="M55" s="31"/>
+      <c r="N55" s="31"/>
+      <c r="O55" s="31"/>
+      <c r="P55" s="31"/>
+      <c r="Q55" s="31"/>
+      <c r="R55" s="31"/>
+      <c r="S55" s="31"/>
+      <c r="T55" s="31"/>
+      <c r="U55" s="31"/>
+      <c r="V55" s="31"/>
+      <c r="W55" s="31"/>
+      <c r="X55" s="31"/>
+      <c r="Y55" s="31"/>
+      <c r="Z55" s="31"/>
+      <c r="AA55" s="31"/>
+      <c r="AB55" s="31"/>
+      <c r="AC55" s="31"/>
+      <c r="AD55" s="31"/>
+      <c r="AE55" s="31"/>
+      <c r="AF55" s="31"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="31" t="s">
-        <v>405</v>
-      </c>
-      <c r="B56" s="34">
+      <c r="A56" s="32" t="s">
+        <v>407</v>
+      </c>
+      <c r="B56" s="35">
         <v>15.14</v>
       </c>
-      <c r="C56" s="34">
+      <c r="C56" s="35">
         <v>9.75</v>
       </c>
-      <c r="D56" s="34">
+      <c r="D56" s="35">
         <v>8.06</v>
       </c>
-      <c r="E56" s="34">
+      <c r="E56" s="35">
         <v>6.72</v>
       </c>
-      <c r="F56" s="34">
+      <c r="F56" s="35">
         <v>11.07</v>
       </c>
-      <c r="G56" s="34">
+      <c r="G56" s="35">
         <v>12.07</v>
       </c>
-      <c r="H56" s="34">
+      <c r="H56" s="35">
         <v>12.56</v>
       </c>
-      <c r="I56" s="34">
+      <c r="I56" s="35">
         <v>14.78</v>
       </c>
-      <c r="J56" s="34">
+      <c r="J56" s="35">
         <v>14.22</v>
       </c>
-      <c r="K56" s="34">
+      <c r="K56" s="35">
         <v>10.75</v>
       </c>
-      <c r="L56" s="34">
+      <c r="L56" s="35">
         <v>12.68</v>
       </c>
-      <c r="M56" s="34">
+      <c r="M56" s="35">
         <v>7.8</v>
       </c>
-      <c r="N56" s="34">
+      <c r="N56" s="35">
         <v>9.41</v>
       </c>
-      <c r="O56" s="34">
+      <c r="O56" s="35">
         <v>7.3</v>
       </c>
-      <c r="P56" s="34">
+      <c r="P56" s="35">
         <v>7.84</v>
       </c>
-      <c r="Q56" s="34">
+      <c r="Q56" s="35">
         <v>25.93</v>
       </c>
-      <c r="R56" s="34">
+      <c r="R56" s="35">
         <v>7.57</v>
       </c>
-      <c r="S56" s="34">
+      <c r="S56" s="35">
         <v>4.86</v>
       </c>
-      <c r="T56" s="34">
+      <c r="T56" s="35">
         <v>10.83</v>
       </c>
-      <c r="U56" s="34">
+      <c r="U56" s="35">
         <v>11.23</v>
       </c>
-      <c r="V56" s="34">
+      <c r="V56" s="35">
         <v>21.26</v>
       </c>
-      <c r="W56" s="34">
+      <c r="W56" s="35">
         <v>11.53</v>
       </c>
-      <c r="X56" s="34">
+      <c r="X56" s="35">
         <v>29.0</v>
       </c>
-      <c r="Y56" s="34">
+      <c r="Y56" s="35">
         <v>8.71</v>
       </c>
-      <c r="Z56" s="34">
+      <c r="Z56" s="35">
         <v>10.09</v>
       </c>
-      <c r="AA56" s="34">
+      <c r="AA56" s="35">
         <v>8.99</v>
       </c>
-      <c r="AB56" s="34">
+      <c r="AB56" s="35">
         <v>6.61</v>
       </c>
-      <c r="AC56" s="34">
+      <c r="AC56" s="35">
         <v>8.47</v>
       </c>
-      <c r="AD56" s="34">
+      <c r="AD56" s="35">
         <v>13.75</v>
       </c>
-      <c r="AE56" s="34">
+      <c r="AE56" s="35">
         <v>11.01</v>
       </c>
-      <c r="AF56" s="34">
+      <c r="AF56" s="35">
         <v>12.42</v>
       </c>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="31" t="s">
-        <v>406</v>
-      </c>
-      <c r="B57" s="34">
+      <c r="A57" s="32" t="s">
+        <v>408</v>
+      </c>
+      <c r="B57" s="35">
         <v>1.6</v>
       </c>
-      <c r="C57" s="34">
+      <c r="C57" s="35">
         <v>1.4</v>
       </c>
-      <c r="D57" s="34">
+      <c r="D57" s="35">
         <v>1.36</v>
       </c>
-      <c r="E57" s="34">
+      <c r="E57" s="35">
         <v>1.4</v>
       </c>
-      <c r="F57" s="34">
+      <c r="F57" s="35">
         <v>1.52</v>
       </c>
-      <c r="G57" s="34">
+      <c r="G57" s="35">
         <v>1.5</v>
       </c>
-      <c r="H57" s="34">
+      <c r="H57" s="35">
         <v>1.57</v>
       </c>
-      <c r="I57" s="34">
+      <c r="I57" s="35">
         <v>1.51</v>
       </c>
-      <c r="J57" s="34">
+      <c r="J57" s="35">
         <v>1.36</v>
       </c>
-      <c r="K57" s="34">
+      <c r="K57" s="35">
         <v>1.21</v>
       </c>
-      <c r="L57" s="34">
+      <c r="L57" s="35">
         <v>1.07</v>
       </c>
-      <c r="M57" s="34">
+      <c r="M57" s="35">
         <v>0.71</v>
       </c>
-      <c r="N57" s="34">
+      <c r="N57" s="35">
         <v>0.66</v>
       </c>
-      <c r="O57" s="34">
+      <c r="O57" s="35">
         <v>0.66</v>
       </c>
-      <c r="P57" s="34">
+      <c r="P57" s="35">
         <v>0.83</v>
       </c>
-      <c r="Q57" s="34">
+      <c r="Q57" s="35">
         <v>0.96</v>
       </c>
-      <c r="R57" s="34">
+      <c r="R57" s="35">
         <v>1.08</v>
       </c>
-      <c r="S57" s="34">
+      <c r="S57" s="35">
         <v>1.06</v>
       </c>
-      <c r="T57" s="34">
+      <c r="T57" s="35">
         <v>1.02</v>
       </c>
-      <c r="U57" s="34">
+      <c r="U57" s="35">
         <v>0.79</v>
       </c>
-      <c r="V57" s="34">
+      <c r="V57" s="35">
         <v>0.65</v>
       </c>
-      <c r="W57" s="34">
+      <c r="W57" s="35">
         <v>0.59</v>
       </c>
-      <c r="X57" s="34">
+      <c r="X57" s="35">
         <v>0.64</v>
       </c>
-      <c r="Y57" s="34">
+      <c r="Y57" s="35">
         <v>0.73</v>
       </c>
-      <c r="Z57" s="34">
+      <c r="Z57" s="35">
         <v>0.94</v>
       </c>
-      <c r="AA57" s="34">
+      <c r="AA57" s="35">
         <v>1.2</v>
       </c>
-      <c r="AB57" s="34">
+      <c r="AB57" s="35">
         <v>1.34</v>
       </c>
-      <c r="AC57" s="32"/>
-      <c r="AD57" s="32"/>
-      <c r="AE57" s="32"/>
-      <c r="AF57" s="32"/>
+      <c r="AC57" s="33"/>
+      <c r="AD57" s="33"/>
+      <c r="AE57" s="33"/>
+      <c r="AF57" s="33"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="29" t="s">
-        <v>407</v>
-      </c>
-      <c r="B58" s="30"/>
-      <c r="C58" s="30"/>
-      <c r="D58" s="30"/>
-      <c r="E58" s="30"/>
-      <c r="F58" s="30"/>
-      <c r="G58" s="30"/>
-      <c r="H58" s="30"/>
-      <c r="I58" s="30"/>
-      <c r="J58" s="30"/>
-      <c r="K58" s="30"/>
-      <c r="L58" s="30"/>
-      <c r="M58" s="30"/>
-      <c r="N58" s="30"/>
-      <c r="O58" s="30"/>
-      <c r="P58" s="30"/>
-      <c r="Q58" s="30"/>
-      <c r="R58" s="30"/>
-      <c r="S58" s="30"/>
-      <c r="T58" s="30"/>
-      <c r="U58" s="30"/>
-      <c r="V58" s="30"/>
-      <c r="W58" s="30"/>
-      <c r="X58" s="30"/>
-      <c r="Y58" s="30"/>
-      <c r="Z58" s="30"/>
-      <c r="AA58" s="30"/>
-      <c r="AB58" s="30"/>
-      <c r="AC58" s="30"/>
-      <c r="AD58" s="30"/>
-      <c r="AE58" s="30"/>
-      <c r="AF58" s="30"/>
+      <c r="A58" s="30" t="s">
+        <v>409</v>
+      </c>
+      <c r="B58" s="31"/>
+      <c r="C58" s="31"/>
+      <c r="D58" s="31"/>
+      <c r="E58" s="31"/>
+      <c r="F58" s="31"/>
+      <c r="G58" s="31"/>
+      <c r="H58" s="31"/>
+      <c r="I58" s="31"/>
+      <c r="J58" s="31"/>
+      <c r="K58" s="31"/>
+      <c r="L58" s="31"/>
+      <c r="M58" s="31"/>
+      <c r="N58" s="31"/>
+      <c r="O58" s="31"/>
+      <c r="P58" s="31"/>
+      <c r="Q58" s="31"/>
+      <c r="R58" s="31"/>
+      <c r="S58" s="31"/>
+      <c r="T58" s="31"/>
+      <c r="U58" s="31"/>
+      <c r="V58" s="31"/>
+      <c r="W58" s="31"/>
+      <c r="X58" s="31"/>
+      <c r="Y58" s="31"/>
+      <c r="Z58" s="31"/>
+      <c r="AA58" s="31"/>
+      <c r="AB58" s="31"/>
+      <c r="AC58" s="31"/>
+      <c r="AD58" s="31"/>
+      <c r="AE58" s="31"/>
+      <c r="AF58" s="31"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="31" t="s">
-        <v>408</v>
-      </c>
-      <c r="B59" s="34">
+      <c r="A59" s="32" t="s">
+        <v>410</v>
+      </c>
+      <c r="B59" s="35">
         <v>1.74</v>
       </c>
-      <c r="C59" s="34">
+      <c r="C59" s="35">
         <v>3.15</v>
       </c>
-      <c r="D59" s="34">
+      <c r="D59" s="35">
         <v>0.14</v>
       </c>
-      <c r="E59" s="34">
+      <c r="E59" s="35">
         <v>0.64</v>
       </c>
-      <c r="F59" s="34">
+      <c r="F59" s="35">
         <v>0.44</v>
       </c>
-      <c r="G59" s="34">
+      <c r="G59" s="35">
         <v>2.75</v>
       </c>
-      <c r="H59" s="34">
+      <c r="H59" s="35">
         <v>1.64</v>
       </c>
-      <c r="I59" s="34">
+      <c r="I59" s="35">
         <v>0.59</v>
       </c>
-      <c r="J59" s="37">
+      <c r="J59" s="38">
         <v>-1.25</v>
       </c>
-      <c r="K59" s="37">
+      <c r="K59" s="38">
         <v>-0.61</v>
       </c>
-      <c r="L59" s="34">
+      <c r="L59" s="35">
         <v>0.29</v>
       </c>
-      <c r="M59" s="34">
+      <c r="M59" s="35">
         <v>0.11</v>
       </c>
-      <c r="N59" s="34">
+      <c r="N59" s="35">
         <v>0.28</v>
       </c>
-      <c r="O59" s="34">
+      <c r="O59" s="35">
         <v>0.51</v>
       </c>
-      <c r="P59" s="34">
+      <c r="P59" s="35">
         <v>0.08</v>
       </c>
-      <c r="Q59" s="37">
+      <c r="Q59" s="38">
         <v>-0.25</v>
       </c>
-      <c r="R59" s="37">
+      <c r="R59" s="38">
         <v>-0.3</v>
       </c>
-      <c r="S59" s="34">
+      <c r="S59" s="35">
         <v>0.12</v>
       </c>
-      <c r="T59" s="34">
+      <c r="T59" s="35">
         <v>0.18</v>
       </c>
-      <c r="U59" s="34">
+      <c r="U59" s="35">
         <v>0.11</v>
       </c>
-      <c r="V59" s="37">
+      <c r="V59" s="38">
         <v>-6.91</v>
       </c>
-      <c r="W59" s="34">
+      <c r="W59" s="35">
         <v>0.04</v>
       </c>
-      <c r="X59" s="37">
+      <c r="X59" s="38">
         <v>-0.4</v>
       </c>
-      <c r="Y59" s="34">
+      <c r="Y59" s="35">
         <v>0.23</v>
       </c>
-      <c r="Z59" s="37">
+      <c r="Z59" s="38">
         <v>-0.19</v>
       </c>
-      <c r="AA59" s="37">
+      <c r="AA59" s="38">
         <v>-0.51</v>
       </c>
-      <c r="AB59" s="34">
+      <c r="AB59" s="35">
         <v>0.18</v>
       </c>
-      <c r="AC59" s="34">
+      <c r="AC59" s="35">
         <v>1.94</v>
       </c>
-      <c r="AD59" s="37">
+      <c r="AD59" s="38">
         <v>-0.82</v>
       </c>
-      <c r="AE59" s="34">
+      <c r="AE59" s="35">
         <v>0.21</v>
       </c>
-      <c r="AF59" s="32"/>
+      <c r="AF59" s="33"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="31" t="s">
-        <v>409</v>
-      </c>
-      <c r="B60" s="34">
+      <c r="A60" s="32" t="s">
+        <v>411</v>
+      </c>
+      <c r="B60" s="35">
         <v>0.54</v>
       </c>
-      <c r="C60" s="34">
+      <c r="C60" s="35">
         <v>0.51</v>
       </c>
-      <c r="D60" s="34">
+      <c r="D60" s="35">
         <v>0.51</v>
       </c>
-      <c r="E60" s="34">
+      <c r="E60" s="35">
         <v>0.79</v>
       </c>
-      <c r="F60" s="34">
+      <c r="F60" s="35">
         <v>1.39</v>
       </c>
-      <c r="G60" s="34">
+      <c r="G60" s="35">
         <v>18.92</v>
       </c>
-      <c r="H60" s="34">
+      <c r="H60" s="35">
         <v>1.78</v>
       </c>
-      <c r="I60" s="34">
+      <c r="I60" s="35">
         <v>0.69</v>
       </c>
-      <c r="J60" s="34">
+      <c r="J60" s="35">
         <v>0.59</v>
       </c>
-      <c r="K60" s="34">
+      <c r="K60" s="35">
         <v>0.4</v>
       </c>
-      <c r="L60" s="34">
+      <c r="L60" s="35">
         <v>0.2</v>
       </c>
-      <c r="M60" s="34">
+      <c r="M60" s="35">
         <v>0.85</v>
       </c>
-      <c r="N60" s="37">
+      <c r="N60" s="38">
         <v>-1.38</v>
       </c>
-      <c r="O60" s="37">
+      <c r="O60" s="38">
         <v>-1.43</v>
       </c>
-      <c r="P60" s="34">
+      <c r="P60" s="35">
         <v>5.9</v>
       </c>
-      <c r="Q60" s="34">
+      <c r="Q60" s="35">
         <v>3.57</v>
       </c>
-      <c r="R60" s="34">
+      <c r="R60" s="35">
         <v>0.32</v>
       </c>
-      <c r="S60" s="34">
+      <c r="S60" s="35">
         <v>0.13</v>
       </c>
-      <c r="T60" s="34">
+      <c r="T60" s="35">
         <v>0.51</v>
       </c>
-      <c r="U60" s="34">
+      <c r="U60" s="35">
         <v>0.62</v>
       </c>
-      <c r="V60" s="37">
+      <c r="V60" s="38">
         <v>-1.46</v>
       </c>
-      <c r="W60" s="37">
+      <c r="W60" s="38">
         <v>-0.86</v>
       </c>
-      <c r="X60" s="37">
+      <c r="X60" s="38">
         <v>-0.33</v>
       </c>
-      <c r="Y60" s="37">
+      <c r="Y60" s="38">
         <v>-1.49</v>
       </c>
-      <c r="Z60" s="37">
+      <c r="Z60" s="38">
         <v>-0.63</v>
       </c>
-      <c r="AA60" s="34">
+      <c r="AA60" s="35">
         <v>1.14</v>
       </c>
-      <c r="AB60" s="32"/>
-      <c r="AC60" s="32"/>
-      <c r="AD60" s="32"/>
-      <c r="AE60" s="32"/>
-      <c r="AF60" s="32"/>
+      <c r="AB60" s="33"/>
+      <c r="AC60" s="33"/>
+      <c r="AD60" s="33"/>
+      <c r="AE60" s="33"/>
+      <c r="AF60" s="33"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="29" t="s">
-        <v>410</v>
-      </c>
-      <c r="B61" s="30"/>
-      <c r="C61" s="30"/>
-      <c r="D61" s="30"/>
-      <c r="E61" s="30"/>
-      <c r="F61" s="30"/>
-      <c r="G61" s="30"/>
-      <c r="H61" s="30"/>
-      <c r="I61" s="30"/>
-      <c r="J61" s="30"/>
-      <c r="K61" s="30"/>
-      <c r="L61" s="30"/>
-      <c r="M61" s="30"/>
-      <c r="N61" s="30"/>
-      <c r="O61" s="30"/>
-      <c r="P61" s="30"/>
-      <c r="Q61" s="30"/>
-      <c r="R61" s="30"/>
-      <c r="S61" s="30"/>
-      <c r="T61" s="30"/>
-      <c r="U61" s="30"/>
-      <c r="V61" s="30"/>
-      <c r="W61" s="30"/>
-      <c r="X61" s="30"/>
-      <c r="Y61" s="30"/>
-      <c r="Z61" s="30"/>
-      <c r="AA61" s="30"/>
-      <c r="AB61" s="30"/>
-      <c r="AC61" s="30"/>
-      <c r="AD61" s="30"/>
-      <c r="AE61" s="30"/>
-      <c r="AF61" s="30"/>
+      <c r="A61" s="30" t="s">
+        <v>412</v>
+      </c>
+      <c r="B61" s="31"/>
+      <c r="C61" s="31"/>
+      <c r="D61" s="31"/>
+      <c r="E61" s="31"/>
+      <c r="F61" s="31"/>
+      <c r="G61" s="31"/>
+      <c r="H61" s="31"/>
+      <c r="I61" s="31"/>
+      <c r="J61" s="31"/>
+      <c r="K61" s="31"/>
+      <c r="L61" s="31"/>
+      <c r="M61" s="31"/>
+      <c r="N61" s="31"/>
+      <c r="O61" s="31"/>
+      <c r="P61" s="31"/>
+      <c r="Q61" s="31"/>
+      <c r="R61" s="31"/>
+      <c r="S61" s="31"/>
+      <c r="T61" s="31"/>
+      <c r="U61" s="31"/>
+      <c r="V61" s="31"/>
+      <c r="W61" s="31"/>
+      <c r="X61" s="31"/>
+      <c r="Y61" s="31"/>
+      <c r="Z61" s="31"/>
+      <c r="AA61" s="31"/>
+      <c r="AB61" s="31"/>
+      <c r="AC61" s="31"/>
+      <c r="AD61" s="31"/>
+      <c r="AE61" s="31"/>
+      <c r="AF61" s="31"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="31" t="s">
-        <v>411</v>
-      </c>
-      <c r="B62" s="34">
+      <c r="A62" s="32" t="s">
+        <v>413</v>
+      </c>
+      <c r="B62" s="35">
         <v>0.55</v>
       </c>
-      <c r="C62" s="34">
+      <c r="C62" s="35">
         <v>0.38</v>
       </c>
-      <c r="D62" s="34">
+      <c r="D62" s="35">
         <v>0.38</v>
       </c>
-      <c r="E62" s="34">
+      <c r="E62" s="35">
         <v>0.26</v>
       </c>
-      <c r="F62" s="34">
+      <c r="F62" s="35">
         <v>0.32</v>
       </c>
-      <c r="G62" s="34">
+      <c r="G62" s="35">
         <v>0.31</v>
       </c>
-      <c r="H62" s="34">
+      <c r="H62" s="35">
         <v>0.32</v>
       </c>
-      <c r="I62" s="34">
+      <c r="I62" s="35">
         <v>0.41</v>
       </c>
-      <c r="J62" s="34">
+      <c r="J62" s="35">
         <v>0.36</v>
       </c>
-      <c r="K62" s="34">
+      <c r="K62" s="35">
         <v>0.33</v>
       </c>
-      <c r="L62" s="34">
+      <c r="L62" s="35">
         <v>0.44</v>
       </c>
-      <c r="M62" s="34">
+      <c r="M62" s="35">
         <v>0.27</v>
       </c>
-      <c r="N62" s="34">
+      <c r="N62" s="35">
         <v>0.27</v>
       </c>
-      <c r="O62" s="34">
+      <c r="O62" s="35">
         <v>0.15</v>
       </c>
-      <c r="P62" s="34">
+      <c r="P62" s="35">
         <v>0.17</v>
       </c>
-      <c r="Q62" s="34">
+      <c r="Q62" s="35">
         <v>0.23</v>
       </c>
-      <c r="R62" s="34">
+      <c r="R62" s="35">
         <v>0.27</v>
       </c>
-      <c r="S62" s="34">
+      <c r="S62" s="35">
         <v>0.25</v>
       </c>
-      <c r="T62" s="34">
+      <c r="T62" s="35">
         <v>0.46</v>
       </c>
-      <c r="U62" s="34">
+      <c r="U62" s="35">
         <v>0.39</v>
       </c>
-      <c r="V62" s="34">
+      <c r="V62" s="35">
         <v>0.35</v>
       </c>
-      <c r="W62" s="34">
+      <c r="W62" s="35">
         <v>0.25</v>
       </c>
-      <c r="X62" s="34">
+      <c r="X62" s="35">
         <v>0.18</v>
       </c>
-      <c r="Y62" s="34">
+      <c r="Y62" s="35">
         <v>0.23</v>
       </c>
-      <c r="Z62" s="34">
+      <c r="Z62" s="35">
         <v>0.28</v>
       </c>
-      <c r="AA62" s="34">
+      <c r="AA62" s="35">
         <v>0.31</v>
       </c>
-      <c r="AB62" s="34">
+      <c r="AB62" s="35">
         <v>0.26</v>
       </c>
-      <c r="AC62" s="34">
+      <c r="AC62" s="35">
         <v>0.26</v>
       </c>
-      <c r="AD62" s="34">
+      <c r="AD62" s="35">
         <v>0.44</v>
       </c>
-      <c r="AE62" s="34">
+      <c r="AE62" s="35">
         <v>0.46</v>
       </c>
-      <c r="AF62" s="34">
+      <c r="AF62" s="35">
         <v>0.42</v>
       </c>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="31" t="s">
-        <v>412</v>
-      </c>
-      <c r="B63" s="34">
+      <c r="A63" s="32" t="s">
+        <v>414</v>
+      </c>
+      <c r="B63" s="35">
         <v>0.39</v>
       </c>
-      <c r="C63" s="34">
+      <c r="C63" s="35">
         <v>0.34</v>
       </c>
-      <c r="D63" s="34">
+      <c r="D63" s="35">
         <v>0.32</v>
       </c>
-      <c r="E63" s="34">
+      <c r="E63" s="35">
         <v>0.32</v>
       </c>
-      <c r="F63" s="34">
+      <c r="F63" s="35">
         <v>0.34</v>
       </c>
-      <c r="G63" s="34">
+      <c r="G63" s="35">
         <v>0.35</v>
       </c>
-      <c r="H63" s="34">
+      <c r="H63" s="35">
         <v>0.37</v>
       </c>
-      <c r="I63" s="34">
+      <c r="I63" s="35">
         <v>0.37</v>
       </c>
-      <c r="J63" s="34">
+      <c r="J63" s="35">
         <v>0.34</v>
       </c>
-      <c r="K63" s="34">
+      <c r="K63" s="35">
         <v>0.3</v>
       </c>
-      <c r="L63" s="34">
+      <c r="L63" s="35">
         <v>0.28</v>
       </c>
-      <c r="M63" s="34">
+      <c r="M63" s="35">
         <v>0.22</v>
       </c>
-      <c r="N63" s="34">
+      <c r="N63" s="35">
         <v>0.21</v>
       </c>
-      <c r="O63" s="34">
+      <c r="O63" s="35">
         <v>0.21</v>
       </c>
-      <c r="P63" s="34">
+      <c r="P63" s="35">
         <v>0.27</v>
       </c>
-      <c r="Q63" s="34">
+      <c r="Q63" s="35">
         <v>0.31</v>
       </c>
-      <c r="R63" s="34">
+      <c r="R63" s="35">
         <v>0.34</v>
       </c>
-      <c r="S63" s="34">
+      <c r="S63" s="35">
         <v>0.34</v>
       </c>
-      <c r="T63" s="34">
+      <c r="T63" s="35">
         <v>0.34</v>
       </c>
-      <c r="U63" s="34">
+      <c r="U63" s="35">
         <v>0.29</v>
       </c>
-      <c r="V63" s="34">
+      <c r="V63" s="35">
         <v>0.26</v>
       </c>
-      <c r="W63" s="34">
+      <c r="W63" s="35">
         <v>0.25</v>
       </c>
-      <c r="X63" s="34">
+      <c r="X63" s="35">
         <v>0.25</v>
       </c>
-      <c r="Y63" s="34">
+      <c r="Y63" s="35">
         <v>0.27</v>
       </c>
-      <c r="Z63" s="34">
+      <c r="Z63" s="35">
         <v>0.3</v>
       </c>
-      <c r="AA63" s="34">
+      <c r="AA63" s="35">
         <v>0.34</v>
       </c>
-      <c r="AB63" s="34">
+      <c r="AB63" s="35">
         <v>0.36</v>
       </c>
-      <c r="AC63" s="32"/>
-      <c r="AD63" s="32"/>
-      <c r="AE63" s="32"/>
-      <c r="AF63" s="32"/>
+      <c r="AC63" s="33"/>
+      <c r="AD63" s="33"/>
+      <c r="AE63" s="33"/>
+      <c r="AF63" s="33"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="29" t="s">
-        <v>413</v>
-      </c>
-      <c r="B64" s="30"/>
-      <c r="C64" s="30"/>
-      <c r="D64" s="30"/>
-      <c r="E64" s="30"/>
-      <c r="F64" s="30"/>
-      <c r="G64" s="30"/>
-      <c r="H64" s="30"/>
-      <c r="I64" s="30"/>
-      <c r="J64" s="30"/>
-      <c r="K64" s="30"/>
-      <c r="L64" s="30"/>
-      <c r="M64" s="30"/>
-      <c r="N64" s="30"/>
-      <c r="O64" s="30"/>
-      <c r="P64" s="30"/>
-      <c r="Q64" s="30"/>
-      <c r="R64" s="30"/>
-      <c r="S64" s="30"/>
-      <c r="T64" s="30"/>
-      <c r="U64" s="30"/>
-      <c r="V64" s="30"/>
-      <c r="W64" s="30"/>
-      <c r="X64" s="30"/>
-      <c r="Y64" s="30"/>
-      <c r="Z64" s="30"/>
-      <c r="AA64" s="30"/>
-      <c r="AB64" s="30"/>
-      <c r="AC64" s="30"/>
-      <c r="AD64" s="30"/>
-      <c r="AE64" s="30"/>
-      <c r="AF64" s="30"/>
+      <c r="A64" s="30" t="s">
+        <v>415</v>
+      </c>
+      <c r="B64" s="31"/>
+      <c r="C64" s="31"/>
+      <c r="D64" s="31"/>
+      <c r="E64" s="31"/>
+      <c r="F64" s="31"/>
+      <c r="G64" s="31"/>
+      <c r="H64" s="31"/>
+      <c r="I64" s="31"/>
+      <c r="J64" s="31"/>
+      <c r="K64" s="31"/>
+      <c r="L64" s="31"/>
+      <c r="M64" s="31"/>
+      <c r="N64" s="31"/>
+      <c r="O64" s="31"/>
+      <c r="P64" s="31"/>
+      <c r="Q64" s="31"/>
+      <c r="R64" s="31"/>
+      <c r="S64" s="31"/>
+      <c r="T64" s="31"/>
+      <c r="U64" s="31"/>
+      <c r="V64" s="31"/>
+      <c r="W64" s="31"/>
+      <c r="X64" s="31"/>
+      <c r="Y64" s="31"/>
+      <c r="Z64" s="31"/>
+      <c r="AA64" s="31"/>
+      <c r="AB64" s="31"/>
+      <c r="AC64" s="31"/>
+      <c r="AD64" s="31"/>
+      <c r="AE64" s="31"/>
+      <c r="AF64" s="31"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="31" t="s">
-        <v>414</v>
-      </c>
-      <c r="B65" s="34">
+      <c r="A65" s="32" t="s">
+        <v>416</v>
+      </c>
+      <c r="B65" s="35">
         <v>6.0</v>
       </c>
-      <c r="C65" s="34">
+      <c r="C65" s="35">
         <v>4.41</v>
       </c>
-      <c r="D65" s="34">
+      <c r="D65" s="35">
         <v>4.13</v>
       </c>
-      <c r="E65" s="34">
+      <c r="E65" s="35">
         <v>3.39</v>
       </c>
-      <c r="F65" s="34">
+      <c r="F65" s="35">
         <v>3.79</v>
       </c>
-      <c r="G65" s="34">
+      <c r="G65" s="35">
         <v>3.2</v>
       </c>
-      <c r="H65" s="34">
+      <c r="H65" s="35">
         <v>4.59</v>
       </c>
-      <c r="I65" s="34">
+      <c r="I65" s="35">
         <v>5.8</v>
       </c>
-      <c r="J65" s="34">
+      <c r="J65" s="35">
         <v>5.53</v>
       </c>
-      <c r="K65" s="34">
+      <c r="K65" s="35">
         <v>4.62</v>
       </c>
-      <c r="L65" s="34">
+      <c r="L65" s="35">
         <v>5.71</v>
       </c>
-      <c r="M65" s="34">
+      <c r="M65" s="35">
         <v>3.61</v>
       </c>
-      <c r="N65" s="34">
+      <c r="N65" s="35">
         <v>4.03</v>
       </c>
-      <c r="O65" s="34">
+      <c r="O65" s="35">
         <v>2.13</v>
       </c>
-      <c r="P65" s="34">
+      <c r="P65" s="35">
         <v>2.73</v>
       </c>
-      <c r="Q65" s="34">
+      <c r="Q65" s="35">
         <v>4.05</v>
       </c>
-      <c r="R65" s="34">
+      <c r="R65" s="35">
         <v>3.53</v>
       </c>
-      <c r="S65" s="34">
+      <c r="S65" s="35">
         <v>3.03</v>
       </c>
-      <c r="T65" s="34">
+      <c r="T65" s="35">
         <v>6.1</v>
       </c>
-      <c r="U65" s="34">
+      <c r="U65" s="35">
         <v>5.88</v>
       </c>
-      <c r="V65" s="34">
+      <c r="V65" s="35">
         <v>6.26</v>
       </c>
-      <c r="W65" s="34">
+      <c r="W65" s="35">
         <v>4.12</v>
       </c>
-      <c r="X65" s="34">
+      <c r="X65" s="35">
         <v>3.64</v>
       </c>
-      <c r="Y65" s="34">
+      <c r="Y65" s="35">
         <v>3.78</v>
       </c>
-      <c r="Z65" s="34">
+      <c r="Z65" s="35">
         <v>4.76</v>
       </c>
-      <c r="AA65" s="34">
+      <c r="AA65" s="35">
         <v>4.41</v>
       </c>
-      <c r="AB65" s="34">
+      <c r="AB65" s="35">
         <v>3.41</v>
       </c>
-      <c r="AC65" s="34">
+      <c r="AC65" s="35">
         <v>3.15</v>
       </c>
-      <c r="AD65" s="34">
+      <c r="AD65" s="35">
         <v>5.64</v>
       </c>
-      <c r="AE65" s="34">
+      <c r="AE65" s="35">
         <v>5.13</v>
       </c>
-      <c r="AF65" s="34">
+      <c r="AF65" s="35">
         <v>5.0</v>
       </c>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="31" t="s">
-        <v>415</v>
-      </c>
-      <c r="B66" s="34">
+      <c r="A66" s="32" t="s">
+        <v>417</v>
+      </c>
+      <c r="B66" s="35">
         <v>4.48</v>
       </c>
-      <c r="C66" s="34">
+      <c r="C66" s="35">
         <v>3.85</v>
       </c>
-      <c r="D66" s="34">
+      <c r="D66" s="35">
         <v>3.8</v>
       </c>
-      <c r="E66" s="34">
+      <c r="E66" s="35">
         <v>3.99</v>
       </c>
-      <c r="F66" s="34">
+      <c r="F66" s="35">
         <v>4.38</v>
       </c>
-      <c r="G66" s="34">
+      <c r="G66" s="35">
         <v>4.58</v>
       </c>
-      <c r="H66" s="34">
+      <c r="H66" s="35">
         <v>5.24</v>
       </c>
-      <c r="I66" s="34">
+      <c r="I66" s="35">
         <v>5.13</v>
       </c>
-      <c r="J66" s="34">
+      <c r="J66" s="35">
         <v>4.8</v>
       </c>
-      <c r="K66" s="34">
+      <c r="K66" s="35">
         <v>4.22</v>
       </c>
-      <c r="L66" s="34">
+      <c r="L66" s="35">
         <v>3.91</v>
       </c>
-      <c r="M66" s="34">
+      <c r="M66" s="35">
         <v>3.29</v>
       </c>
-      <c r="N66" s="34">
+      <c r="N66" s="35">
         <v>3.23</v>
       </c>
-      <c r="O66" s="34">
+      <c r="O66" s="35">
         <v>2.98</v>
       </c>
-      <c r="P66" s="34">
+      <c r="P66" s="35">
         <v>3.78</v>
       </c>
-      <c r="Q66" s="34">
+      <c r="Q66" s="35">
         <v>4.34</v>
       </c>
-      <c r="R66" s="34">
+      <c r="R66" s="35">
         <v>4.62</v>
       </c>
-      <c r="S66" s="34">
+      <c r="S66" s="35">
         <v>4.85</v>
       </c>
-      <c r="T66" s="34">
+      <c r="T66" s="35">
         <v>5.41</v>
       </c>
-      <c r="U66" s="34">
+      <c r="U66" s="35">
         <v>4.86</v>
       </c>
-      <c r="V66" s="34">
+      <c r="V66" s="35">
         <v>4.55</v>
       </c>
-      <c r="W66" s="34">
+      <c r="W66" s="35">
         <v>4.13</v>
       </c>
-      <c r="X66" s="34">
+      <c r="X66" s="35">
         <v>3.97</v>
       </c>
-      <c r="Y66" s="34">
+      <c r="Y66" s="35">
         <v>3.85</v>
       </c>
-      <c r="Z66" s="34">
+      <c r="Z66" s="35">
         <v>4.2</v>
       </c>
-      <c r="AA66" s="34">
+      <c r="AA66" s="35">
         <v>4.28</v>
       </c>
-      <c r="AB66" s="34">
+      <c r="AB66" s="35">
         <v>4.35</v>
       </c>
-      <c r="AC66" s="32"/>
-      <c r="AD66" s="32"/>
-      <c r="AE66" s="32"/>
-      <c r="AF66" s="32"/>
+      <c r="AC66" s="33"/>
+      <c r="AD66" s="33"/>
+      <c r="AE66" s="33"/>
+      <c r="AF66" s="33"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="29" t="s">
-        <v>416</v>
-      </c>
-      <c r="B67" s="30"/>
-      <c r="C67" s="30"/>
-      <c r="D67" s="30"/>
-      <c r="E67" s="30"/>
-      <c r="F67" s="30"/>
-      <c r="G67" s="30"/>
-      <c r="H67" s="30"/>
-      <c r="I67" s="30"/>
-      <c r="J67" s="30"/>
-      <c r="K67" s="30"/>
-      <c r="L67" s="30"/>
-      <c r="M67" s="30"/>
-      <c r="N67" s="30"/>
-      <c r="O67" s="30"/>
-      <c r="P67" s="30"/>
-      <c r="Q67" s="30"/>
-      <c r="R67" s="30"/>
-      <c r="S67" s="30"/>
-      <c r="T67" s="30"/>
-      <c r="U67" s="30"/>
-      <c r="V67" s="30"/>
-      <c r="W67" s="30"/>
-      <c r="X67" s="30"/>
-      <c r="Y67" s="30"/>
-      <c r="Z67" s="30"/>
-      <c r="AA67" s="30"/>
-      <c r="AB67" s="30"/>
-      <c r="AC67" s="30"/>
-      <c r="AD67" s="30"/>
-      <c r="AE67" s="30"/>
-      <c r="AF67" s="30"/>
+      <c r="A67" s="30" t="s">
+        <v>418</v>
+      </c>
+      <c r="B67" s="31"/>
+      <c r="C67" s="31"/>
+      <c r="D67" s="31"/>
+      <c r="E67" s="31"/>
+      <c r="F67" s="31"/>
+      <c r="G67" s="31"/>
+      <c r="H67" s="31"/>
+      <c r="I67" s="31"/>
+      <c r="J67" s="31"/>
+      <c r="K67" s="31"/>
+      <c r="L67" s="31"/>
+      <c r="M67" s="31"/>
+      <c r="N67" s="31"/>
+      <c r="O67" s="31"/>
+      <c r="P67" s="31"/>
+      <c r="Q67" s="31"/>
+      <c r="R67" s="31"/>
+      <c r="S67" s="31"/>
+      <c r="T67" s="31"/>
+      <c r="U67" s="31"/>
+      <c r="V67" s="31"/>
+      <c r="W67" s="31"/>
+      <c r="X67" s="31"/>
+      <c r="Y67" s="31"/>
+      <c r="Z67" s="31"/>
+      <c r="AA67" s="31"/>
+      <c r="AB67" s="31"/>
+      <c r="AC67" s="31"/>
+      <c r="AD67" s="31"/>
+      <c r="AE67" s="31"/>
+      <c r="AF67" s="31"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="31" t="s">
-        <v>417</v>
-      </c>
-      <c r="B68" s="34">
+      <c r="A68" s="32" t="s">
+        <v>419</v>
+      </c>
+      <c r="B68" s="35">
         <v>4.5</v>
       </c>
-      <c r="C68" s="34">
+      <c r="C68" s="35">
         <v>4.22</v>
       </c>
-      <c r="D68" s="34">
+      <c r="D68" s="35">
         <v>6.9</v>
       </c>
-      <c r="E68" s="34">
+      <c r="E68" s="35">
         <v>8.1</v>
       </c>
-      <c r="F68" s="34">
+      <c r="F68" s="35">
         <v>9.85</v>
       </c>
-      <c r="G68" s="34">
+      <c r="G68" s="35">
         <v>2.61</v>
       </c>
-      <c r="H68" s="34">
+      <c r="H68" s="35">
         <v>4.55</v>
       </c>
-      <c r="I68" s="34">
+      <c r="I68" s="35">
         <v>6.57</v>
       </c>
-      <c r="J68" s="34">
+      <c r="J68" s="35">
         <v>8.2</v>
       </c>
-      <c r="K68" s="34">
+      <c r="K68" s="35">
         <v>8.18</v>
       </c>
-      <c r="L68" s="34">
+      <c r="L68" s="35">
         <v>3.99</v>
       </c>
-      <c r="M68" s="34">
+      <c r="M68" s="35">
         <v>3.7</v>
       </c>
-      <c r="N68" s="34">
+      <c r="N68" s="35">
         <v>48.06</v>
       </c>
-      <c r="O68" s="34">
+      <c r="O68" s="35">
         <v>2.65</v>
       </c>
-      <c r="P68" s="34">
+      <c r="P68" s="35">
         <v>3.12</v>
       </c>
-      <c r="Q68" s="34">
+      <c r="Q68" s="35">
         <v>4.28</v>
       </c>
-      <c r="R68" s="34">
+      <c r="R68" s="35">
         <v>2.85</v>
       </c>
-      <c r="S68" s="34">
+      <c r="S68" s="35">
         <v>3.41</v>
       </c>
-      <c r="T68" s="34">
+      <c r="T68" s="35">
         <v>8.28</v>
       </c>
-      <c r="U68" s="34">
+      <c r="U68" s="35">
         <v>12.43</v>
       </c>
-      <c r="V68" s="34">
+      <c r="V68" s="35">
         <v>7.82</v>
       </c>
-      <c r="W68" s="34">
+      <c r="W68" s="35">
         <v>5.84</v>
       </c>
-      <c r="X68" s="34">
+      <c r="X68" s="35">
         <v>3.47</v>
       </c>
-      <c r="Y68" s="34">
+      <c r="Y68" s="35">
         <v>3.57</v>
       </c>
-      <c r="Z68" s="32"/>
-      <c r="AA68" s="34">
+      <c r="Z68" s="33"/>
+      <c r="AA68" s="35">
         <v>4.13</v>
       </c>
-      <c r="AB68" s="34">
+      <c r="AB68" s="35">
         <v>4.45</v>
       </c>
-      <c r="AC68" s="34">
+      <c r="AC68" s="35">
         <v>4.39</v>
       </c>
-      <c r="AD68" s="34">
+      <c r="AD68" s="35">
         <v>9.89</v>
       </c>
-      <c r="AE68" s="34">
+      <c r="AE68" s="35">
         <v>7.36</v>
       </c>
-      <c r="AF68" s="34">
+      <c r="AF68" s="35">
         <v>6.31</v>
       </c>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="31" t="s">
-        <v>418</v>
-      </c>
-      <c r="B69" s="34">
+      <c r="A69" s="32" t="s">
+        <v>420</v>
+      </c>
+      <c r="B69" s="35">
         <v>5.47</v>
       </c>
-      <c r="C69" s="34">
+      <c r="C69" s="35">
         <v>5.14</v>
       </c>
-      <c r="D69" s="34">
+      <c r="D69" s="35">
         <v>5.41</v>
       </c>
-      <c r="E69" s="34">
+      <c r="E69" s="35">
         <v>5.24</v>
       </c>
-      <c r="F69" s="34">
+      <c r="F69" s="35">
         <v>5.19</v>
       </c>
-      <c r="G69" s="34">
+      <c r="G69" s="35">
         <v>4.97</v>
       </c>
-      <c r="H69" s="34">
+      <c r="H69" s="35">
         <v>5.68</v>
       </c>
-      <c r="I69" s="34">
+      <c r="I69" s="35">
         <v>5.64</v>
       </c>
-      <c r="J69" s="34">
+      <c r="J69" s="35">
         <v>6.02</v>
       </c>
-      <c r="K69" s="34">
+      <c r="K69" s="35">
         <v>5.11</v>
       </c>
-      <c r="L69" s="34">
+      <c r="L69" s="35">
         <v>4.33</v>
       </c>
-      <c r="M69" s="34">
+      <c r="M69" s="35">
         <v>4.56</v>
       </c>
-      <c r="N69" s="34">
+      <c r="N69" s="35">
         <v>4.37</v>
       </c>
-      <c r="O69" s="34">
+      <c r="O69" s="35">
         <v>3.16</v>
       </c>
-      <c r="P69" s="34">
+      <c r="P69" s="35">
         <v>4.02</v>
       </c>
-      <c r="Q69" s="34">
+      <c r="Q69" s="35">
         <v>4.91</v>
       </c>
-      <c r="R69" s="34">
+      <c r="R69" s="35">
         <v>5.35</v>
       </c>
-      <c r="S69" s="34">
+      <c r="S69" s="35">
         <v>6.54</v>
       </c>
-      <c r="T69" s="34">
+      <c r="T69" s="35">
         <v>7.44</v>
       </c>
-      <c r="U69" s="34">
+      <c r="U69" s="35">
         <v>6.18</v>
       </c>
-      <c r="V69" s="34">
+      <c r="V69" s="35">
         <v>7.16</v>
       </c>
-      <c r="W69" s="34">
+      <c r="W69" s="35">
         <v>6.0</v>
       </c>
-      <c r="X69" s="34">
+      <c r="X69" s="35">
         <v>5.65</v>
       </c>
-      <c r="Y69" s="34">
+      <c r="Y69" s="35">
         <v>5.96</v>
       </c>
-      <c r="Z69" s="34">
+      <c r="Z69" s="35">
         <v>7.73</v>
       </c>
-      <c r="AA69" s="34">
+      <c r="AA69" s="35">
         <v>5.57</v>
       </c>
-      <c r="AB69" s="34">
+      <c r="AB69" s="35">
         <v>6.15</v>
       </c>
-      <c r="AC69" s="32"/>
-      <c r="AD69" s="32"/>
-      <c r="AE69" s="32"/>
-      <c r="AF69" s="32"/>
+      <c r="AC69" s="33"/>
+      <c r="AD69" s="33"/>
+      <c r="AE69" s="33"/>
+      <c r="AF69" s="33"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="29" t="s">
-        <v>419</v>
-      </c>
-      <c r="B70" s="30"/>
-      <c r="C70" s="30"/>
-      <c r="D70" s="30"/>
-      <c r="E70" s="30"/>
-      <c r="F70" s="30"/>
-      <c r="G70" s="30"/>
-      <c r="H70" s="30"/>
-      <c r="I70" s="30"/>
-      <c r="J70" s="30"/>
-      <c r="K70" s="30"/>
-      <c r="L70" s="30"/>
-      <c r="M70" s="30"/>
-      <c r="N70" s="30"/>
-      <c r="O70" s="30"/>
-      <c r="P70" s="30"/>
-      <c r="Q70" s="30"/>
-      <c r="R70" s="30"/>
-      <c r="S70" s="30"/>
-      <c r="T70" s="30"/>
-      <c r="U70" s="30"/>
-      <c r="V70" s="30"/>
-      <c r="W70" s="30"/>
-      <c r="X70" s="30"/>
-      <c r="Y70" s="30"/>
-      <c r="Z70" s="30"/>
-      <c r="AA70" s="30"/>
-      <c r="AB70" s="30"/>
-      <c r="AC70" s="30"/>
-      <c r="AD70" s="30"/>
-      <c r="AE70" s="30"/>
-      <c r="AF70" s="30"/>
+      <c r="A70" s="30" t="s">
+        <v>421</v>
+      </c>
+      <c r="B70" s="31"/>
+      <c r="C70" s="31"/>
+      <c r="D70" s="31"/>
+      <c r="E70" s="31"/>
+      <c r="F70" s="31"/>
+      <c r="G70" s="31"/>
+      <c r="H70" s="31"/>
+      <c r="I70" s="31"/>
+      <c r="J70" s="31"/>
+      <c r="K70" s="31"/>
+      <c r="L70" s="31"/>
+      <c r="M70" s="31"/>
+      <c r="N70" s="31"/>
+      <c r="O70" s="31"/>
+      <c r="P70" s="31"/>
+      <c r="Q70" s="31"/>
+      <c r="R70" s="31"/>
+      <c r="S70" s="31"/>
+      <c r="T70" s="31"/>
+      <c r="U70" s="31"/>
+      <c r="V70" s="31"/>
+      <c r="W70" s="31"/>
+      <c r="X70" s="31"/>
+      <c r="Y70" s="31"/>
+      <c r="Z70" s="31"/>
+      <c r="AA70" s="31"/>
+      <c r="AB70" s="31"/>
+      <c r="AC70" s="31"/>
+      <c r="AD70" s="31"/>
+      <c r="AE70" s="31"/>
+      <c r="AF70" s="31"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="31" t="s">
-        <v>420</v>
-      </c>
-      <c r="B71" s="34">
+      <c r="A71" s="32" t="s">
+        <v>422</v>
+      </c>
+      <c r="B71" s="35">
         <v>6.64</v>
       </c>
-      <c r="C71" s="34">
+      <c r="C71" s="35">
         <v>7.37</v>
       </c>
-      <c r="D71" s="34">
+      <c r="D71" s="35">
         <v>41.13</v>
       </c>
-      <c r="E71" s="32"/>
-      <c r="F71" s="32"/>
-      <c r="G71" s="34">
+      <c r="E71" s="33"/>
+      <c r="F71" s="33"/>
+      <c r="G71" s="35">
         <v>3.92</v>
       </c>
-      <c r="H71" s="34">
+      <c r="H71" s="35">
         <v>9.17</v>
       </c>
-      <c r="I71" s="34">
+      <c r="I71" s="35">
         <v>17.36</v>
       </c>
-      <c r="J71" s="32"/>
-      <c r="K71" s="32"/>
-      <c r="L71" s="34">
+      <c r="J71" s="33"/>
+      <c r="K71" s="33"/>
+      <c r="L71" s="35">
         <v>6.35</v>
       </c>
-      <c r="M71" s="34">
+      <c r="M71" s="35">
         <v>7.31</v>
       </c>
-      <c r="N71" s="32"/>
-      <c r="O71" s="34">
+      <c r="N71" s="33"/>
+      <c r="O71" s="35">
         <v>16.25</v>
       </c>
-      <c r="P71" s="34">
+      <c r="P71" s="35">
         <v>30.57</v>
       </c>
-      <c r="Q71" s="32"/>
-      <c r="R71" s="34">
+      <c r="Q71" s="33"/>
+      <c r="R71" s="35">
         <v>10.07</v>
       </c>
-      <c r="S71" s="34">
+      <c r="S71" s="35">
         <v>58.06</v>
       </c>
-      <c r="T71" s="34">
+      <c r="T71" s="35">
         <v>8.28</v>
       </c>
-      <c r="U71" s="32"/>
-      <c r="V71" s="32"/>
-      <c r="W71" s="32"/>
-      <c r="X71" s="34">
+      <c r="U71" s="33"/>
+      <c r="V71" s="33"/>
+      <c r="W71" s="33"/>
+      <c r="X71" s="35">
         <v>5.12</v>
       </c>
-      <c r="Y71" s="34">
+      <c r="Y71" s="35">
         <v>10.66</v>
       </c>
-      <c r="Z71" s="32"/>
-      <c r="AA71" s="34">
+      <c r="Z71" s="33"/>
+      <c r="AA71" s="35">
         <v>38.97</v>
       </c>
-      <c r="AB71" s="34">
+      <c r="AB71" s="35">
         <v>38.02</v>
       </c>
-      <c r="AC71" s="33">
+      <c r="AC71" s="34">
         <v>553.01</v>
       </c>
-      <c r="AD71" s="32"/>
-      <c r="AE71" s="34">
+      <c r="AD71" s="33"/>
+      <c r="AE71" s="35">
         <v>49.33</v>
       </c>
-      <c r="AF71" s="32"/>
+      <c r="AF71" s="33"/>
     </row>
     <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="31" t="s">
-        <v>421</v>
-      </c>
-      <c r="B72" s="34">
+      <c r="A72" s="32" t="s">
+        <v>423</v>
+      </c>
+      <c r="B72" s="35">
         <v>14.45</v>
       </c>
-      <c r="C72" s="34">
+      <c r="C72" s="35">
         <v>16.45</v>
       </c>
-      <c r="D72" s="34">
+      <c r="D72" s="35">
         <v>22.59</v>
       </c>
-      <c r="E72" s="34">
+      <c r="E72" s="35">
         <v>18.55</v>
       </c>
-      <c r="F72" s="34">
+      <c r="F72" s="35">
         <v>14.98</v>
       </c>
-      <c r="G72" s="34">
+      <c r="G72" s="35">
         <v>13.81</v>
       </c>
-      <c r="H72" s="34">
+      <c r="H72" s="35">
         <v>18.32</v>
       </c>
-      <c r="I72" s="34">
+      <c r="I72" s="35">
         <v>19.17</v>
       </c>
-      <c r="J72" s="34">
+      <c r="J72" s="35">
         <v>36.81</v>
       </c>
-      <c r="K72" s="34">
+      <c r="K72" s="35">
         <v>23.16</v>
       </c>
-      <c r="L72" s="34">
+      <c r="L72" s="35">
         <v>12.83</v>
       </c>
-      <c r="M72" s="33">
+      <c r="M72" s="34">
         <v>113.02</v>
       </c>
-      <c r="N72" s="32"/>
-      <c r="O72" s="34">
+      <c r="N72" s="33"/>
+      <c r="O72" s="35">
         <v>31.02</v>
       </c>
-      <c r="P72" s="34">
+      <c r="P72" s="35">
         <v>18.42</v>
       </c>
-      <c r="Q72" s="34">
+      <c r="Q72" s="35">
         <v>36.07</v>
       </c>
-      <c r="R72" s="34">
+      <c r="R72" s="35">
         <v>34.52</v>
       </c>
-      <c r="S72" s="33">
+      <c r="S72" s="34">
         <v>103.9</v>
       </c>
-      <c r="T72" s="34">
+      <c r="T72" s="35">
         <v>39.51</v>
       </c>
-      <c r="U72" s="32"/>
-      <c r="V72" s="32"/>
-      <c r="W72" s="32"/>
-      <c r="X72" s="32"/>
-      <c r="Y72" s="32"/>
-      <c r="Z72" s="32"/>
-      <c r="AA72" s="33">
+      <c r="U72" s="33"/>
+      <c r="V72" s="33"/>
+      <c r="W72" s="33"/>
+      <c r="X72" s="33"/>
+      <c r="Y72" s="33"/>
+      <c r="Z72" s="33"/>
+      <c r="AA72" s="34">
         <v>184.59</v>
       </c>
-      <c r="AB72" s="32"/>
-      <c r="AC72" s="32"/>
-      <c r="AD72" s="32"/>
-      <c r="AE72" s="32"/>
-      <c r="AF72" s="32"/>
+      <c r="AB72" s="33"/>
+      <c r="AC72" s="33"/>
+      <c r="AD72" s="33"/>
+      <c r="AE72" s="33"/>
+      <c r="AF72" s="33"/>
     </row>
     <row r="73" ht="15.75" customHeight="1"/>
     <row r="74" ht="15.75" customHeight="1"/>
